--- a/workspaces/nasdaq_hourly_24hrs/volume/volume_ratio_12.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volume/volume_ratio_12.xlsx
@@ -618,1969 +618,1969 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.4</t>
+          <t>X ≈ 0.4008</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>46.01353848502531</v>
+        <v>46.03136398195772</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>45.69551098832704</v>
+        <v>45.7138032528693</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>44.28121115508188</v>
+        <v>44.30169682802549</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>43.58553037829525</v>
+        <v>43.60702373056641</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>43.23545300382924</v>
+        <v>43.2862493317085</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>43.43707682916801</v>
+        <v>43.48765962931985</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.079441072153692</v>
+        <v>-7.011038717820803</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.359161908067705</v>
+        <v>-7.290292054704494</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.321068156909192</v>
+        <v>-7.252267831039902</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.090783601119774</v>
+        <v>-8.023431686528212</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>41.99351664892069</v>
+        <v>42.06078266292433</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>41.72978777043572</v>
+        <v>41.79740128511666</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>40.62166864407362</v>
+        <v>40.69061229311735</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>40.41452582210058</v>
+        <v>40.46994541331414</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>39.77083838924649</v>
+        <v>39.82725859664581</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>40.37858897016604</v>
+        <v>40.43420069840798</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>40.24504684171654</v>
+        <v>40.31457591814872</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>40.1539329425411</v>
+        <v>40.22361089801936</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>40.38359926685141</v>
+        <v>40.45305229777581</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>40.58365193565123</v>
+        <v>40.65291495247375</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>40.05449203008909</v>
+        <v>40.1107479859545</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>39.99223913083519</v>
+        <v>40.04866121897347</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>40.28061970184157</v>
+        <v>40.33670668981365</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>40.2046783625731</v>
+        <v>40.27453271028038</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.4727</t>
+          <t>X ≈ 0.4737</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>21.18188115459593</v>
+        <v>21.20788550289091</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>20.8554936953763</v>
+        <v>20.88197900000102</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>19.43284499047135</v>
+        <v>19.46153878638703</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>18.72879490009128</v>
+        <v>18.7585107995851</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.494299591459566</v>
+        <v>-6.427001151297773</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-31.18253460067905</v>
+        <v>-31.10714142362475</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-31.96084780238991</v>
+        <v>-31.88414727803816</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.359094520393597</v>
+        <v>-7.290220425448368</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>17.5773318412498</v>
+        <v>17.63781371150303</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>16.80762477379806</v>
+        <v>16.87507930509089</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>17.0864192795303</v>
+        <v>17.15359078941741</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>16.81427571565455</v>
+        <v>16.88180325179387</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>15.6977382448112</v>
+        <v>15.76660444631677</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>15.48216697137536</v>
+        <v>15.54593840420365</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>39.7706448826981</v>
+        <v>39.82703759832359</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>40.37842125297657</v>
+        <v>40.43400516974023</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>40.24488024825894</v>
+        <v>40.31440941209355</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>40.15379455920467</v>
+        <v>40.22347258593615</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>40.38348844740606</v>
+        <v>40.45294153550925</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>40.58356760922379</v>
+        <v>40.65283067249875</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>40.05443631932082</v>
+        <v>40.11066447852135</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>39.99221136469523</v>
+        <v>40.04860572504011</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>40.28061970184157</v>
+        <v>40.33667884422364</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>40.2046783625731</v>
+        <v>40.27453271027469</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.5454</t>
+          <t>X ≈ 0.5465</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-36.75686135844326</v>
+        <v>-36.71168816654075</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-20.54345123252849</v>
+        <v>-20.50325689453382</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.415064726999532</v>
+        <v>-5.378139109563719</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.127504809737232</v>
+        <v>-6.089542322339732</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-6.494185108959876</v>
+        <v>-6.426881319593626</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.309202303306073</v>
+        <v>-6.242072724972992</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.079093767099167</v>
+        <v>-7.010669735937768</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9.234138865426758</v>
+        <v>9.297470063717739</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.321044619110516</v>
+        <v>-7.252244247372381</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.090737668423785</v>
+        <v>-8.023387149467005</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.820385421555322</v>
+        <v>-7.753309308874435</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>25.11910178771855</v>
+        <v>25.18665786675938</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>24.00541420251422</v>
+        <v>24.07430608580254</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>23.79268738040886</v>
+        <v>23.85364144550498</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>23.14333692843469</v>
+        <v>23.20529095483491</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>23.74549909499697</v>
+        <v>23.80665338179418</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>6.979318482788557</v>
+        <v>7.048778402073523</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>23.51526027801208</v>
+        <v>23.58490949195709</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>23.73933522613118</v>
+        <v>23.80876524854114</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>23.9337897967971</v>
+        <v>24.00303555497617</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>23.39903360517071</v>
+        <v>23.46087065385873</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>23.33117875903249</v>
+        <v>23.39319177725104</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>23.61395303517491</v>
+        <v>23.67564030334437</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.6181</t>
+          <t>X ≈ 0.6194</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>25</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-21.5256107682405</v>
+        <v>-21.48540215220795</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-25.8407609183268</v>
+        <v>-25.79872713988368</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-23.30397384785024</v>
+        <v>-23.26103992205693</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-8.115506908016677</v>
+        <v>-8.076859258370192</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.5266577024658332</v>
+        <v>-0.4613414664112341</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3396564597986256</v>
+        <v>-0.2745176157153679</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.088308443595878</v>
+        <v>-5.020533814323436</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.367680104943389</v>
+        <v>-5.29945941939657</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.328947894845676</v>
+        <v>-5.260798505598096</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-14.06572025470366</v>
+        <v>-13.99839833492221</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.827604801323695</v>
+        <v>-5.760523932724936</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.121461619318055</v>
+        <v>-2.054002038618556</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.244372944929019</v>
+        <v>-3.175568045960908</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.455379004863978</v>
+        <v>-7.383899521426983</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-4.124952805713626</v>
+        <v>-4.053810123077959</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.4596911301917359</v>
+        <v>0.5286890892057485</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.3262279644051205</v>
+        <v>0.395672757384844</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.2215526150027642</v>
+        <v>0.2911603927543354</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.556792492614498</v>
+        <v>-3.487401296108025</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.6242418122756135</v>
+        <v>0.6934626935264561</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>4.078816281377001</v>
+        <v>4.147183797660766</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.005781266510574312</v>
+        <v>0.07570797383240091</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.2806197018406564</v>
+        <v>0.35023400831831</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-3.795321637426895</v>
+        <v>-3.725467289718722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.6908</t>
+          <t>X ≈ 0.6923</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.282372213297919</v>
+        <v>-2.061318434790927</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.267481320273085</v>
+        <v>5.362894350417932</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.26258698292957</v>
+        <v>2.385076327227218</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.552369598198908</v>
+        <v>1.675536608036069</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9685734661096248</v>
+        <v>-1.766018284571302</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.939684924176895</v>
+        <v>-4.687190362854068</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.128909194628505</v>
+        <v>-3.900595513788893</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-9.727946552837494</v>
+        <v>-10.3985681730273</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.78765332289975</v>
+        <v>-2.58478947832684</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.346287172629793</v>
+        <v>4.425776701229836</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.285045037696904</v>
+        <v>-3.082669334405743</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.181120025536728</v>
+        <v>1.309424663332791</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.642061057350709</v>
+        <v>1.74666221901645</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.005071932561236</v>
+        <v>3.08369909743368</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-4.56802261648788</v>
+        <v>-5.362312096666408</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.8075153540551412</v>
+        <v>-1.653495963618298</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.9409590577253582</v>
+        <v>-0.2280350831683222</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.215103217267547</v>
+        <v>-3.452277281478231</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.8303047067390068</v>
+        <v>-0.1169753298221323</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-2.229914841198486</v>
+        <v>-1.491760272133547</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-2.773601688350652</v>
+        <v>-2.033945207574796</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-4.437103488268221</v>
+        <v>-3.671665217697715</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-5.751126329904103</v>
+        <v>-4.960404739932542</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-4.239766081871707</v>
+        <v>-3.475467289719624</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.7636</t>
+          <t>X ≈ 0.7651</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3980855543916988</v>
+        <v>1.396607368644432</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.373592331982849</v>
+        <v>-4.401799138846513</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.233559233983577</v>
+        <v>-0.3633504892017001</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.945187957509354</v>
+        <v>-0.1622338757982789</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.4770133248532815</v>
+        <v>1.326009124826889</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.453203065649802</v>
+        <v>3.338065920429365</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1022626747979345</v>
+        <v>1.660908202106548</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.481104059395541</v>
+        <v>3.210590348325127</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.382267507016792</v>
+        <v>5.077397505856041</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>6.334561036508951</v>
+        <v>7.05079890887221</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>9.402763681069061</v>
+        <v>10.98147454001249</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.127576046136838</v>
+        <v>10.70719574018236</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>10.80338145243778</v>
+        <v>12.3336175777335</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>9.6546488121758</v>
+        <v>11.19857215549011</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>9.933461512020806</v>
+        <v>11.4615659987042</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>5.868345215851598</v>
+        <v>6.568263916303394</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.869869984862149</v>
+        <v>3.691165336249455</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>5.632385155888358</v>
+        <v>5.419526474754164</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>7.716867574172376</v>
+        <v>7.469455721633146</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>5.105310524725397</v>
+        <v>4.909002043237635</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>5.49816785113304</v>
+        <v>5.283266979643834</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>5.424392900022646</v>
+        <v>5.20961649571003</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.766601010252991</v>
+        <v>4.56890768307909</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.756080231732192</v>
+        <v>3.577285003858563</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.8364</t>
+          <t>X ≈ 0.838</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.150845375482866</v>
+        <v>-0.1064716330801403</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.815026422052469</v>
+        <v>0.5708834772056974</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.408063551396367</v>
+        <v>1.154992935873878</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.9790051784785092</v>
+        <v>-0.06626860472862006</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.934957364961704</v>
+        <v>-2.431018687178501</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.4809787912003</v>
+        <v>-3.259627051262285</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.717843067926616</v>
+        <v>-3.531178638029871</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.485403473390626</v>
+        <v>-3.010820852029127</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.105154421658497</v>
+        <v>0.07639445009262147</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.86648302495729</v>
+        <v>1.121272930740801</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.224997972092709</v>
+        <v>5.458193032199773</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.862533178747462</v>
+        <v>0.608440593264433</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.785281876666858</v>
+        <v>1.013208509104039</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.054695195074984</v>
+        <v>0.7927717928730686</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.955952221102102</v>
+        <v>2.171988978877565</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.017055644563271</v>
+        <v>1.748929092891231</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.930359166665397</v>
+        <v>4.161855638074798</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.733089227929149</v>
+        <v>-0.01467767292185584</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.5867155553828169</v>
+        <v>-1.83657127289316</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.1117262324768475</v>
+        <v>-1.141431151257613</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.08136937862028759</v>
+        <v>-0.6643849447735448</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>2.568818646696982</v>
+        <v>1.808904762431588</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.745021323799584</v>
+        <v>-0.9758220346471234</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.743139901034638</v>
+        <v>2.009226587831279</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 0.9091</t>
+          <t>X ≈ 0.9109</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1682562626328803</v>
+        <v>-0.4728445876741816</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.594883096384848</v>
+        <v>1.801834144114387</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.8582273524719923</v>
+        <v>1.273031823000103</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.544525308114004</v>
+        <v>1.919297851539319</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.9469877927141539</v>
+        <v>1.58469746367669</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2009160549086744</v>
+        <v>1.093058068137054</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.197388868509627</v>
+        <v>2.135248801858026</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.219887946707253</v>
+        <v>0.9508006888056997</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.259224202370838</v>
+        <v>0.7656091610774425</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.8887772792202355</v>
+        <v>1.579843314754264</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.995560030619934</v>
+        <v>2.210212453409888</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.35545360583211</v>
+        <v>3.748390787043689</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.702621572670026</v>
+        <v>3.30885791038893</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.548502997879218</v>
+        <v>2.180368308918368</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3.700342971922204</v>
+        <v>4.607643754949372</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>3.126365488259033</v>
+        <v>3.614409234596387</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.461204633769725</v>
+        <v>3.937484618626243</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>4.295902110187967</v>
+        <v>4.517540903479954</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.514079057461835</v>
+        <v>5.190369856006491</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>3.061548150056282</v>
+        <v>3.786531863801315</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.754773864565202</v>
+        <v>3.471843448698472</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.445757746520094</v>
+        <v>2.715210904058246</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.252450687757111</v>
+        <v>2.308248441620989</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.707025780413474</v>
+        <v>1.777949566772406</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.9817</t>
+          <t>X ≈ 0.9837</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.010153770310538</v>
+        <v>1.728176794587576</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4919174580132903</v>
+        <v>-0.5858144056335135</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.355577693857555</v>
+        <v>2.141772531373462</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.8642749127216831</v>
+        <v>0.6400375213028724</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.252077106415364</v>
+        <v>-1.873226339607079</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.6748764369703437</v>
+        <v>-1.091345077234187</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.4707439525894159</v>
+        <v>-1.065751933446109</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.723000000213176</v>
+        <v>-2.135217940143562</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.489361165411808</v>
+        <v>-1.900008236952409</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5072204754751866</v>
+        <v>-0.6856804276836073</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.744264206244779</v>
+        <v>-3.789286977777152</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.766872389793072</v>
+        <v>-1.884200752449416</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.890000838431483</v>
+        <v>-3.006412782942071</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.720492924294817</v>
+        <v>-3.027751705703693</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-2.793924128542905</v>
+        <v>-3.288094302913763</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.2448790629114583</v>
+        <v>-0.1935873489918265</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.160583602946502</v>
+        <v>-1.121359914818242</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.8741305158174697</v>
+        <v>-0.6278649732128301</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.657919367832406</v>
+        <v>-0.6109956271477444</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2746923980375584</v>
+        <v>-0.4246412070478129</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.6677550765580733</v>
+        <v>0.2287114256754421</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.582723760195492</v>
+        <v>-0.643316752307264</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.8958508863937453</v>
+        <v>-0.7672477672197004</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.363949088407288</v>
+        <v>-1.442034155987095</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 1.054</t>
+          <t>X ≈ 1.056</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.545432550048091</v>
+        <v>-3.521388988546448</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4635730919183771</v>
+        <v>-0.2044686868564227</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.39257658434893</v>
+        <v>-2.48347348158169</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.560795149330211</v>
+        <v>0.4576144014328278</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.04880561143132667</v>
+        <v>0.3668095920940999</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3510816087383688</v>
+        <v>-0.42218266605758</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1460945964405411</v>
+        <v>-0.2194000610618687</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.266888251482598</v>
+        <v>2.432221116465783</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.08666384543865</v>
+        <v>1.499580137342086</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.292415742016964</v>
+        <v>1.459502168452467</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8319740044012889</v>
+        <v>1.0005789547265</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.161802942406176</v>
+        <v>-1.233426572483651</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.900874488449958</v>
+        <v>-1.870223215471356</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9983748790652456</v>
+        <v>-1.603534904119485</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.412021222937689</v>
+        <v>-1.527285758244062</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.5720266519721093</v>
+        <v>-0.4398975669640848</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.503752650737496</v>
+        <v>1.280752628338952</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.54322252448155</v>
+        <v>1.318762557127783</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.252824754916873</v>
+        <v>1.781800053537765</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.703904331609252</v>
+        <v>1.48071998926428</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.6689120558086614</v>
+        <v>0.2023046643764417</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.087610610518695</v>
+        <v>0.7603681162318239</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.118058125486861</v>
+        <v>0.7915879782979687</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.781033042376059</v>
+        <v>1.453893889641556</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 1.127</t>
+          <t>X ≈ 1.129</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8382054876150065</v>
+        <v>0.6998986324825651</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.755221833526377</v>
+        <v>2.246394158856532</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.070014965521104</v>
+        <v>2.317437671765511</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2283275516347842</v>
+        <v>0.09864765712460155</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2392722788018773</v>
+        <v>-0.235972621173218</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.931562590482706</v>
+        <v>1.839434389142546</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.66276229646639</v>
+        <v>2.957115312298498</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.3451569214058168</v>
+        <v>-0.347245527744164</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.891280983605526</v>
+        <v>0.8329418671494651</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.117573168722799</v>
+        <v>0.05975153996117655</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.015155108423876</v>
+        <v>-0.4233952785054171</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.48974345566414</v>
+        <v>0.6497088182563573</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7434331193447363</v>
+        <v>-0.4724030202975626</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2309679629715049</v>
+        <v>-0.6937729019414363</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.775093063679527</v>
+        <v>-3.625868119120952</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.558218519142805</v>
+        <v>-3.788769991295311</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.692312213291729</v>
+        <v>-3.543727475583751</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.419959096404668</v>
+        <v>-3.269802530180762</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-4.849887283088762</v>
+        <v>-5.331564794520361</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-6.33583636392612</v>
+        <v>-7.04626824304124</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-7.634644848291813</v>
+        <v>-7.969318321989505</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-6.201889027093841</v>
+        <v>-6.527248481092208</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.143622722400856</v>
+        <v>-2.838909805371138</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-4.49229133439664</v>
+        <v>-5.35284371557514</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 1.2</t>
+          <t>X ≈ 1.203</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.941741101863826</v>
+        <v>2.037925989858167</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-7.355682483576686</v>
+        <v>-6.786299723020242</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.288413261249616</v>
+        <v>1.95995744640642</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5469447364211746</v>
+        <v>0.1179104116508043</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.649284949263802</v>
+        <v>1.488373823070852</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.275903177057231</v>
+        <v>1.109972190242487</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.633266812237586</v>
+        <v>0.9074054540554144</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.165750453519998</v>
+        <v>3.470816568428482</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.953322904810733</v>
+        <v>1.561310345505241</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.109135210481533</v>
+        <v>4.767931266613758</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.455234435830242</v>
+        <v>1.632564009204181</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.069669807326235</v>
+        <v>-0.9204469773095312</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.871060029204358</v>
+        <v>-3.746266566633793</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.843137313873157</v>
+        <v>-1.688120643112498</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-4.18654684632569</v>
+        <v>-4.052094023922621</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-5.288764084849461</v>
+        <v>-5.17071421870186</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-5.422857778998385</v>
+        <v>-5.304631355679334</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-3.837916963160438</v>
+        <v>-3.700264548745011</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.932722172471102</v>
+        <v>-1.776035225751407</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-3.436424552396076</v>
+        <v>-3.302391893585387</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.288040232520821</v>
+        <v>-2.703023046132856</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-4.057839551421281</v>
+        <v>-3.919935623466195</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.352148659740358</v>
+        <v>-4.792492179353424</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-4.428089999008755</v>
+        <v>-4.296895861148194</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 1.272</t>
+          <t>X ≈ 1.276</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.097824679457219</v>
+        <v>1.406373507207483</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>5.495786702173021</v>
+        <v>5.70175399173894</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.335877407454277</v>
+        <v>0.5669614988876575</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.622084094261119</v>
+        <v>0.7820950455455389</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6724328808064968</v>
+        <v>0.4314118228879735</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.134166017366063</v>
+        <v>-3.104004996053447</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.373344719091897</v>
+        <v>4.485508947820584</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.472270282914295</v>
+        <v>0.4681735740049504</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.14909224691413</v>
+        <v>-2.254793626457939</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-7.738645949040112</v>
+        <v>-4.878861160370782</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.825698569857117</v>
+        <v>-0.8943155328317474</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.023378913042123</v>
+        <v>-3.97433953196763</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.518221431154522</v>
+        <v>-1.3996181595165</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.743154006866234</v>
+        <v>-0.692060249544177</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-5.611463978089887</v>
+        <v>-5.098553544820206</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-6.84585473294733</v>
+        <v>-6.347919054906924</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-8.809191019506791</v>
+        <v>-8.34812385859415</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.256486554296892</v>
+        <v>-4.722642752463834</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-4.505098588933144</v>
+        <v>-3.028855688517538</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-3.402629615969346</v>
+        <v>-1.914155959553433</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-3.030806788192997</v>
+        <v>-1.524588597077823</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.192935748512205</v>
+        <v>-1.605366376108371</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.665940802759003</v>
+        <v>4.83634627191492</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.7551370781694331</v>
+        <v>3.825934579439249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 1.345</t>
+          <t>X ≈ 1.349</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.047482200512398</v>
+        <v>-4.532175134422815</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.87355786722047</v>
+        <v>-5.759774454002667</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.676050874895552</v>
+        <v>-3.627392039877456</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-6.178205513243768</v>
+        <v>-7.026997612847929</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-7.479909367162207</v>
+        <v>-9.169502299800556</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.648384334664804</v>
+        <v>-3.999610875639284</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.562924607768956</v>
+        <v>-3.88149243932294</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.01161138528012629</v>
+        <v>-2.358893059984027</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.456783341658266</v>
+        <v>-6.812061903065619</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.433695763444412</v>
+        <v>-4.894534394459392</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4381669859114723</v>
+        <v>-1.925495545972638</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.072752549688182</v>
+        <v>3.184579457808724</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.009332016210585437</v>
+        <v>0.2731523640572391</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.144908253643983</v>
+        <v>-2.645339747437077</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.912147855304752</v>
+        <v>2.09504143952838</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.2798730925015676</v>
+        <v>-0.01054503742676616</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.349126587694073</v>
+        <v>-1.043125815003307</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.383531838706908</v>
+        <v>-2.048052472673966</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.101420883593505</v>
+        <v>-3.630626223548049</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.915524681198242</v>
+        <v>-3.449861763747464</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6601312464167606</v>
+        <v>-0.3888043281097922</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.979097094849671</v>
+        <v>-3.167352992221595</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.710034503765918</v>
+        <v>-2.892878279739591</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.851396403782047</v>
+        <v>-2.968710532962866</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 1.418</t>
+          <t>X ≈ 1.421</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.8675486549960851</v>
+        <v>-2.859982708173234</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>7.055980772190452</v>
+        <v>6.835639380720643</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.661629818705237</v>
+        <v>-0.3500689041878076</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.991842302921512</v>
+        <v>-1.055754892382716</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5.938599769394202</v>
+        <v>8.705295706701847</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.985413505208065</v>
+        <v>3.13192852882581</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.211392749849892</v>
+        <v>2.363941108057702</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9420750907645896</v>
+        <v>2.091995523763877</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6.511942394425375</v>
+        <v>3.571134442797508</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>7.115726082794019</v>
+        <v>5.679004868901075</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>8.7731139481279</v>
+        <v>8.840116473662242</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7.111764232017379</v>
+        <v>5.675098340172454</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.611972271140928</v>
+        <v>3.12591023776352</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.392933816855418</v>
+        <v>4.352602403844784</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>9.270753684189323</v>
+        <v>8.035020012411785</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>5.725978156252218</v>
+        <v>4.288846028207217</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>6.979000771344658</v>
+        <v>5.602306759266654</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>5.487288966173992</v>
+        <v>4.050481361899429</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>7.090140518181194</v>
+        <v>5.713357436369797</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>7.277572233967561</v>
+        <v>5.911673684744628</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>5.347255515728286</v>
+        <v>3.919852154459598</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>5.274015901247814</v>
+        <v>5.29328155536934</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>5.558397479619423</v>
+        <v>5.567756267851394</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>8.260233918128741</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 1.49</t>
+          <t>X ≈ 1.494</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>8.078351735404446</v>
+        <v>7.619747089588778</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.9312733058860516</v>
+        <v>-2.733498408952457</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.845098260723191</v>
+        <v>2.094516156737576</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.090068282499431</v>
+        <v>-3.638235397783191</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.508434307576806</v>
+        <v>2.306473588606764</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-5.770978690958017</v>
+        <v>-3.809811430537337</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.054985619164889</v>
+        <v>-2.067434402036113</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.34593673810047</v>
+        <v>-2.362721975674475</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.072876445935449</v>
+        <v>-4.829345954980333</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.611624362862585</v>
+        <v>-5.583050986020844</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-11.55661012348405</v>
+        <v>-11.61982505301305</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-8.102597727830656</v>
+        <v>-8.115062553523494</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.727999224970148</v>
+        <v>-4.745473287887876</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.458833643149703</v>
+        <v>-2.439740020465486</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.8719682277288</v>
+        <v>-1.834206437150961</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-8.27102126974777</v>
+        <v>-6.291277331261931</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.663581037736392</v>
+        <v>-2.636330297238366</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-7.262741086122979</v>
+        <v>-5.266899909086561</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.305621952477487</v>
+        <v>-1.262685975082299</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.118040201410501</v>
+        <v>-1.077869518337451</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-3.662316521301484</v>
+        <v>-1.620415686303446</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.981325227240809</v>
+        <v>-4.227907217332756</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-4.719380298158477</v>
+        <v>-3.953432504850781</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-4.795321637426973</v>
+        <v>-2.763441973263923</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 1.563</t>
+          <t>X ≈ 1.567</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4.634718452644194</v>
+        <v>7.932249763530216</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.209115777540426</v>
+        <v>0.8238078519370049</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.046664951471293</v>
+        <v>-1.989071588246532</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.151888076064132</v>
+        <v>4.10116979665095</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4.55187211566269</v>
+        <v>3.783155263917934</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6124379540901259</v>
+        <v>1.261831687388444</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.925682002586505</v>
+        <v>-2.244688153008752</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.952149614512862</v>
+        <v>-6.613208371247623</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-7.301930890908956</v>
+        <v>-5.210950574564094</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-9.470216526408855</v>
+        <v>-7.356632259138181</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-6.429026993015022</v>
+        <v>-4.348236300751829</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.329435088318291</v>
+        <v>-3.262216624841365</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.8418351670623</v>
+        <v>2.449662405945595</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.622054797683916</v>
+        <v>2.229383222417006</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-4.556348999007312</v>
+        <v>-3.890235471351154</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.585760689799486</v>
+        <v>-1.928680391295906</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-4.10520920441774</v>
+        <v>-3.428965993467713</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.05571353559226111</v>
+        <v>0.5636993124581977</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.543386383077952</v>
+        <v>0.7779913075466425</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-3.807025661960772</v>
+        <v>-4.511197071658067</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-4.351811447445961</v>
+        <v>-5.053743239624133</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.652300732688083</v>
+        <v>-1.020000159937304</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.386046964825141</v>
+        <v>-2.115388461153884</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.07309941520468044</v>
+        <v>-0.8213577006785258</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 1.637</t>
+          <t>X ≈ 1.639</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9.51640988261564</v>
+        <v>5.854354410755036</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>7.938588031906022</v>
+        <v>5.519380993851193</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.488955847729912</v>
+        <v>0.2832813351453751</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.291083597513399</v>
+        <v>1.522665030377162</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.183774343977653</v>
+        <v>2.476542934991258</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>9.423229412564851</v>
+        <v>6.506285662728835</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8.647807239307419</v>
+        <v>5.753114727124611</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>10.9056219863926</v>
+        <v>9.319406182533285</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7.165588333340096</v>
+        <v>4.244861878406496</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.115900102658621</v>
+        <v>2.18480867256541</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.395371452180747</v>
+        <v>2.461469805381498</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.111165466299056</v>
+        <v>2.180118911279337</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.483533390852287</v>
+        <v>1.06215982573157</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.264732621021224</v>
+        <v>0.8423816946120297</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.6368229022841092</v>
+        <v>-1.085989443521171</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.219067638283704</v>
+        <v>0.7864297909368645</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.084973944134781</v>
+        <v>0.6525126539593913</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.9774159290332065</v>
+        <v>0.5450704594840445</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-5.113283367272345</v>
+        <v>-4.348565918997728</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.64374959873733</v>
+        <v>3.514795200909546</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.8373824785875001</v>
+        <v>1.690197750892239</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.752033004327672</v>
+        <v>-2.231802056670716</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.305936157537765</v>
+        <v>3.170877784016469</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>4.76164038788955</v>
+        <v>5.659148094895762</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 1.709</t>
+          <t>X ≈ 1.712</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.601051253541421</v>
+        <v>-3.592871676855438</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.98680944073493</v>
+        <v>-1.945943108353134</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.314770468338921</v>
+        <v>4.472495336379041</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.160460753350982</v>
+        <v>-4.109709626580532</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-13.28716844687172</v>
+        <v>-12.3654521910948</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.363912895431987</v>
+        <v>-0.2690507432894336</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.2603467673391719</v>
+        <v>2.933946987989088</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.376111094202699</v>
+        <v>4.662643931061631</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4759518773275602</v>
+        <v>2.708084970159568</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.220153623931772</v>
+        <v>-0.06956664470074259</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.88385746275916</v>
+        <v>6.177424282899203</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.536549648205408</v>
+        <v>7.883858777259249</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.387586531146745</v>
+        <v>-1.188728676835943</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.276062306168804</v>
+        <v>2.571422487342211</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>4.52357018598898</v>
+        <v>5.905371475395306</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>5.1438851546826</v>
+        <v>6.499758397338297</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.059273033267523</v>
+        <v>4.376312464549294</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.9994442460265063</v>
+        <v>2.2775980669131</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.170412780104058</v>
+        <v>4.487363141652438</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.5457437507476399</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.091107631685361</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.8007635154563744</v>
+        <v>2.075890251021598</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.856635200119221</v>
+        <v>-1.649635036496356</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.932576539387689</v>
+        <v>-1.725467289719631</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 1.782</t>
+          <t>X ≈ 1.786</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.184738955990426</v>
+        <v>-2.452034732739293</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.9979927409634044</v>
+        <v>-0.325671634716052</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.931284833873995</v>
+        <v>-6.656143642568971</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.68443937063887</v>
+        <v>-4.931819232778011</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.005396557337434</v>
+        <v>-0.3581173093149559</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.163040252665546</v>
+        <v>-0.1901218737693995</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.674771898281918</v>
+        <v>-5.934804505569552</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.559601847444213</v>
+        <v>-6.304638986971852</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.961012008242513</v>
+        <v>-6.236973794585964</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-5.675805583654331</v>
+        <v>-9.431355439208879</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-7.938839478932181</v>
+        <v>-9.144206791811342</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-8.188412464728266</v>
+        <v>-9.383689179552533</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.344541211071558</v>
+        <v>-0.6115632882934605</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.5857912376440879</v>
+        <v>-3.319553159504395</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.1125012249650155</v>
+        <v>-4.030052478027407</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>7.078206009136686</v>
+        <v>1.564334443915619</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4.400323321763523</v>
+        <v>-1.082671698297467</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.291895430606331</v>
+        <v>-1.174423396883071</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.511463068600058</v>
+        <v>-0.9716210211943235</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>7.249184807568625</v>
+        <v>5.694282380396729</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.608072986936499</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>9.19792966158618</v>
+        <v>7.575890251021598</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>5.350364963503651</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.3072424651372</v>
+        <v>2.774532710280376</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 1.855</t>
+          <t>X ≈ 1.859</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.57194625208151</v>
+        <v>12.83283709709431</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.585761615839843</v>
+        <v>5.209171409855614</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-15.11498928731524</v>
+        <v>-10.8592569959005</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-8.237689483099494</v>
+        <v>-4.241216863296479</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-8.653566555572851</v>
+        <v>-4.580073607233281</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8500051814326142</v>
+        <v>-0.7085908173712454</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.597567669761936</v>
+        <v>-5.195518098743911</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.792906024800487</v>
+        <v>-1.77002583979322</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.885029377272545</v>
+        <v>-1.728538657878573</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-10.27544570961016</v>
+        <v>-9.908861741322418</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-6.154932596341034</v>
+        <v>-9.634802099160495</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.51196172248801</v>
+        <v>-2.506144095201194</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-15.25082541061077</v>
+        <v>-11.03671356946461</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-15.47218222164513</v>
+        <v>-11.2577924459112</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-16.23232803558121</v>
+        <v>-11.91593574349181</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-27.12512223697211</v>
+        <v>-22.43265993265993</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-23.46366937241645</v>
+        <v>-22.56657706963745</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-23.54334914478707</v>
+        <v>-22.67141777345859</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-23.35252962557991</v>
+        <v>-18.75182268883056</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-19.31933198380564</v>
+        <v>-18.56497687886247</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-16.04168219037451</v>
+        <v>-11.70011563942116</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-16.21885182091597</v>
+        <v>-11.7759616008302</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-13.56553414431228</v>
+        <v>-11.50148688834815</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-13.64147548358075</v>
+        <v>-11.57731914157148</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 1.927</t>
+          <t>X ≈ 1.931</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>24</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4672573679809915</v>
+        <v>0.4829152628056619</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-3.970392469725972</v>
+        <v>-7.988495198910556</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.282330717814617</v>
+        <v>-1.274039000416728</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.29716539598213</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>10.13860618396819</v>
+        <v>5.977128676229491</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>10.32577079697489</v>
+        <v>6.172159378455873</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.21957133158763</v>
+        <v>1.285963382737577</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.107683352735734</v>
+        <v>5.174418604651109</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.149199417758368</v>
+        <v>5.21590578656587</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.375364006988882</v>
+        <v>4.442990110529323</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.4830566074376108</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.370629370629374</v>
+        <v>0.2716336825766632</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-5.087195181191106</v>
+        <v>-5.018195050946204</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.141885325558789</v>
+        <v>-1.07260726072613</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969632</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>6.993483124209689</v>
+        <v>11.22971922665896</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>6.888499708114409</v>
+        <v>11.12487852283772</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>7.104622871046224</v>
+        <v>7.174103237095359</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>11.45833333333334</v>
+        <v>11.52761571373</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>10.91513292433539</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>10.83917786869284</v>
+        <v>6.742556917688198</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>11.11395303517491</v>
+        <v>7.017031630170251</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>2.774532710280376</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 2</t>
+          <t>X ≈ 2.004</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.662450070550051</v>
+        <v>-0.6270859158836615</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.538477745026633</v>
+        <v>5.016302066530393</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-11.00455294003677</v>
+        <v>-14.8004298537878</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.60723514211886</v>
+        <v>-3.112835782707208</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9725049271429071</v>
+        <v>5.948326832911555</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-6.340895869691678</v>
+        <v>-0.02839745718151931</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.113762001745663</v>
+        <v>-0.7973699505957157</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.836761091708709</v>
+        <v>5.174418604651166</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.795245026686075</v>
+        <v>5.21590578656587</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.569080437455547</v>
+        <v>4.442990110529337</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.29472117034021</v>
+        <v>4.71704975269126</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-13.68492618492618</v>
+        <v>-8.061699650756651</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.96836037436442</v>
+        <v>15.81513828238715</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.191448007774504</v>
+        <v>9.344059405940556</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.9769612131816885</v>
+        <v>2.43591610836004</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>9.280303030303031</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.437927568654146</v>
+        <v>2.896385893325558</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.332944152558866</v>
+        <v>2.791545189504376</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.549067315490682</v>
+        <v>3.007436570428702</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-14.93055555555551</v>
+        <v>-15.55571761960323</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-9.918200408997954</v>
+        <v>-9.848263787569302</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-4.438599909085049</v>
+        <v>-3.674109748978445</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-9.719380298158391</v>
+        <v>-9.649635036496306</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-9.795321637426937</v>
+        <v>-9.725467289719667</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 2.072</t>
+          <t>X ≈ 2.077</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>14.09798743778664</v>
+        <v>12.80152693763777</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.364852739468795</v>
+        <v>5.948461664477719</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.693859758375879</v>
+        <v>-2.059605693732017</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.122923588039818</v>
+        <v>3.745728761635419</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.6147966601586319</v>
+        <v>3.444444845333862</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>15.08767555887975</v>
+        <v>16.8060142060344</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14.31480942682567</v>
+        <v>16.28596338273757</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>21.1791119241643</v>
+        <v>22.67441860465111</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>21.22062798918694</v>
+        <v>22.71590578656587</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>13.30393543556037</v>
+        <v>15.27632344386271</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>13.57829470267571</v>
+        <v>15.55038308602463</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.29920079920075</v>
+        <v>15.27163368257663</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.17470958071366</v>
+        <v>14.14847161572052</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-9.475218658892068</v>
+        <v>-6.072607260726024</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.99129275507233</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-2.396232705450949</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-2.530326399599772</v>
+        <v>0.396385893325558</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-2.635309815695109</v>
+        <v>0.2915451895043759</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-2.419186652763237</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.910714285714292</v>
+        <v>0.6942823803966789</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>4.367513876716338</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.291558821073828</v>
+        <v>0.07589025102159752</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.566333987555858</v>
+        <v>0.3503649635036012</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.490392648287489</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
   </sheetData>
@@ -2774,2457 +2774,2457 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2945</v>
+        <v>2948</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.05269141043807934</v>
+        <v>0.04726336147541588</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02819030770956488</v>
+        <v>-0.03357539426156819</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1703073742092513</v>
+        <v>0.1643819802050928</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.0154672361540733</v>
+        <v>0.009613404100520029</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2632850689868746</v>
+        <v>-0.2735173010321361</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1246796534754608</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1353086302245501</v>
+        <v>0.1244154020873296</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1465609727492492</v>
+        <v>0.1355934864877639</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02919084264068772</v>
+        <v>-0.03991994798326459</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2115155118925571</v>
+        <v>0.2200171375564111</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2011441130758556</v>
+        <v>0.2096148084533809</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.280104835942403</v>
+        <v>0.2885369956259964</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.07986049376162896</v>
+        <v>-0.0708948593104779</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1457232305142071</v>
+        <v>-0.1567015003833845</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1748003044334894</v>
+        <v>-0.1858700892042364</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>4.942651405315246e-05</v>
+        <v>-0.01115213044146657</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.1370502765874235</v>
+        <v>0.1458781072727433</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.1879347363630046</v>
+        <v>0.1967263611941803</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.3904824844745107</v>
+        <v>0.3990354864178656</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.02120081411126762</v>
+        <v>0.03010074705209576</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1285838497852012</v>
+        <v>-0.1396904226082754</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.04846639471524128</v>
+        <v>-0.05970296931738517</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.1108404149145699</v>
+        <v>0.09943244400551521</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.03489907564610206</v>
+        <v>0.04386785274984817</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.07272</t>
+          <t>X &gt; 0.07287</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2945</v>
+        <v>2948</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.05269141043807934</v>
+        <v>0.04726336147541588</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.02819030770956488</v>
+        <v>-0.03357539426156819</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1703073742092513</v>
+        <v>0.1643819802050928</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.0154672361540733</v>
+        <v>0.009613404100520029</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2632850689868746</v>
+        <v>-0.2735173010321361</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1246796534754608</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1353086302245501</v>
+        <v>0.1244154020873296</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1465609727492492</v>
+        <v>0.1355934864877639</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.02919084264068772</v>
+        <v>-0.03991994798326459</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2115155118925571</v>
+        <v>0.2200171375564111</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2011441130758556</v>
+        <v>0.2096148084533809</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.280104835942403</v>
+        <v>0.2885369956259964</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.07986049376162896</v>
+        <v>-0.0708948593104779</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1457232305142071</v>
+        <v>-0.1567015003833845</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1748003044334894</v>
+        <v>-0.1858700892042364</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>4.942651405315246e-05</v>
+        <v>-0.01115213044146657</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.1370502765874235</v>
+        <v>0.1458781072727433</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.1879347363630046</v>
+        <v>0.1967263611941803</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.3904824844745107</v>
+        <v>0.3990354864178656</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.02120081411126762</v>
+        <v>0.03010074705209576</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1285838497852012</v>
+        <v>-0.1396904226082754</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.04846639471524128</v>
+        <v>-0.05970296931738517</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.1108404149145699</v>
+        <v>0.09943244400551521</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.03489907564610206</v>
+        <v>0.04386785274984817</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.1454</t>
+          <t>X &gt; 0.1457</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2945</v>
+        <v>2948</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.05269141043807934</v>
+        <v>0.04726336147541588</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.02819030770956488</v>
+        <v>-0.03357539426156819</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1703073742092513</v>
+        <v>0.1643819802050928</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.0154672361540733</v>
+        <v>0.009613404100520029</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2632850689868746</v>
+        <v>-0.2735173010321361</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1246796534754608</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1353086302245501</v>
+        <v>0.1244154020873296</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1465609727492492</v>
+        <v>0.1355934864877639</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02919084264068772</v>
+        <v>-0.03991994798326459</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2115155118925571</v>
+        <v>0.2200171375564111</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2011441130758556</v>
+        <v>0.2096148084533809</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.280104835942403</v>
+        <v>0.2885369956259964</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.07986049376162896</v>
+        <v>-0.0708948593104779</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1457232305142071</v>
+        <v>-0.1567015003833845</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1748003044334894</v>
+        <v>-0.1858700892042364</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>4.942651405315246e-05</v>
+        <v>-0.01115213044146657</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1370502765874235</v>
+        <v>0.1458781072727433</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.1879347363630046</v>
+        <v>0.1967263611941803</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.3904824844745107</v>
+        <v>0.3990354864178656</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.02120081411126762</v>
+        <v>0.03010074705209576</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1285838497852012</v>
+        <v>-0.1396904226082754</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.04846639471524128</v>
+        <v>-0.05970296931738517</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.1108404149145699</v>
+        <v>0.09943244400551521</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.03489907564610206</v>
+        <v>0.04386785274984817</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.2182</t>
+          <t>X &gt; 0.2186</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2945</v>
+        <v>2948</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.05269141043807934</v>
+        <v>0.04726336147541588</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.02819030770956488</v>
+        <v>-0.03357539426156819</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1703073742092513</v>
+        <v>0.1643819802050928</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0154672361540733</v>
+        <v>0.009613404100520029</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2632850689868746</v>
+        <v>-0.2735173010321361</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1246796534754608</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1353086302245501</v>
+        <v>0.1244154020873296</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1465609727492492</v>
+        <v>0.1355934864877639</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.02919084264068772</v>
+        <v>-0.03991994798326459</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2115155118925571</v>
+        <v>0.2200171375564111</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2011441130758556</v>
+        <v>0.2096148084533809</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.280104835942403</v>
+        <v>0.2885369956259964</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.07986049376162896</v>
+        <v>-0.0708948593104779</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1457232305142071</v>
+        <v>-0.1567015003833845</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.1748003044334894</v>
+        <v>-0.1858700892042364</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>4.942651405315246e-05</v>
+        <v>-0.01115213044146657</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.1370502765874235</v>
+        <v>0.1458781072727433</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.1879347363630046</v>
+        <v>0.1967263611941803</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.3904824844745107</v>
+        <v>0.3990354864178656</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.02120081411126762</v>
+        <v>0.03010074705209576</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1285838497852012</v>
+        <v>-0.1396904226082754</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.04846639471524128</v>
+        <v>-0.05970296931738517</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.1108404149145699</v>
+        <v>0.09943244400551521</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.03489907564610206</v>
+        <v>0.04386785274984817</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.2909</t>
+          <t>X &gt; 0.2915</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2945</v>
+        <v>2948</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.05269141043807934</v>
+        <v>0.04726336147541588</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02819030770956488</v>
+        <v>-0.03357539426156819</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1703073742092513</v>
+        <v>0.1643819802050928</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.0154672361540733</v>
+        <v>0.009613404100520029</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2632850689868746</v>
+        <v>-0.2735173010321361</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1246796534754608</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1353086302245501</v>
+        <v>0.1244154020873296</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1465609727492492</v>
+        <v>0.1355934864877639</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.02919084264068772</v>
+        <v>-0.03991994798326459</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2115155118925571</v>
+        <v>0.2200171375564111</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2011441130758556</v>
+        <v>0.2096148084533809</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.280104835942403</v>
+        <v>0.2885369956259964</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.07986049376162896</v>
+        <v>-0.0708948593104779</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1457232305142071</v>
+        <v>-0.1567015003833845</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.1748003044334894</v>
+        <v>-0.1858700892042364</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>4.942651405315246e-05</v>
+        <v>-0.01115213044146657</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.1370502765874235</v>
+        <v>0.1458781072727433</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.1879347363630046</v>
+        <v>0.1967263611941803</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.3904824844745107</v>
+        <v>0.3990354864178656</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.02120081411126762</v>
+        <v>0.03010074705209576</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.1285838497852012</v>
+        <v>-0.1396904226082754</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.04846639471524128</v>
+        <v>-0.05970296931738517</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.1108404149145699</v>
+        <v>0.09943244400551521</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.03489907564610206</v>
+        <v>0.04386785274984817</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.3636</t>
+          <t>X &gt; 0.3644</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2945</v>
+        <v>2948</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.05269141043807934</v>
+        <v>0.04726336147541588</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.02819030770956488</v>
+        <v>-0.03357539426156819</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1703073742092513</v>
+        <v>0.1643819802050928</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.0154672361540733</v>
+        <v>0.009613404100520029</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2632850689868746</v>
+        <v>-0.2735173010321361</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1246796534754608</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1353086302245501</v>
+        <v>0.1244154020873296</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1465609727492492</v>
+        <v>0.1355934864877639</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.02919084264068772</v>
+        <v>-0.03991994798326459</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2115155118925571</v>
+        <v>0.2200171375564111</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2011441130758556</v>
+        <v>0.2096148084533809</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.280104835942403</v>
+        <v>0.2885369956259964</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.07986049376162896</v>
+        <v>-0.0708948593104779</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1457232305142071</v>
+        <v>-0.1567015003833845</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1748003044334894</v>
+        <v>-0.1858700892042364</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>4.942651405315246e-05</v>
+        <v>-0.01115213044146657</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.1370502765874235</v>
+        <v>0.1458781072727433</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.1879347363630046</v>
+        <v>0.1967263611941803</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.3904824844745107</v>
+        <v>0.3990354864178656</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.02120081411126762</v>
+        <v>0.03010074705209576</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.1285838497852012</v>
+        <v>-0.1396904226082754</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.04846639471524128</v>
+        <v>-0.05970296931738517</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.1108404149145699</v>
+        <v>0.09943244400551521</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.03489907564610206</v>
+        <v>0.04386785274984817</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.4363</t>
+          <t>X &gt; 0.4372</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2943</v>
+        <v>2946</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.02145739951413361</v>
+        <v>0.01604537055859367</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.05926315942280524</v>
+        <v>-0.06463267779661663</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1403305452722066</v>
+        <v>0.1344177474502999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.01414204902577154</v>
+        <v>-0.01998429469546181</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2928458831715943</v>
+        <v>-0.30308944402789</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1542832936267686</v>
+        <v>-0.1646852775089158</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1402116201683938</v>
+        <v>0.1292595664592895</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1516617018561632</v>
+        <v>0.1406348208673833</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.02423543841760534</v>
+        <v>-0.03502358146387508</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2171575772089085</v>
+        <v>0.2256135047146444</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1727429084983214</v>
+        <v>0.1812026103172784</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2519365159053706</v>
+        <v>0.2603571828021742</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1075203844431414</v>
+        <v>-0.09856730136915814</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.173287110264539</v>
+        <v>-0.1842823876296151</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2019465080989207</v>
+        <v>-0.213034467130818</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.02739096733144208</v>
+        <v>-0.0386099395581283</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.1097937379770784</v>
+        <v>0.1186081155477794</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1607746968073229</v>
+        <v>0.1695526446043445</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.3633040157131333</v>
+        <v>0.3718433500897191</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.006364562118122308</v>
+        <v>0.002522461780252172</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.1558914106957516</v>
+        <v>-0.1670159069318018</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.07567720377099363</v>
+        <v>-0.08693200135288492</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.08354189008485946</v>
+        <v>0.07211589665601537</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.00760055081639166</v>
+        <v>0.01655579242565608</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.5091</t>
+          <t>X &gt; 0.5101</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2939</v>
+        <v>2942</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.007342088413849979</v>
+        <v>-0.0127674644275757</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.08772829294414208</v>
+        <v>-0.09311209544147658</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1140732952617256</v>
+        <v>0.1081402205448825</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.03965132013720307</v>
+        <v>-0.04551589917442556</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2844056603634471</v>
+        <v>-0.2947632554388093</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1120536218920876</v>
+        <v>-0.1226153167392212</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1839013914137979</v>
+        <v>0.1727856124749252</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1618838947411518</v>
+        <v>0.1507379551247823</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.04819129725349569</v>
+        <v>-0.05905191224969286</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.194577832810694</v>
+        <v>0.2029765695679728</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.149723274104268</v>
+        <v>0.1581266236699719</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.229395053911837</v>
+        <v>0.2377583438232591</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1290314543706685</v>
+        <v>-0.1201378951797381</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1945942951323687</v>
+        <v>-0.2056694995151815</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.2563494905974508</v>
+        <v>-0.2674737221484307</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.08238356647442657</v>
+        <v>-0.09363728844908792</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.05516959845984104</v>
+        <v>0.0639571280609772</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.1063439110129707</v>
+        <v>0.115094561747334</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.3088362587458633</v>
+        <v>0.3173483151673295</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.06160774983005268</v>
+        <v>-0.05274648208204269</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2106179540506616</v>
+        <v>-0.2217782188086872</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1302098864092684</v>
+        <v>-0.1415010533262304</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.02883337996337332</v>
+        <v>0.01737141950093246</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.04710795930509448</v>
+        <v>-0.03817973023627275</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.5818</t>
+          <t>X &gt; 0.583</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2933</v>
+        <v>2936</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.06783592577646402</v>
+        <v>0.06223032992278377</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.04588228624877644</v>
+        <v>-0.05140199026622128</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1253841810897356</v>
+        <v>0.1193519630450979</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.02719747733542732</v>
+        <v>-0.03316434653852696</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2717023952111859</v>
+        <v>-0.2822316790134209</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.09937619533617692</v>
+        <v>-0.1101096135888753</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1987592062624444</v>
+        <v>0.1874656983368084</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1433249005972357</v>
+        <v>0.132045723295235</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.03331331568815443</v>
+        <v>-0.04435192791361686</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2115269951043857</v>
+        <v>0.2197879395660109</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1660276219303611</v>
+        <v>0.1742944082732549</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1784785041665771</v>
+        <v>0.1867728543349614</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1784029763417934</v>
+        <v>-0.1695815817893802</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2436647656585365</v>
+        <v>-0.2548370286943751</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.304217925140307</v>
+        <v>-0.3154425872921323</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1311279565081165</v>
+        <v>-0.1424798443147068</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.04100495703264784</v>
+        <v>0.04968297014404754</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.05845659488547028</v>
+        <v>0.06713172469649464</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2609047913731004</v>
+        <v>0.269341332333461</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1106948228882771</v>
+        <v>-0.1019067995964633</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2589159115533235</v>
+        <v>-0.270176002608423</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.1782045443951645</v>
+        <v>-0.1895964746421157</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.01941439294193259</v>
+        <v>-0.03097654143335404</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.06126094871227394</v>
+        <v>-0.05244276655885471</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.6545</t>
+          <t>X &gt; 0.6558</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2908</v>
+        <v>2911</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2534742226645079</v>
+        <v>0.2472838551901404</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1758756112071964</v>
+        <v>0.1697189746051109</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.326805759742939</v>
+        <v>0.3201454350916677</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.04233750745378728</v>
+        <v>0.03591582274892602</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2695105510979232</v>
+        <v>-0.2806934637317511</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.09731051218226838</v>
+        <v>-0.1086976589158581</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2442119886718146</v>
+        <v>0.232192592124683</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1907028666008515</v>
+        <v>0.1786921089246718</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.01221311638850864</v>
+        <v>0.0004475102320853352</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3342681165779737</v>
+        <v>0.3418953448776563</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2175547232306911</v>
+        <v>0.2252633050526995</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1982510292996977</v>
+        <v>0.206016884676373</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1520449126503607</v>
+        <v>-0.1437658272018538</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.181665846820799</v>
+        <v>-0.1936118269361131</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.2713711672261638</v>
+        <v>-0.2833370605334125</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.1362072127555436</v>
+        <v>-0.1482439196627041</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03855290229251551</v>
+        <v>0.04671157039103235</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.05705446266299674</v>
+        <v>0.06520774094470738</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2937254351487937</v>
+        <v>0.3016046664835912</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.1170130539333556</v>
+        <v>-0.1087375235154227</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.2962072818501866</v>
+        <v>-0.3081127923736986</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1797862656030986</v>
+        <v>-0.1918749395036343</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.02199377821344939</v>
+        <v>-0.03425042111173582</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.02915932656032538</v>
+        <v>-0.02089841304494655</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.7272</t>
+          <t>X &gt; 0.7287</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2845</v>
+        <v>2847</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2874841788914395</v>
+        <v>0.2991807805708149</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.04098240921381802</v>
+        <v>0.05297741364549324</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2617954901257917</v>
+        <v>0.2737261948048086</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.01324492548713607</v>
+        <v>-0.0009425299937362297</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2540304232786781</v>
+        <v>-0.2473036539201061</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.01222454102034476</v>
+        <v>-0.005774043512957405</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3189067635568463</v>
+        <v>0.3250968558333085</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4103425549750597</v>
+        <v>0.4164668395340669</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.05206956126554729</v>
+        <v>0.05856312922321649</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2232814028587384</v>
+        <v>0.2500904952792879</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2729725738241697</v>
+        <v>0.2996249801230704</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1543421552178117</v>
+        <v>0.1812124948505911</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.2139179095256054</v>
+        <v>-0.186262277836903</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2743774391234624</v>
+        <v>-0.2672851318745302</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1762256342548127</v>
+        <v>-0.1691627007467886</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.1213416897671848</v>
+        <v>-0.114406149795073</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.06024332530872556</v>
+        <v>0.0528878211208621</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.1516576028512659</v>
+        <v>0.1442801123655286</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3186160850394515</v>
+        <v>0.3110142624665784</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.0702247191011196</v>
+        <v>-0.07764744416467551</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2413475814601895</v>
+        <v>-0.2693164191482467</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.08551175416972967</v>
+        <v>-0.1136499385185843</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.1048727774127443</v>
+        <v>0.07648855900927032</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.06408082303004647</v>
+        <v>0.05675961579495237</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.8</t>
+          <t>X &gt; 0.8016</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2738</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3142759836618154</v>
+        <v>0.2554921399206975</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2525819334315074</v>
+        <v>0.2303224261442551</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.320233384749514</v>
+        <v>0.2990882687846153</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.06225467437640475</v>
+        <v>0.005478491442602262</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2825993352765366</v>
+        <v>-0.3099373620586903</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.147652135583435</v>
+        <v>-0.1388925811571156</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3353659052310434</v>
+        <v>0.2719180988048961</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3684976020996018</v>
+        <v>0.3052325581395365</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.07807330951435887</v>
+        <v>-0.1412370705769916</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.01554508392015208</v>
+        <v>-0.02064625310698176</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.08381619479351343</v>
+        <v>-0.1256203091493688</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1963284168524311</v>
+        <v>-0.2378277439153536</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6444697837878692</v>
+        <v>-0.6846797008672709</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6624000135898669</v>
+        <v>-0.7237418317732676</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.571308367874785</v>
+        <v>-0.632182944808207</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.3554163789202889</v>
+        <v>-0.3804437820831268</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.0886354375006988</v>
+        <v>-0.09195229909426672</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.06252714812571014</v>
+        <v>-0.06572786919048923</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.02949522699079665</v>
+        <v>0.02603613279194406</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2724826705581904</v>
+        <v>-0.2761663609385465</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4656456644724116</v>
+        <v>-0.4903652104076883</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3008367351772563</v>
+        <v>-0.3255696029929993</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.077305791219068</v>
+        <v>-0.1023550072886081</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.08020111149556186</v>
+        <v>-0.0833927827802583</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.8727</t>
+          <t>X &gt; 0.8745</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2501269347412034</v>
+        <v>0.2834012270600326</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2094530796048844</v>
+        <v>0.2040635882182116</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2368173869138204</v>
+        <v>0.2330940458304482</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.008042749257064941</v>
+        <v>0.01101052560844096</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1558947282027674</v>
+        <v>-0.1463921458024018</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.03126988480401849</v>
+        <v>0.1017305329815983</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.492808197706772</v>
+        <v>0.5651545112437759</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5106567486668823</v>
+        <v>0.5609156692304254</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1688044961359552</v>
+        <v>-0.1580174710692148</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1598610419347395</v>
+        <v>-0.1086935229866768</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5675829122700407</v>
+        <v>-0.5561582379079937</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3542041585519868</v>
+        <v>-0.3030789611015194</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.9074668635317451</v>
+        <v>-0.8155947634771792</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8707498231414377</v>
+        <v>-0.8406720719112286</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.9184636234196191</v>
+        <v>-0.8483976171301535</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.6140211939337732</v>
+        <v>-0.5446283153226972</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.4734973910250417</v>
+        <v>-0.4199406372866861</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1235358753497309</v>
+        <v>-0.06966407629853677</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.0767469385766546</v>
+        <v>0.1696518100202198</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.3019442262372394</v>
+        <v>-0.2094504290335308</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5075913716698537</v>
+        <v>-0.4769474810860004</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.5208850243889955</v>
+        <v>-0.4901474848274603</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.02610463948757058</v>
+        <v>-0.03500664483295424</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.2200168792672486</v>
+        <v>-0.2447434502231616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.9454</t>
+          <t>X &gt; 0.9473</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2117</v>
+        <v>2103</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3343174128145989</v>
+        <v>0.4412670913816257</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.06933444384728205</v>
+        <v>-0.1294700656279346</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1117722072597047</v>
+        <v>0.01600765297382623</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3204631519212526</v>
+        <v>-0.3873433194146969</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3778257409144317</v>
+        <v>-0.5077560728405928</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.00286770067759079</v>
+        <v>-0.1052085007479562</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3510267306486625</v>
+        <v>0.2373982613247776</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5691676176488443</v>
+        <v>0.4795274031374461</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2549359205874921</v>
+        <v>-0.3508239815363581</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3708765945148187</v>
+        <v>-0.4611745842174244</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.08335943266264</v>
+        <v>-1.133636475420388</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.100691738914584</v>
+        <v>-1.148820862877912</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.633918291884108</v>
+        <v>-1.676571807617556</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.357571600068596</v>
+        <v>-1.471312455736324</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.847897543880464</v>
+        <v>-1.987343010540954</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.366692297672152</v>
+        <v>-1.412824931782268</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.26527021226385</v>
+        <v>-1.329550569453012</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.012851218684197</v>
+        <v>-1.027240389243254</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.8161692081616891</v>
+        <v>-0.8784200978199976</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.9787735849056531</v>
+        <v>-1.043609357495015</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.164071102721408</v>
+        <v>-1.301255240560749</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.117857069928576</v>
+        <v>-1.159264143277689</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.4846141196038829</v>
+        <v>-0.524159751325243</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.6077921145171246</v>
+        <v>-0.6669794152545734</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 1.018</t>
+          <t>X &gt; 1.02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1198329434163838</v>
+        <v>0.03880656622171585</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.06477715367895343</v>
+        <v>0.01324436280077634</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.600325364715971</v>
+        <v>-0.648791475664261</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6964534524613271</v>
+        <v>-0.7086403239087673</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1003719783721309</v>
+        <v>-0.08072698192298589</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2104020289486144</v>
+        <v>0.2031900166175902</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.6118251428772865</v>
+        <v>0.644937741711928</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.296613470237283</v>
+        <v>1.297247388770273</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.1368231801346056</v>
+        <v>0.1336587350450742</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3276062900407695</v>
+        <v>-0.390963955268262</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2388905872818654</v>
+        <v>-0.303124052398708</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8892716194696391</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.23528599646459</v>
+        <v>-1.260685210465518</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.9250327852861702</v>
+        <v>-0.9845608550910967</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.547665087018082</v>
+        <v>-1.58055374869403</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.722712677092161</v>
+        <v>-1.794122078460177</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.29849371615424</v>
+        <v>-1.394658882793841</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.056875835026482</v>
+        <v>-1.152138693507453</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.8663916217073862</v>
+        <v>-0.9620528442661893</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.202221876942197</v>
+        <v>-1.237181794058095</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.745422285940151</v>
+        <v>-1.779727962024126</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.287687802949023</v>
+        <v>-1.32061847715795</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.3541033846550192</v>
+        <v>-0.4481378437327876</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.3678169703453804</v>
+        <v>-0.4245933821041419</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 1.091</t>
+          <t>X &gt; 1.093</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.358881894579234</v>
+        <v>1.251358525042335</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2433868120574019</v>
+        <v>0.0873943303409348</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.005548070064193666</v>
+        <v>-0.02392488452753128</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.12146838362483</v>
+        <v>-1.105850092288705</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1178040724420555</v>
+        <v>-0.2331515724041111</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4002124843199013</v>
+        <v>0.4161830558216053</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8680411413477671</v>
+        <v>0.9393189013177263</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9686105050536113</v>
+        <v>0.9106914831869446</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1842719989773443</v>
+        <v>-0.3315546630594355</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.8752573683217406</v>
+        <v>-1.021206392384862</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6008981012064041</v>
+        <v>-0.7471467502229387</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7971419632562871</v>
+        <v>-0.8116996507566938</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.010282726068212</v>
+        <v>-1.053085237212478</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9002393714024777</v>
+        <v>-0.7737470994805946</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.593519715508201</v>
+        <v>-1.598696068453975</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.111703956191867</v>
+        <v>-2.25535168195718</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.245797650340791</v>
+        <v>-2.305865983238242</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.935843307099958</v>
+        <v>-1.993692508577361</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.9208477823314</v>
+        <v>-1.896570107367623</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.184642560266006</v>
+        <v>-2.162860476746133</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.561591930194957</v>
+        <v>-2.454780078296118</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.090661288267846</v>
+        <v>-2.029372906873135</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.8517699734290431</v>
+        <v>-0.8703708224495301</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.09423920611966</v>
+        <v>-1.064379423610838</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 1.164</t>
+          <t>X &gt; 1.166</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.505582611162524</v>
+        <v>1.406974353093005</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4643233754215856</v>
+        <v>-0.5218513294225886</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.576116028549059</v>
+        <v>-0.6846312711209563</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.501773748521877</v>
+        <v>-1.445745916425729</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2184104296761973</v>
+        <v>-0.2323555039209992</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.0312458166694114</v>
+        <v>0.01455741133297295</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3623779770453908</v>
+        <v>0.3699192703220646</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.144268718589387</v>
+        <v>1.265667270606343</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.7690596055961976</v>
+        <v>-0.6601625895025052</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.436737903839088</v>
+        <v>-1.326240658701394</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.056221524197213</v>
+        <v>-0.8385058028642547</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.441472540198653</v>
+        <v>-1.224092813149859</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.504392633420402</v>
+        <v>-1.216947279110137</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.088806769295523</v>
+        <v>-0.7963149256102042</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.260611109406575</v>
+        <v>-1.026650736559752</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.985898358946343</v>
+        <v>-1.822638146167563</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.119992053095267</v>
+        <v>-1.956555283145036</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.799443554296928</v>
+        <v>-1.6335885003352</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.095590121499022</v>
+        <v>-0.9272529370659441</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.015042598509055</v>
+        <v>-0.7848172980598562</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.132257916985175</v>
+        <v>-0.8986389215457251</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.9323217759412046</v>
+        <v>-0.7601226107147383</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.4877901167283412</v>
+        <v>-0.3148710879984904</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.1368371123468535</v>
+        <v>0.1457773454735118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 1.236</t>
+          <t>X &gt; 1.239</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.404003594249204</v>
+        <v>1.261113670881763</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.14063789055664</v>
+        <v>0.9263368725319481</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.010355086831126</v>
+        <v>-1.295995901989244</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.724148400024283</v>
+        <v>-1.807225252506825</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6533868534556433</v>
+        <v>-0.6301462994607192</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3356739375768001</v>
+        <v>-0.2386758598812548</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.06639465621773866</v>
+        <v>0.2456655290363017</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4405815250594856</v>
+        <v>0.7558903523515639</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.403088163940978</v>
+        <v>-1.173713135904563</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.961237300200601</v>
+        <v>-2.735065080009392</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.64112639909834</v>
+        <v>-1.409757080423013</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.528063439828145</v>
+        <v>-1.294288349836847</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.9532082530865225</v>
+        <v>-0.6322301386654416</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.9131271556241458</v>
+        <v>-0.5901511203751895</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.5791760759398912</v>
+        <v>-0.3272417863768027</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.216678314887339</v>
+        <v>-1.048644338118017</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.350772009036262</v>
+        <v>-1.18256147509549</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.324693826180038</v>
+        <v>-1.155823231548254</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.9006264727857882</v>
+        <v>-0.7310351028255795</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.4511154855643014</v>
+        <v>-0.2028152449330847</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.8630822987617393</v>
+        <v>-0.48150917015505</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.2044051361254517</v>
+        <v>-0.02965064607602841</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.4121986492099907</v>
+        <v>0.7202460731469813</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.8625730994152079</v>
+        <v>1.17281540512846</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 1.309</t>
+          <t>X &gt; 1.312</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.120399142194408</v>
+        <v>1.237201667055842</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4114347869219515</v>
+        <v>0.1402297467548053</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.403195857763706</v>
+        <v>-1.602667351056674</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.116989170956863</v>
+        <v>-2.233467209263146</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6501978872786154</v>
+        <v>-0.8048950980627296</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3003255043541273</v>
+        <v>0.2330013979194092</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3198688719747125</v>
+        <v>-0.4522779260558849</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.928294039758633</v>
+        <v>0.8032529604793837</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.7758770348410167</v>
+        <v>-0.9957506551519231</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.161333240717489</v>
+        <v>-2.382163263703745</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.275353178495109</v>
+        <v>-1.49460668902649</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.9428262868629744</v>
+        <v>-0.8531106937014741</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6911707163593022</v>
+        <v>-0.5059062644638033</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6067171298401419</v>
+        <v>-0.5733753098812144</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.2634036188901447</v>
+        <v>0.4581895338592687</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.2741587610186187</v>
+        <v>-0.1763021924312298</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.1019737415381314</v>
+        <v>-0.002999667350323421</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.6663752280775199</v>
+        <v>-0.5686698642590642</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.2971127083310066</v>
+        <v>-0.3527784833347383</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.04307044410413141</v>
+        <v>0.07889776501210832</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.5001299648938229</v>
+        <v>-0.3098022491077614</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.1285439218625015</v>
+        <v>0.2297364048677579</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.03484397219487079</v>
+        <v>0.04267265581133728</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.8805616191015133</v>
+        <v>0.7360711718188426</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 1.382</t>
+          <t>X &gt; 1.385</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.530258156292994</v>
+        <v>2.425329357156272</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.647637386174218</v>
+        <v>1.3552584411594</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.152836506967546</v>
+        <v>-1.185701784342186</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.318183750690871</v>
+        <v>-1.246302320955323</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.6931460986543669</v>
+        <v>0.9176863479352235</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.8803107116611528</v>
+        <v>1.104652534032603</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.07537077688282068</v>
+        <v>0.2539239495890868</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.108597429518184</v>
+        <v>1.454455573227875</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3415071100660541</v>
+        <v>0.2020425702996889</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.714379582754653</v>
+        <v>-1.864773290579677</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.440020315639316</v>
+        <v>-1.405870764868766</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.535964035964035</v>
+        <v>-1.684620168316762</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.8289534229493398</v>
+        <v>-0.6663431990942996</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.5008596845331468</v>
+        <v>-0.1466813348001494</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.06088982466935278</v>
+        <v>0.1211012935452231</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.2730348024364844</v>
+        <v>-0.2104377104377164</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.1433302190109274</v>
+        <v>0.2112007081403675</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.3286256741485758</v>
+        <v>-0.2640103660511812</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.2544699658474627</v>
+        <v>0.3222513852435114</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.625</v>
+        <v>0.8055996345711307</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.4686591245942822</v>
+        <v>-0.2935328042668957</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.739789489487876</v>
+        <v>0.9293225330253065</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.5747373489003849</v>
+        <v>0.6472109746353709</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.41791365669075</v>
+        <v>1.499022506198742</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 1.454</t>
+          <t>X &gt; 1.457</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.048567669879453</v>
+        <v>3.201258149725923</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.8226358527141286</v>
+        <v>0.5506918776919107</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9226815950075675</v>
+        <v>-1.30837980291804</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.215422276621787</v>
+        <v>-1.274276305150032</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1070078511195121</v>
+        <v>-0.2256009834581718</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.7117357092556844</v>
+        <v>0.8070311645842381</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.271656738587815</v>
+        <v>-0.05584452686694164</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.133999142209419</v>
+        <v>1.36085928261727</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5997457299209614</v>
+        <v>-0.2925687897053137</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.061344853770549</v>
+        <v>-2.972264126758759</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.997956050790243</v>
+        <v>-2.910068891376497</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.855109025995098</v>
+        <v>-2.765089481265171</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.658925138997013</v>
+        <v>-1.223078278122365</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.247370557626304</v>
+        <v>-0.8072144794097227</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.484360868393559</v>
+        <v>-1.040729326884126</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.18813847410086</v>
+        <v>-0.8709708550472897</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.8993991872772682</v>
+        <v>-0.5802595419186076</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.215799093858806</v>
+        <v>-0.8974144707928673</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.7882594404407328</v>
+        <v>-0.4692088648154638</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.3897991543340353</v>
+        <v>0.05598450805630506</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.355832544304512</v>
+        <v>-0.9120935748033432</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.04812783345668947</v>
+        <v>0.2886562084684101</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.1854819930736937</v>
+        <v>-0.0751669513899671</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>0.3741698879968212</v>
+        <v>0.7000646251739937</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 1.527</t>
+          <t>X &gt; 1.53</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.022081125894772</v>
+        <v>2.308519975175628</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.180576497326399</v>
+        <v>1.21424950593974</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.89569789209547</v>
+        <v>-1.995921441825438</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8328414590957394</v>
+        <v>-0.7966477416768356</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.4366899243228346</v>
+        <v>-0.7371966131081251</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.034738648074814</v>
+        <v>1.73984590886711</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.5004511962238354</v>
+        <v>0.3505892330777201</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.252353403497153</v>
+        <v>2.113194114855247</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.5172197223268924</v>
+        <v>0.6240690518719916</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.5408796478334</v>
+        <v>-2.444764991511434</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.25129195432212</v>
+        <v>-1.150297186084209</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.784192964396006</v>
+        <v>-1.684148630348524</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.6244202234922867</v>
+        <v>-0.5113923298577063</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5919699279276571</v>
+        <v>-0.4773691654879713</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.997094060365967</v>
+        <v>-0.8804104222522042</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.2573478107250295</v>
+        <v>0.224180581323445</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.1311988096325436</v>
+        <v>-0.1648385964703607</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.01827070048082646</v>
+        <v>-0.01457725947521027</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.274511989004651</v>
+        <v>-0.3088899601835422</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.1669847328244245</v>
+        <v>0.2850752192714125</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.8851215285908367</v>
+        <v>-0.7689799001012787</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.074546825435775</v>
+        <v>1.201209944116222</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.7398033753109488</v>
+        <v>0.7084212294883017</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.429168158491464</v>
+        <v>1.399852403375</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 1.6</t>
+          <t>X &gt; 1.603</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.434237727376143</v>
+        <v>1.017537979735735</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.718257259171438</v>
+        <v>1.303879193808285</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.411730303735915</v>
+        <v>-1.997493892489793</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.504405604506715</v>
+        <v>-1.920989503620007</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.559116383319584</v>
+        <v>-1.774887452802787</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.354756304221368</v>
+        <v>1.849578733294599</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.271331165956155</v>
+        <v>0.9463604569277564</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.098366582549403</v>
+        <v>4.116424874243641</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.27652861030495</v>
+        <v>1.963554689387188</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.9817788501539226</v>
+        <v>-1.317197977244916</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.08630157061622157</v>
+        <v>-0.416179087434088</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9865134865134877</v>
+        <v>-1.32188773853099</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.179327686367081</v>
+        <v>-1.191131310089297</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.090125491190264</v>
+        <v>-1.098730562711438</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.1962616991716644</v>
+        <v>-0.189475741169737</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.8970472233430442</v>
+        <v>0.7183908045977034</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.762953529194121</v>
+        <v>0.5844736676202302</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.03491715359727721</v>
+        <v>-0.147326283849857</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.6835391227232392</v>
+        <v>-0.5583941505744363</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.061137071651089</v>
+        <v>1.386106279767795</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.1051162968484292</v>
+        <v>0.2146292941917025</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.688087526013639</v>
+        <v>1.71111037680776</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.218119701841566</v>
+        <v>1.356654271679751</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.767178362573098</v>
+        <v>1.909752836066538</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 1.673</t>
+          <t>X &gt; 1.676</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.215105012308172</v>
+        <v>-0.5544273603455423</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3207723302311862</v>
+        <v>-0.06615889120565299</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.362577631394835</v>
+        <v>-2.738745841471207</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.076370944587993</v>
+        <v>-3.040177227169089</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.44164072961204</v>
+        <v>-3.156602328835845</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.03770495335358959</v>
+        <v>0.3361489812284759</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.146683812445296</v>
+        <v>-0.6158346808862163</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.866942611994986</v>
+        <v>2.425455949049507</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.6738907757830646</v>
+        <v>1.222129852955916</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.980603071200356</v>
+        <v>-2.455350138433275</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.883198536595316</v>
+        <v>-1.351414977599156</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.985337707559921</v>
+        <v>-2.460039899719348</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.052215757322799</v>
+        <v>-1.923450929231073</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.862049934612287</v>
+        <v>-1.729592046341565</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.0518453711804483</v>
+        <v>0.101891212094479</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.7914886640886465</v>
+        <v>0.6962781340374704</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.6573949699397232</v>
+        <v>0.5623609970599972</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.2740347271472885</v>
+        <v>-0.3723552254333811</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.7685347167762586</v>
+        <v>0.6734116741631411</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.5423553719008254</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.4140681775929949</v>
+        <v>-0.2649304542359658</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.815761890731338</v>
+        <v>2.992556917688262</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.8615325649121033</v>
+        <v>0.7670316301703153</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.7855912256436355</v>
+        <v>0.6911993769470399</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 1.745</t>
+          <t>X &gt; 1.749</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>190</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3062457580824045</v>
+        <v>0.2451632492623332</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.3948481573250859</v>
+        <v>0.4285211659384274</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-3.88649738448126</v>
+        <v>-4.63644088827391</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.516957364341081</v>
+        <v>-2.758721332587122</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7988938160318</v>
+        <v>-0.7332207861361226</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.9507707969749859</v>
+        <v>0.495412066627928</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.384595335079041</v>
+        <v>-1.549987751642874</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.461850019402398</v>
+        <v>1.836722269572633</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.9825327510917035</v>
+        <v>0.83108903263917</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.916302659677726</v>
+        <v>-3.083187899941827</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.162776725895725</v>
+        <v>-3.332688467203987</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-5.004370629370626</v>
+        <v>-5.18211849892424</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.962195181191106</v>
+        <v>-2.116798890387685</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.704385325558789</v>
+        <v>-2.861437976258351</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.279983231262761</v>
+        <v>-1.425340436142584</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.376786183386578</v>
+        <v>-0.8309535141995923</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.01268033188857487</v>
+        <v>-0.4413104417529752</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.6158632936307811</v>
+        <v>-1.069711354998248</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.1238200787251102</v>
+        <v>-0.3302597646498313</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.8344240837696333</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.2323365346524113</v>
+        <v>-0.3745795770429865</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.356629875673569</v>
+        <v>3.2337849878637</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.859567070262621</v>
+        <v>1.402996542451021</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>1.783625730994153</v>
+        <v>1.327164289227746</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 1.818</t>
+          <t>X &gt; 1.822</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.07935016392072924</v>
+        <v>0.9644160444627659</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.2390690926767718</v>
+        <v>0.6296392461129514</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-4.133207910797047</v>
+        <v>-4.09785348712856</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.215422276621787</v>
+        <v>-2.179228559202883</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.264902587961615</v>
+        <v>-0.8332483799551085</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.895946235571472</v>
+        <v>0.6782211174005539</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5348146333246575</v>
+        <v>-0.380703283929094</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.791893879051521</v>
+        <v>4.007751937984494</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.51762047038995</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.203583361432109</v>
+        <v>-1.390343222803956</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.929224094316773</v>
+        <v>-1.78295024730869</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.182002208317996</v>
+        <v>-4.061699650756694</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.332809216278818</v>
+        <v>-2.518195050946147</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.554166027313173</v>
+        <v>-2.739273927392738</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-1.581518318982056</v>
+        <v>-0.7307505583066245</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-2.302247743044894</v>
+        <v>-1.469696969696976</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-1.120551963509598</v>
+        <v>-0.2702807733411063</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-1.883430116446981</v>
+        <v>-1.04178814382896</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-1.009412216673063</v>
+        <v>-0.1592300962379625</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.8223684210526301</v>
+        <v>-0.6390509529366071</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.7076740932084888</v>
+        <v>-0.5149304542359658</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.847949798517334</v>
+        <v>2.075890251021598</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.5455203640932211</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>1.131830680453895</v>
+        <v>0.941199376947047</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 1.891</t>
+          <t>X &gt; 1.895</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.0868198184492</v>
+        <v>-1.640847113431967</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.04104295214115439</v>
+        <v>-0.3756239117817799</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.848997384481258</v>
+        <v>-2.613642960812768</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.9627906976744143</v>
+        <v>-1.726596980255508</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2719395173015329</v>
+        <v>-0.01077454957697199</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.259104130308316</v>
+        <v>0.9826432494236315</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3137620017457081</v>
+        <v>0.6762072851766021</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.207683352735735</v>
+        <v>5.276044620911321</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.649199417758368</v>
+        <v>3.691515542663431</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5246359930110671</v>
+        <v>0.4795754763830331</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.050276725895728</v>
+        <v>-0.05937301153633712</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.529370629370625</v>
+        <v>-4.403163065390835</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.8538618478577717</v>
+        <v>-0.6482763517591579</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.075218658892126</v>
+        <v>-0.8693552282057482</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1.465850102070576</v>
+        <v>1.724533994538902</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>2.860910151691954</v>
+        <v>3.131929046563187</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.526816457543035</v>
+        <v>4.624028169748328</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.621833041447751</v>
+        <v>3.706179335845839</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.63795620437957</v>
+        <v>3.922070716770165</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.024999999999999</v>
+        <v>3.295908396656884</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.481799591002044</v>
+        <v>1.940354098609561</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>5.605844535359445</v>
+        <v>5.116540657525654</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.480619701841569</v>
+        <v>2.951990979763806</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.204678362573098</v>
+        <v>3.689166856621839</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 1.964</t>
+          <t>X &gt; 1.968</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.693729248888054</v>
+        <v>-2.155698598580479</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.8926638639186066</v>
+        <v>1.469920642673671</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.983650849827789</v>
+        <v>-2.938395436060297</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.687543172921941</v>
+        <v>-4.641448465404025</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.072614938144007</v>
+        <v>-1.46238745280278</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.8953513152362262</v>
+        <v>-0.2754212667054006</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.6781184373892728</v>
+        <v>0.5283876251618196</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.993821966597118</v>
+        <v>5.300681230913796</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.05514001181777</v>
+        <v>3.321966392626479</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.688992428654629</v>
+        <v>-0.4812523137130427</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.414633161539292</v>
+        <v>-0.2071926715511196</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.644222114519138</v>
+        <v>-5.536447125504161</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1520787462016315</v>
+        <v>0.41109787834678</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.05937707473371</v>
+        <v>-0.8200820082008136</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.2618897060309706</v>
+        <v>0.5419767144206489</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>1.847048765553339</v>
+        <v>2.146464646464644</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>2.70305408130541</v>
+        <v>3.022648519588188</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.607971655309136</v>
+        <v>1.907706805665988</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.814193828141946</v>
+        <v>3.133699196691332</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.021039603960396</v>
+        <v>1.300342986457338</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.4778391949624421</v>
+        <v>0.7577968184913075</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.36228017892379</v>
+        <v>4.722354897486248</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>1.66675831570295</v>
+        <v>1.966526579665263</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>3.571014996236464</v>
+        <v>3.910896346644009</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 2.036</t>
+          <t>X &gt; 2.04</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>83</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.483645215274606</v>
+        <v>-2.450370922955777</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.7526078415096435</v>
+        <v>0.786280850122985</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.02731063749330787</v>
+        <v>-0.6517381989080064</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.355561782011769</v>
+        <v>-4.936120789779324</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.311193012818947</v>
+        <v>-2.890958881374218</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2856101544047149</v>
+        <v>-0.3230403143244516</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.7175632994591084</v>
+        <v>0.7839553506090553</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.258285762374292</v>
+        <v>5.325021014289725</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.890163273180058</v>
+        <v>2.956869641987559</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.498129968914668</v>
+        <v>-1.430503865374227</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.223770701799332</v>
+        <v>-1.156444223212304</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-5.117322436599537</v>
+        <v>-5.049651457985604</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-2.627355823761377</v>
+        <v>-2.558355693516418</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.848712634795731</v>
+        <v>-2.779434569963009</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.106813957492264</v>
+        <v>0.1768799637817295</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.7018740071136449</v>
+        <v>0.7712668857247209</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.977418867181591</v>
+        <v>3.046988302964117</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.667616173977869</v>
+        <v>1.737328322034493</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.088558614018126</v>
+        <v>3.158038980067261</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.480421686746979</v>
+        <v>4.549704067143708</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.732402000640604</v>
+        <v>2.802338622069257</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>6.270904776323299</v>
+        <v>6.34095049198546</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>4.136041388588545</v>
+        <v>4.20578665025063</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>6.46973860353696</v>
+        <v>6.539592951244238</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 2.109</t>
+          <t>X &gt; 2.113</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-5.848034449229054</v>
+        <v>-5.814760156910225</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3861085145980141</v>
+        <v>-0.3524355059846727</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.3765336163653146</v>
+        <v>-0.3411791926968277</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-6.887428378833832</v>
+        <v>-6.851234661414928</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-2.904872076901356</v>
+        <v>-4.288474409324529</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-2.71770746389457</v>
+        <v>-4.10150822322715</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-2.04129823362976</v>
+        <v>-2.63560524471341</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>2.027973207808195</v>
+        <v>1.497948016415876</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.8290614518068509</v>
+        <v>-1.401741272257659</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-4.501447587213953</v>
+        <v>-5.115833418882382</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-4.227088320098616</v>
+        <v>-4.841773776720458</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-8.854008310530041</v>
+        <v>-9.53228788605081</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-5.630673442060662</v>
+        <v>-6.243685247024573</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.5042041661385</v>
+        <v>-2.052999417588815</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.735415319461886</v>
+        <v>0.2300337554188587</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>1.330475369083267</v>
+        <v>0.8244206773618501</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>4.094932399572009</v>
+        <v>3.631680010972616</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>2.540673621157893</v>
+        <v>2.056251071857318</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>4.206072146408545</v>
+        <v>3.74273068807576</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>4.393115942028977</v>
+        <v>5.400164733337903</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>2.400640170712187</v>
+        <v>3.387030330077756</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>7.722949074551018</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>4.048735643870543</v>
+        <v>5.056247316444825</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>7.921591533809796</v>
       </c>
     </row>
   </sheetData>
@@ -5448,2379 +5448,2379 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.07272</t>
+          <t>X &lt; 0.07287</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.7833291145302397</v>
+        <v>-0.7500548222114105</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.4761063422366618</v>
+        <v>-0.4424333336233204</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.915806806322799</v>
+        <v>-1.880452382654312</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.130670783327517</v>
+        <v>-1.094477065908613</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.6453870547747655</v>
+        <v>0.7110600846704429</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2381121437816134</v>
+        <v>-0.1726375407953427</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.867509325086182</v>
+        <v>-1.801117273936235</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.931931208292106</v>
+        <v>-1.865195956376674</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.8197513317062928</v>
+        <v>-0.753044962898791</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.330644576702056</v>
+        <v>-2.382491688185823</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.270877584264824</v>
+        <v>-2.322564808336537</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.764563762417836</v>
+        <v>-2.815446974097171</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4555785860551964</v>
+        <v>-0.5124848439511425</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.03315857305521064</v>
+        <v>0.03611949177751228</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.1662792866199254</v>
+        <v>0.236345292909391</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.9553988611835891</v>
+        <v>-0.8860059825725131</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-1.823721176865568</v>
+        <v>-1.878292218262423</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-2.143758356401712</v>
+        <v>-2.197725196761724</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-3.43301153755592</v>
+        <v>-3.483979738584175</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.095430107526887</v>
+        <v>-1.151211181835031</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1332541724388108</v>
+        <v>-0.06331755101015801</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.6393167549631471</v>
+        <v>-0.5692710393009861</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.654864169126171</v>
+        <v>-1.585118907464086</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-1.174631982254496</v>
+        <v>-1.230843633805641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.1454</t>
+          <t>X &lt; 0.1457</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.7833291145302397</v>
+        <v>-0.7500548222114105</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4761063422366618</v>
+        <v>-0.4424333336233204</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.915806806322799</v>
+        <v>-1.880452382654312</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.130670783327517</v>
+        <v>-1.094477065908613</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.6453870547747655</v>
+        <v>0.7110600846704429</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2381121437816134</v>
+        <v>-0.1726375407953427</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.867509325086182</v>
+        <v>-1.801117273936235</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.931931208292106</v>
+        <v>-1.865195956376674</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.8197513317062928</v>
+        <v>-0.753044962898791</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.330644576702056</v>
+        <v>-2.382491688185823</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.270877584264824</v>
+        <v>-2.322564808336537</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.764563762417836</v>
+        <v>-2.815446974097171</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4555785860551964</v>
+        <v>-0.5124848439511425</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.03315857305521064</v>
+        <v>0.03611949177751228</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.1662792866199254</v>
+        <v>0.236345292909391</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.9553988611835891</v>
+        <v>-0.8860059825725131</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-1.823721176865568</v>
+        <v>-1.878292218262423</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-2.143758356401712</v>
+        <v>-2.197725196761724</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-3.43301153755592</v>
+        <v>-3.483979738584175</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.095430107526887</v>
+        <v>-1.151211181835031</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1332541724388108</v>
+        <v>-0.06331755101015801</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.6393167549631471</v>
+        <v>-0.5692710393009861</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-1.654864169126171</v>
+        <v>-1.585118907464086</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-1.174631982254496</v>
+        <v>-1.230843633805641</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.2182</t>
+          <t>X &lt; 0.2186</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.7833291145302397</v>
+        <v>-0.7500548222114105</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.4761063422366618</v>
+        <v>-0.4424333336233204</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.915806806322799</v>
+        <v>-1.880452382654312</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.130670783327517</v>
+        <v>-1.094477065908613</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6453870547747655</v>
+        <v>0.7110600846704429</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2381121437816134</v>
+        <v>-0.1726375407953427</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.867509325086182</v>
+        <v>-1.801117273936235</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.931931208292106</v>
+        <v>-1.865195956376674</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.8197513317062928</v>
+        <v>-0.753044962898791</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.330644576702056</v>
+        <v>-2.382491688185823</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.270877584264824</v>
+        <v>-2.322564808336537</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.764563762417836</v>
+        <v>-2.815446974097171</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4555785860551964</v>
+        <v>-0.5124848439511425</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.03315857305521064</v>
+        <v>0.03611949177751228</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.1662792866199254</v>
+        <v>0.236345292909391</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.9553988611835891</v>
+        <v>-0.8860059825725131</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.823721176865568</v>
+        <v>-1.878292218262423</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-2.143758356401712</v>
+        <v>-2.197725196761724</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.43301153755592</v>
+        <v>-3.483979738584175</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.095430107526887</v>
+        <v>-1.151211181835031</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1332541724388108</v>
+        <v>-0.06331755101015801</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.6393167549631471</v>
+        <v>-0.5692710393009861</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.654864169126171</v>
+        <v>-1.585118907464086</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.174631982254496</v>
+        <v>-1.230843633805641</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.2909</t>
+          <t>X &lt; 0.2915</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.7833291145302397</v>
+        <v>-0.7500548222114105</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4761063422366618</v>
+        <v>-0.4424333336233204</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.915806806322799</v>
+        <v>-1.880452382654312</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.130670783327517</v>
+        <v>-1.094477065908613</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.6453870547747655</v>
+        <v>0.7110600846704429</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2381121437816134</v>
+        <v>-0.1726375407953427</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.867509325086182</v>
+        <v>-1.801117273936235</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.931931208292106</v>
+        <v>-1.865195956376674</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.8197513317062928</v>
+        <v>-0.753044962898791</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.330644576702056</v>
+        <v>-2.382491688185823</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.270877584264824</v>
+        <v>-2.322564808336537</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.764563762417836</v>
+        <v>-2.815446974097171</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4555785860551964</v>
+        <v>-0.5124848439511425</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.03315857305521064</v>
+        <v>0.03611949177751228</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.1662792866199254</v>
+        <v>0.236345292909391</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.9553988611835891</v>
+        <v>-0.8860059825725131</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.823721176865568</v>
+        <v>-1.878292218262423</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.143758356401712</v>
+        <v>-2.197725196761724</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.43301153755592</v>
+        <v>-3.483979738584175</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.095430107526887</v>
+        <v>-1.151211181835031</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.1332541724388108</v>
+        <v>-0.06331755101015801</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.6393167549631471</v>
+        <v>-0.5692710393009861</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-1.654864169126171</v>
+        <v>-1.585118907464086</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-1.174631982254496</v>
+        <v>-1.230843633805641</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.3636</t>
+          <t>X &lt; 0.3644</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7833291145302397</v>
+        <v>-0.7500548222114105</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.4761063422366618</v>
+        <v>-0.4424333336233204</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.915806806322799</v>
+        <v>-1.880452382654312</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.130670783327517</v>
+        <v>-1.094477065908613</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.6453870547747655</v>
+        <v>0.7110600846704429</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2381121437816134</v>
+        <v>-0.1726375407953427</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.867509325086182</v>
+        <v>-1.801117273936235</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.931931208292106</v>
+        <v>-1.865195956376674</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.8197513317062928</v>
+        <v>-0.753044962898791</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.330644576702056</v>
+        <v>-2.382491688185823</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.270877584264824</v>
+        <v>-2.322564808336537</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.764563762417836</v>
+        <v>-2.815446974097171</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4555785860551964</v>
+        <v>-0.5124848439511425</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.03315857305521064</v>
+        <v>0.03611949177751228</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.1662792866199254</v>
+        <v>0.236345292909391</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.9553988611835891</v>
+        <v>-0.8860059825725131</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.823721176865568</v>
+        <v>-1.878292218262423</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.143758356401712</v>
+        <v>-2.197725196761724</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.43301153755592</v>
+        <v>-3.483979738584175</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.095430107526887</v>
+        <v>-1.151211181835031</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.1332541724388108</v>
+        <v>-0.06331755101015801</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.6393167549631471</v>
+        <v>-0.5692710393009861</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.654864169126171</v>
+        <v>-1.585118907464086</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.174631982254496</v>
+        <v>-1.230843633805641</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.4363</t>
+          <t>X &lt; 0.4372</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.582436970782787</v>
+        <v>-0.5491626784639578</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2779536368130309</v>
+        <v>-0.2442806281996894</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.717654100899168</v>
+        <v>-1.682299677230681</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.9389101006594913</v>
+        <v>-0.9027163832405876</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.8280162763633712</v>
+        <v>0.8936893062590485</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05091719165329778</v>
+        <v>0.01455741133297295</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.889881404730779</v>
+        <v>-1.823489353580833</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.955216434044651</v>
+        <v>-1.888481182129219</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.8476022879985621</v>
+        <v>-0.7808959191910603</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.355405223780288</v>
+        <v>-2.406690060046309</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.081045956664951</v>
+        <v>-2.132630417884386</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.573815073815069</v>
+        <v>-2.624599437537078</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2795028734987923</v>
+        <v>-0.3362476451181493</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1401659564924884</v>
+        <v>0.2094440213252113</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.3359355721560391</v>
+        <v>0.4060015784455047</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.7784060876242833</v>
+        <v>-0.7090132090132073</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.643204955733196</v>
+        <v>-1.697631200691532</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.962321134141106</v>
+        <v>-2.016147118187938</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-3.24512730739773</v>
+        <v>-3.295982232990099</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.9167558886509681</v>
+        <v>-0.9723842862699357</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.03897303853951684</v>
+        <v>0.1089096599681696</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.4652475417283526</v>
+        <v>-0.3952018260661916</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.475268949122032</v>
+        <v>-1.405523687459947</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.997038375624328</v>
+        <v>-1.053090416057955</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.5091</t>
+          <t>X &lt; 0.5101</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3971658032137952</v>
+        <v>-0.3638915108949661</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.09809184639934898</v>
+        <v>-0.06441883778600754</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.537792310485486</v>
+        <v>-1.502437886816999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.7716701902748326</v>
+        <v>-0.7354764728559289</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.7658084390774391</v>
+        <v>0.8314814689731165</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.315525890833328</v>
+        <v>-0.2500512878470573</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.145474475318643</v>
+        <v>-2.079082424168696</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.001196139864682</v>
+        <v>-1.93446088794925</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6911811319245089</v>
+        <v>-0.6244747631170071</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.192432603180556</v>
+        <v>-2.243056401098528</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.91807333606522</v>
+        <v>-1.968996758936605</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.409031646319782</v>
+        <v>-2.459162652870859</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1436923563323518</v>
+        <v>-0.1996608719468469</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2705440529722765</v>
+        <v>0.3398221178049994</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.6709348478332871</v>
+        <v>0.7410008541227526</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.4289203567826263</v>
+        <v>-0.3595274781715503</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.286771652860367</v>
+        <v>-1.34090224226766</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.604069294008724</v>
+        <v>-1.657607352868503</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-2.874145706448459</v>
+        <v>-2.924766819401803</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.5639596602972432</v>
+        <v>-0.6192769416371675</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.379039506076353</v>
+        <v>0.4489761275050057</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1215439996724115</v>
+        <v>-0.05149828401025047</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.120654183508755</v>
+        <v>-1.05090892184667</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.646385467214138</v>
+        <v>-0.70211272496379</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.5818</t>
+          <t>X &lt; 0.583</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8557497982351379</v>
+        <v>-0.8224755059163087</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.355852243985936</v>
+        <v>-0.3221792353725945</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.586784440848689</v>
+        <v>-1.551430017180202</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8391998834781731</v>
+        <v>-0.8030061660592693</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.6744447365082138</v>
+        <v>0.7401177664038912</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3910002538252968</v>
+        <v>-0.3255256508390261</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.207707721996222</v>
+        <v>-2.141315670846275</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.859957565844638</v>
+        <v>-1.793222313929206</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7746001647050917</v>
+        <v>-0.7078937958975899</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.266895407237001</v>
+        <v>-2.315882540827616</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.992536140121665</v>
+        <v>-2.041822898665693</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.062425022676067</v>
+        <v>-2.111804034890312</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.160364093564823</v>
+        <v>0.1053261738276916</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5666223452919823</v>
+        <v>0.6359004101247052</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.9537162108571877</v>
+        <v>1.023782217146653</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1248639068854516</v>
+        <v>-0.05547102827437556</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.182617504721122</v>
+        <v>-1.235413269854362</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.287600920816402</v>
+        <v>-1.340253973675544</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.538982998974738</v>
+        <v>-2.588797739194725</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2555031446540923</v>
+        <v>-0.3099017200216778</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.6688016874381049</v>
+        <v>0.7387383088667576</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.1735594200554615</v>
+        <v>0.2436051357176225</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.8095270486825399</v>
+        <v>-0.7397817870204548</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.5516241584353025</v>
+        <v>-0.6059704343737167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.6545</t>
+          <t>X &lt; 0.6558</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.888407120036504</v>
+        <v>-1.855132827717675</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.628344539442736</v>
+        <v>-1.594671530829395</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.671219606703481</v>
+        <v>-2.635865183034994</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.202473237356955</v>
+        <v>-1.166279519938051</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6147966601586745</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3885149173107223</v>
+        <v>-0.3230403143244516</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.351857239840939</v>
+        <v>-2.285465188690992</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.035173790121405</v>
+        <v>-1.968438538205973</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.001594233035284</v>
+        <v>-0.9348878642277825</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.856246330983232</v>
+        <v>-2.898279730740455</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.18427274975258</v>
+        <v>-2.22739469175314</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.065752339112173</v>
+        <v>-2.109318698375738</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.009329044676853471</v>
+        <v>-0.05787759062868503</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1669284584040938</v>
+        <v>0.2362065232368167</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.7008401617127191</v>
+        <v>0.7709061680021847</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.09574988806947005</v>
+        <v>-0.02635700945839403</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.107446490664138</v>
+        <v>-1.154309931724143</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.212429906759418</v>
+        <v>-1.259150635545325</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.589932241835569</v>
+        <v>-2.633716511082227</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.2116533864541807</v>
+        <v>-0.2599919734800125</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.8387717025558317</v>
+        <v>0.9087083239844844</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.1652070851602332</v>
+        <v>0.2352528008223942</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.7552368718636089</v>
+        <v>-0.6854916102015238</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.7134853100815945</v>
+        <v>-0.7613238634247992</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.7272</t>
+          <t>X &lt; 0.7287</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.822269553898948</v>
+        <v>-1.880283733150279</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.7465103242751994</v>
+        <v>-0.8066098272747411</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.009843945327816</v>
+        <v>-2.068572538277557</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.783601985152373</v>
+        <v>-0.8449068394104415</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4384298171251686</v>
+        <v>0.4038097302957979</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.7853403141361213</v>
+        <v>-0.8176747878321677</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.440040661357699</v>
+        <v>-2.469905161863359</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.894962149909766</v>
+        <v>-2.92417294464461</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.089777654552037</v>
+        <v>-1.122122382448218</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.940890409972191</v>
+        <v>-2.071094396512869</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.196566478545904</v>
+        <v>-2.325203768435458</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.592268155872389</v>
+        <v>-1.723671481742606</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2867741945450604</v>
+        <v>0.1461241978801482</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5954527191997556</v>
+        <v>0.5587860373338955</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1131999253921236</v>
+        <v>0.07700958278685022</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.1751322511348974</v>
+        <v>-0.2104377104377164</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.089112745996793</v>
+        <v>-1.049822219549227</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.548078462977031</v>
+        <v>-1.507396609437428</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-2.393902202700083</v>
+        <v>-2.349706286714159</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.4369469026548671</v>
+        <v>-0.3991920464110379</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.4357818918870038</v>
+        <v>0.5757644809819311</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.3481377655255216</v>
+        <v>-0.2067952613458885</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.312300652140735</v>
+        <v>-1.169069665471611</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.107378375015557</v>
+        <v>-1.06822347346521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.8</t>
+          <t>X &lt; 0.8016</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.59697007043922</v>
+        <v>-1.351334558040527</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.487041727516782</v>
+        <v>-1.39069038150113</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.888166523947135</v>
+        <v>-1.794736018419862</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.9699123593954866</v>
+        <v>-0.7351641885272997</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.4452332858475287</v>
+        <v>0.5538607008161236</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1094418637569561</v>
+        <v>-0.145436037754159</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.069251615989032</v>
+        <v>-1.80364764631215</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.199438308985336</v>
+        <v>-1.934148603620621</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3775068136956392</v>
+        <v>-0.1201355723706143</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.6209212827584665</v>
+        <v>-0.5976302735178862</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3465620156431299</v>
+        <v>-0.1758601439113576</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1172861314020395</v>
+        <v>0.2839428898636882</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.96456311499513</v>
+        <v>2.114990571899746</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.040383124168798</v>
+        <v>2.280449938484978</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.67862870533952</v>
+        <v>1.918164629070098</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7878046539207801</v>
+        <v>0.8853326161018487</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2981835424569681</v>
+        <v>-0.2840874794555077</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.4031669585522479</v>
+        <v>-0.3889281832766898</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.7822818908585276</v>
+        <v>-0.7647527786837287</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.4464285714285694</v>
+        <v>0.4575959898641884</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.242513876716338</v>
+        <v>1.336921397615889</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.5713207258356263</v>
+        <v>0.6684828436141927</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.3443802981584341</v>
+        <v>-0.2422276290889371</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.3318343050871064</v>
+        <v>-0.3180598823122125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.8727</t>
+          <t>X &lt; 0.8745</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.9760731853145188</v>
+        <v>-1.069418542003397</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.966817012243574</v>
+        <v>-0.9470524832103564</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.143601288040387</v>
+        <v>-1.127928675098488</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5306067896284432</v>
+        <v>-0.583739837398376</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.09127887350305741</v>
+        <v>-0.1195303099456453</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6446933380461104</v>
+        <v>-0.8468498381339771</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.992933463195648</v>
+        <v>-2.190227093452897</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.041338511475999</v>
+        <v>-2.176839976584532</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.04355086992863022</v>
+        <v>-0.07585622716410256</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.06011986397879809</v>
+        <v>-0.2105035893560654</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.135898389311649</v>
+        <v>1.0944838878574</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5111823660210746</v>
+        <v>0.3575443354976073</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.151668106059276</v>
+        <v>1.868975624884328</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.045518668296808</v>
+        <v>1.947270415114914</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2.193039042162745</v>
+        <v>1.977200512029768</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.290403239249564</v>
+        <v>1.080761745899366</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.8804496755361058</v>
+        <v>0.7174868107567534</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1472557705476376</v>
+        <v>-0.3047850857249799</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.7385143838557227</v>
+        <v>-1.006324897461205</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.3712514417531736</v>
+        <v>0.09795210516737285</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.9814535702408023</v>
+        <v>0.8865238128899406</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.020838768346742</v>
+        <v>0.9254884140525874</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.4344898713994922</v>
+        <v>-0.4073847494699407</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.1353942979079719</v>
+        <v>0.2056463727373199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.9454</t>
+          <t>X &lt; 0.9473</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1292</v>
+        <v>1310</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7103030839648028</v>
+        <v>-0.8693968476764624</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1216910697407698</v>
+        <v>-0.02425613062676746</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4836394168138227</v>
+        <v>-0.3224575504784326</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1546207044827526</v>
+        <v>0.2563817431487365</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.2516005342506915</v>
+        <v>0.4525061642184909</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3655681904318442</v>
+        <v>-0.1963939110823034</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9409224955728632</v>
+        <v>-0.7403790691367931</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.296637634918589</v>
+        <v>-1.127862764170132</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.05660682516577253</v>
+        <v>0.2064000831438122</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.2537423853673175</v>
+        <v>0.390478695004262</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.423293598679237</v>
+        <v>1.470667422150562</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.453318706023495</v>
+        <v>1.496563867902864</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.338101057860932</v>
+        <v>2.353599820848729</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.884904988712201</v>
+        <v>2.026986235208895</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.694289051065944</v>
+        <v>2.864977893257063</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.898313552001078</v>
+        <v>1.93381180223286</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.73439573055154</v>
+        <v>1.799894665255387</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.320054232476366</v>
+        <v>1.313665708192403</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.994800751943373</v>
+        <v>1.071891185226569</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.259184068058786</v>
+        <v>1.335014645842961</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.566718384505528</v>
+        <v>1.754789647545209</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.490763328862919</v>
+        <v>1.526271930410907</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.4507666469305107</v>
+        <v>0.5030367192288452</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.6535947712418277</v>
+        <v>0.732547977455944</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 1.018</t>
+          <t>X &lt; 1.02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1802</v>
+        <v>1811</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.2229894344642176</v>
+        <v>-0.1499180315188227</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2268562798650322</v>
+        <v>-0.1802443738279891</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3212952715099036</v>
+        <v>0.3619345969430015</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3565463189001719</v>
+        <v>0.3640520846509787</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1744693224774707</v>
+        <v>-0.191760390096519</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4536653555954899</v>
+        <v>-0.444838208399581</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.8084522672324326</v>
+        <v>-0.8317483884395429</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.418865319830637</v>
+        <v>-1.40923577069281</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3817740335690658</v>
+        <v>-0.3771046702310485</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.03806461573271491</v>
+        <v>0.09276984621219242</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.04296775579605594</v>
+        <v>0.01319300338000318</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5409894814326961</v>
+        <v>0.5608898809237388</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8569414762419569</v>
+        <v>0.8702347011199691</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.5801830031577353</v>
+        <v>0.6271354809130329</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.140088329217392</v>
+        <v>1.160405904278406</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.291935082439878</v>
+        <v>1.347080072245639</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.9143996061017887</v>
+        <v>0.9924123833917804</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.6985514449954238</v>
+        <v>0.7771964036324093</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.526648000388434</v>
+        <v>0.606774318773077</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.8245565410199589</v>
+        <v>0.8488077667101877</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.313080789005376</v>
+        <v>1.333403799399221</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.9043470311997055</v>
+        <v>0.9262491687466081</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.06985985713829734</v>
+        <v>0.1515797619575423</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.08259179209585454</v>
+        <v>0.130965620274857</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 1.091</t>
+          <t>X &lt; 1.093</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2208</v>
+        <v>2218</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8362835679129574</v>
+        <v>-0.7708919564812931</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2705581816563907</v>
+        <v>-0.1846862715843827</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1787271142109859</v>
+        <v>-0.162296461710433</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3942169634341894</v>
+        <v>0.3814820143584967</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1513142005894039</v>
+        <v>-0.08895836842217619</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.4346740482309031</v>
+        <v>-0.4405918232583659</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.6861571302978078</v>
+        <v>-0.7188241696262807</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.7391817803269589</v>
+        <v>-0.7023214043295312</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1112877270318933</v>
+        <v>-0.03218581648756924</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.2688658120430887</v>
+        <v>0.3437088886066419</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1181205653006572</v>
+        <v>0.1945778425789442</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2265462631316311</v>
+        <v>0.2304351807039779</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3484879036108239</v>
+        <v>0.3657000801400017</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2896999667859959</v>
+        <v>0.216361564213976</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.6705517295570118</v>
+        <v>0.6646610476312915</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.9491560829758541</v>
+        <v>1.016351635163517</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.023333870478353</v>
+        <v>1.044742489453434</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.8553172043436774</v>
+        <v>0.8771307750899666</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.8451960233840907</v>
+        <v>0.8227518857440117</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.9869909502262431</v>
+        <v>0.9645526506669952</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.19542566614917</v>
+        <v>1.125147659028265</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.9383931999135342</v>
+        <v>0.8964493132398133</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2625119607822626</v>
+        <v>0.2692107705370148</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.3948957538774422</v>
+        <v>0.3737211683507056</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 1.164</t>
+          <t>X &lt; 1.166</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2472</v>
+        <v>2481</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6572267959358271</v>
+        <v>-0.614795009223549</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.05345448748902726</v>
+        <v>0.0740954146015369</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.06186343611407352</v>
+        <v>0.1018002802622391</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3764447148004351</v>
+        <v>0.3515418083525859</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1095494163000694</v>
+        <v>-0.1045856076363236</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1814755798366008</v>
+        <v>-0.1984056229027544</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3276162103643117</v>
+        <v>-0.3285572751043802</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6235817560474999</v>
+        <v>-0.6642651834708246</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1028658158244369</v>
+        <v>0.05940498399765204</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3598460706729369</v>
+        <v>0.31312258744628</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.2142394031365384</v>
+        <v>0.1286963390366793</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3619565186729403</v>
+        <v>0.2749817473951737</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.3910130512544185</v>
+        <v>0.276769459566772</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2341071384433633</v>
+        <v>0.1197828786094135</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.3018614060673457</v>
+        <v>0.2093379016853305</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.5739501193948158</v>
+        <v>0.5061678734245163</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.625685601323319</v>
+        <v>0.5573516880941725</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.5046613242760358</v>
+        <v>0.4364727257362588</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.2359360023593595</v>
+        <v>0.1692723192209726</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.2046281325788186</v>
+        <v>0.1145722354691898</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.2516338004642407</v>
+        <v>0.1597909848833794</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.1756787448216315</v>
+        <v>0.1081223219321501</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.00565002937897674</v>
+        <v>-0.06059394060593348</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.1270368477828896</v>
+        <v>-0.2333270236978606</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 1.236</t>
+          <t>X &lt; 1.239</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2649</v>
+        <v>2656</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4834307150601092</v>
+        <v>-0.4397988169138074</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4432308543290588</v>
+        <v>-0.3801182938042587</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.144095708611836</v>
+        <v>0.2251730751557588</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3148660803954328</v>
+        <v>0.3364978118014292</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.008378285145255404</v>
+        <v>0.00070733925415567</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.0838496464673284</v>
+        <v>-0.1120642041351587</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1964687686629958</v>
+        <v>-0.2470702128662694</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3031853949137542</v>
+        <v>-0.3915484118405885</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2272362737192566</v>
+        <v>0.1587254341099253</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.6789757451379259</v>
+        <v>0.6076562770710154</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.298010816445256</v>
+        <v>0.2283067883385783</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2667137079787665</v>
+        <v>0.196558607501558</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1058368338748039</v>
+        <v>0.0118349790838792</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.09524102460449058</v>
+        <v>0.0007435967028897039</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.001494412545334001</v>
+        <v>-0.07159703964897091</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.1820857357160648</v>
+        <v>0.1319565440196797</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.221275560445406</v>
+        <v>0.1708219835511287</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.2142915633180351</v>
+        <v>0.1636775700985851</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.09104821041275102</v>
+        <v>0.04109584083110462</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.03890041493775698</v>
+        <v>-0.1105314593926749</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>-0.02885069501851234</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.1073630118103779</v>
+        <v>-0.1574556277890906</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.2854180340074919</v>
+        <v>-0.3722545321681565</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.414423185180766</v>
+        <v>-0.5010696993581831</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 1.309</t>
+          <t>X &lt; 1.312</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2758</v>
+        <v>2763</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3407880724174603</v>
+        <v>-0.3674658184679416</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2074951185933287</v>
+        <v>-0.1433101298458368</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1906422551583802</v>
+        <v>0.2379049153571344</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3260341040559354</v>
+        <v>0.3528846612131744</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.01886466589355962</v>
+        <v>0.01709418866590084</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2442147730105759</v>
+        <v>-0.2279050680012986</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.09463533267316393</v>
+        <v>-0.0639286259017311</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3887065389610171</v>
+        <v>-0.3576303690614822</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.01382035638653178</v>
+        <v>0.06460895659468235</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3441252926516327</v>
+        <v>0.3934405609798333</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1338273203470521</v>
+        <v>0.1838846481491245</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.05639012234603769</v>
+        <v>0.03422534022779899</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.001380379184887204</v>
+        <v>-0.04313795273722576</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.0177141380964656</v>
+        <v>-0.02643121455002273</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.2209805781030809</v>
+        <v>-0.2661769988214857</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.09625337942237167</v>
+        <v>-0.1195164642818085</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.1364481099560564</v>
+        <v>-0.1597715642403514</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.002641976655070266</v>
+        <v>-0.0263738856401261</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.09083771086852721</v>
+        <v>-0.07803505949540579</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.1721014492753667</v>
+        <v>-0.1803110420824936</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.04143346445282958</v>
+        <v>-0.0868755012352409</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.1898785527159461</v>
+        <v>-0.2134406712207166</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.1688185004056209</v>
+        <v>-0.1706191175383154</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.3682005351789002</v>
+        <v>-0.33350203456218</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 1.382</t>
+          <t>X &lt; 1.385</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2865</v>
+        <v>2874</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.5534556637258348</v>
+        <v>-0.5288139184112168</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4192865145678653</v>
+        <v>-0.3609577063165474</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.0834341104892502</v>
+        <v>0.08808714299345155</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.0828720365379354</v>
+        <v>0.06717464604206214</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.2975849533683714</v>
+        <v>-0.3378199787543394</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3339514252472355</v>
+        <v>-0.3737251780934372</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1495383129648786</v>
+        <v>-0.2110944227314491</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.3735536173824059</v>
+        <v>-0.4349996778973093</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2277984974605403</v>
+        <v>-0.2006165549651371</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.1652493041734999</v>
+        <v>0.1896983572376243</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.1121711183323697</v>
+        <v>0.1026650039911274</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1314989358467642</v>
+        <v>0.1560534699090468</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.001531332378831962</v>
+        <v>-0.03090887433958045</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.05997327079604986</v>
+        <v>-0.1274112843126076</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.1411136862302556</v>
+        <v>-0.1751178958037301</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.1031567006757328</v>
+        <v>-0.1153061331818677</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1817171544388572</v>
+        <v>-0.1938918844522135</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.09175580872646805</v>
+        <v>-0.1044256336981206</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.2033822410718145</v>
+        <v>-0.2152875435393327</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.274581589958153</v>
+        <v>-0.30641254663594</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.06469500264985584</v>
+        <v>-0.09852447578619206</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.2942252483111858</v>
+        <v>-0.3274477183803484</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.2636929290028149</v>
+        <v>-0.275721993018081</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.4235938887358088</v>
+        <v>-0.4352793982791212</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 1.454</t>
+          <t>X &lt; 1.457</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2937</v>
+        <v>2943</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.5618074679970775</v>
+        <v>-0.5844472485214567</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2360312689568858</v>
+        <v>-0.191840127998006</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.01631564428354437</v>
+        <v>0.07807721492227415</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.03219914660452616</v>
+        <v>0.04102721710846424</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1447215053872597</v>
+        <v>-0.1257872500315855</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2772102328353157</v>
+        <v>-0.291648447232788</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1161340790076437</v>
+        <v>-0.1508182264578224</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3414691896371451</v>
+        <v>-0.3759703030255324</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.06266498902130024</v>
+        <v>-0.1122403568712045</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3358590900679488</v>
+        <v>0.318624628295872</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.3247571954068533</v>
+        <v>0.3077741941266368</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.302933408634118</v>
+        <v>0.2857436272656528</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1147735900241074</v>
+        <v>0.04304210900419037</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.04939933771228766</v>
+        <v>-0.02247175937105794</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.09003488467926246</v>
+        <v>0.01724447162672504</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.03971449951804118</v>
+        <v>-0.0120698510529067</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.00617708645968662</v>
+        <v>-0.05800542576566414</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.04508253159050923</v>
+        <v>-0.006962273182196554</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.02447154128517326</v>
+        <v>-0.07620781369074336</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.0892857142857153</v>
+        <v>-0.1608245079643211</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.06818951954917196</v>
+        <v>-0.004407711533993108</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.1575319112028453</v>
+        <v>-0.1957566080615933</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.121014062624063</v>
+        <v>-0.1387654712789512</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.2107114910189978</v>
+        <v>-0.2623344320913503</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 1.527</t>
+          <t>X &lt; 1.53</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3017</v>
+        <v>3022</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3320074775321586</v>
+        <v>-0.3688970969900041</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2543562089326699</v>
+        <v>-0.2585186486238911</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1175375298797405</v>
+        <v>0.1309440743961758</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.05076433853108853</v>
+        <v>-0.05552096840951037</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.100901616515209</v>
+        <v>-0.06225583055863382</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4226630968595018</v>
+        <v>-0.3833870336573497</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2206221600570473</v>
+        <v>-0.2007603390091859</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4474139748789128</v>
+        <v>-0.4273265385822853</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2220877109545114</v>
+        <v>-0.2353458603379508</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1784343272266398</v>
+        <v>0.1637479359000551</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.009696854025015966</v>
+        <v>-0.004440029774087861</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.08007766927489968</v>
+        <v>0.06556708185127746</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.06681624309901224</v>
+        <v>-0.08195934294262486</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.07025998120617771</v>
+        <v>-0.08558427601254692</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.01510227888181248</v>
+        <v>-0.03108059130992302</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.1806242398424374</v>
+        <v>-0.1762007663295222</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.1296837078555768</v>
+        <v>-0.1254106720641417</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.1487824449850734</v>
+        <v>-0.1445301325967208</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.1115307204797418</v>
+        <v>-0.1072362649976029</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.1697019867549656</v>
+        <v>-0.1847658681161519</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.03082048186976039</v>
+        <v>-0.04661089500731919</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.2857392949917923</v>
+        <v>-0.301093875962529</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.24290581174359</v>
+        <v>-0.2384540904162904</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.3322788797205689</v>
+        <v>-0.3277174551729729</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 1.6</t>
+          <t>X &lt; 1.603</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3089</v>
+        <v>3095</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2164179641296968</v>
+        <v>-0.1726390209464199</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2769931880913887</v>
+        <v>-0.2332532082803382</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.02075808527420975</v>
+        <v>0.08121565101242112</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.0007110725219163783</v>
+        <v>0.04306882951313185</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.007676799980224303</v>
+        <v>0.02861511789129167</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3988668841844358</v>
+        <v>-0.3448523178143716</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.2838650945292116</v>
+        <v>-0.24891286284263</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5763321161653252</v>
+        <v>-0.5731698197861306</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3875510658006291</v>
+        <v>-0.352604988602998</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.04659665086337128</v>
+        <v>-0.0132518457125812</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1405993065408779</v>
+        <v>-0.1067352489179711</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.04611796722154793</v>
+        <v>-0.01276211051201415</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.02209942048526869</v>
+        <v>-0.02222081584147872</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.03059482937969449</v>
+        <v>-0.03094059405940186</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.1212300012886018</v>
+        <v>-0.1220922706280376</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.2367642669126937</v>
+        <v>-0.2176015473887745</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2224565634585858</v>
+        <v>-0.2034206207021754</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1466220328896739</v>
+        <v>-0.1278096492052967</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.07287470412349961</v>
+        <v>-0.08630334567326514</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.254689521345405</v>
+        <v>-0.2866792201195665</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.1317235406705564</v>
+        <v>-0.1645969057100345</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.3177800601098184</v>
+        <v>-0.3180393582777228</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.2695421104561717</v>
+        <v>-0.282709971896864</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.3262377915220753</v>
+        <v>-0.3393606661331958</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 1.673</t>
+          <t>X &lt; 1.676</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3168</v>
+        <v>3173</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.02725876990792386</v>
+        <v>-0.02355929633206699</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.07142431292728446</v>
+        <v>-0.09091213233315898</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.05774877177854165</v>
+        <v>0.08620034849465696</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.08328588738521603</v>
+        <v>0.08029957146862898</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1124418720896045</v>
+        <v>0.08933668512825221</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1537099400434343</v>
+        <v>-0.1763306426853433</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.06066743686979947</v>
+        <v>-0.101618931467506</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2898653587664626</v>
+        <v>-0.3306002159260046</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1989615379159488</v>
+        <v>-0.2398519793581926</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.08291117680026616</v>
+        <v>0.04091854744086021</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.001896732187013583</v>
+        <v>-0.04354679361953373</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.0833417683637947</v>
+        <v>0.04131542462019411</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.01588948988223393</v>
+        <v>0.004582203216600078</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.002111315918966739</v>
+        <v>-0.009334685825592715</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.145819195003682</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.2005071711426893</v>
+        <v>-0.1929674099485368</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.1898817151097631</v>
+        <v>-0.18241247093993</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1185388463555839</v>
+        <v>-0.1112238476258938</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.198865989819673</v>
+        <v>-0.1913358563890526</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.1823163040050488</v>
+        <v>-0.1933474590744666</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.1074748569474835</v>
+        <v>-0.1190446439924742</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.3538903967958191</v>
+        <v>-0.3650546308681655</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.2053380135260596</v>
+        <v>-0.1978391952865195</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.1993620414673103</v>
+        <v>-0.1919028396723519</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 1.745</t>
+          <t>X &lt; 1.749</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3219</v>
+        <v>3223</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.04645854684373063</v>
+        <v>-0.07932999964843646</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1180060000739331</v>
+        <v>-0.1199792479939958</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1099896445490032</v>
+        <v>0.1556257834019803</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.0003232967648756357</v>
+        <v>0.01537832838646125</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1003719783721309</v>
+        <v>-0.1043627614447615</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2048835049312459</v>
+        <v>-0.1778602910956479</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.06366923736722896</v>
+        <v>-0.05447090768127794</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2317846336546125</v>
+        <v>-0.2533145639714434</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2035233545188646</v>
+        <v>-0.1941961596806578</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.03073386152313873</v>
+        <v>0.03940543809427766</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.04446011620954238</v>
+        <v>0.05321667695714183</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1549279150703811</v>
+        <v>0.1634085743515286</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.02213941910932249</v>
+        <v>-0.01381315590541732</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.02276708638212455</v>
+        <v>0.03094059405940186</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.05975436166160364</v>
+        <v>-0.05170382354958036</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.1156552543836824</v>
+        <v>-0.08889201613659736</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.1382998215267364</v>
+        <v>-0.1115112884644702</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.1007476037135362</v>
+        <v>-0.07400623552660335</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1453512731258613</v>
+        <v>-0.1185318212663731</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.1881595282433253</v>
+        <v>-0.1795942852369876</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.1231057179082313</v>
+        <v>-0.1148477925290052</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.3357703714728686</v>
+        <v>-0.3272105241722016</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.2473306087174336</v>
+        <v>-0.2203546394740172</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2426655330466616</v>
+        <v>-0.2156937867720643</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 1.818</t>
+          <t>X &lt; 1.822</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3258</v>
+        <v>3263</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.06021472688528462</v>
+        <v>-0.1085694033223419</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1044769081925665</v>
+        <v>-0.1224408475112995</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.07266216402392445</v>
+        <v>0.07081773388558332</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.04438972117151252</v>
+        <v>-0.04613370686325879</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.08727904191702152</v>
+        <v>-0.1076175655732783</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1882241139664842</v>
+        <v>-0.1778602910956479</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1192598636882849</v>
+        <v>-0.1266382432786841</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3192949546275372</v>
+        <v>-0.3264963084320911</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2603360345643679</v>
+        <v>-0.2676207540076518</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.03842382547819057</v>
+        <v>-0.07715026176234829</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.05211158828105056</v>
+        <v>-0.06011752447597729</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.0535599304336003</v>
+        <v>0.04517057825093929</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.01786397833561892</v>
+        <v>-0.02175847998299929</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.02891357251283466</v>
+        <v>-0.01089018159376565</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.06066551336115111</v>
+        <v>-0.1007587082658787</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.0291357901150846</v>
+        <v>-0.06890210574099598</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.08372275814323871</v>
+        <v>-0.1234917825154156</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.04785742744590493</v>
+        <v>-0.0877757037351472</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.08932767054378843</v>
+        <v>-0.1290383377720374</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.09870438515792301</v>
+        <v>-0.1076766033804333</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.1022494887525554</v>
+        <v>-0.1115828322723047</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2212189810566443</v>
+        <v>-0.2303884626078059</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1612336274005273</v>
+        <v>-0.1520860168885037</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.188200704339117</v>
+        <v>-0.1790376237680391</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 1.891</t>
+          <t>X &lt; 1.895</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3284</v>
+        <v>3290</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.01613872734055377</v>
+        <v>-0.001463241489950917</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.09099132281568956</v>
+        <v>-0.07834294501441263</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.04808966889881106</v>
+        <v>-0.01926399435764381</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1095219325412486</v>
+        <v>-0.08064776622891401</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.1550662350448135</v>
+        <v>-0.1443705241449891</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1931066510363166</v>
+        <v>-0.1822854941018406</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1310294964442775</v>
+        <v>-0.1680231105594743</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3014075563551728</v>
+        <v>-0.3382855695775149</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2425859717536056</v>
+        <v>-0.2795556355218736</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1197845679049294</v>
+        <v>-0.1574941509718357</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1008075114583562</v>
+        <v>-0.1383847008357932</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.03203713761966753</v>
+        <v>0.02430882895257724</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.103634230255345</v>
+        <v>-0.1118535382732162</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.09452649131471702</v>
+        <v>-0.1029102910290973</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1888113009054351</v>
+        <v>-0.1974576412610531</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.2438286089398787</v>
+        <v>-0.2519892680596101</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.2687472009194423</v>
+        <v>-0.3072841097075099</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.2340940102239841</v>
+        <v>-0.2727751988451388</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2735062462133158</v>
+        <v>-0.2816377846547553</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2509124087591204</v>
+        <v>-0.2589659499007837</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2285137646413986</v>
+        <v>-0.2065996515231419</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.3471682461378265</v>
+        <v>-0.3250818024413391</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.2673255036378848</v>
+        <v>-0.2451986949588232</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2947126240286053</v>
+        <v>-0.2725797517257007</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 1.964</t>
+          <t>X &lt; 1.968</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3308</v>
+        <v>3314</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.01957228794289279</v>
+        <v>0.002331297362637486</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1192398461986741</v>
+        <v>-0.1363917582124969</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.05698777198502114</v>
+        <v>-0.02810440695738947</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.03298300536673082</v>
+        <v>-0.004148000663683149</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.08081070812678348</v>
+        <v>-0.0998424347955833</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1172037470218044</v>
+        <v>-0.136123758449628</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1212807987381908</v>
+        <v>-0.1575470745825527</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.2623527483472969</v>
+        <v>-0.2985543683218097</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2036443980707006</v>
+        <v>-0.2399368088081104</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.08730908151196104</v>
+        <v>-0.1243175817783069</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.09658807789813295</v>
+        <v>-0.1334161324905381</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.0634004549667182</v>
+        <v>0.02609349416212581</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1396708264657889</v>
+        <v>-0.1472677326503984</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1021023237504721</v>
+        <v>-0.1099117131929788</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1401794426988019</v>
+        <v>-0.1483451013901842</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1904770618182923</v>
+        <v>-0.1981737908890153</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2161699677963327</v>
+        <v>-0.2239091985142494</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1825121607248477</v>
+        <v>-0.1903825213389894</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2200576803170833</v>
+        <v>-0.2277246227017642</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1660628019323624</v>
+        <v>-0.1737103863302139</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1477383129544663</v>
+        <v>-0.1557705708071708</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2660587879033969</v>
+        <v>-0.2739288080857634</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1847776991859362</v>
+        <v>-0.1926214618357136</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2427218792648702</v>
+        <v>-0.250512552242256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 2.036</t>
+          <t>X &lt; 2.04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3326</v>
+        <v>3330</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0002862803027596783</v>
+        <v>-0.001228975007151689</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1102828779690697</v>
+        <v>-0.1111058574696315</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1158632344961958</v>
+        <v>-0.1002101249918752</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.03607222785971231</v>
+        <v>-0.02029659207993717</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.08560906266857415</v>
+        <v>-0.07051170608832535</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1507044821318715</v>
+        <v>-0.1355945562184004</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1589310116170779</v>
+        <v>-0.1606056840884449</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2708325060314749</v>
+        <v>-0.2723835471719056</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2122193191467545</v>
+        <v>-0.2138401028212797</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1006838972026785</v>
+        <v>-0.1024644349251602</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1084378519813853</v>
+        <v>-0.1102012194893689</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.01073671684815736</v>
+        <v>-0.01262723902718932</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.06896523413286815</v>
+        <v>-0.07082400435330527</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.06274863491131555</v>
+        <v>-0.06462322878994087</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.135961699366824</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.1509674727831438</v>
+        <v>-0.1527407084626944</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2072369477974974</v>
+        <v>-0.2089482391287376</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.1743254219376027</v>
+        <v>-0.1760807097762012</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2104977133628552</v>
+        <v>-0.2122036094813424</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.245870870870867</v>
+        <v>-0.2475292572757368</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2005674861983167</v>
+        <v>-0.2022991911096597</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.2886266184867168</v>
+        <v>-0.290256207561832</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.2363625644644145</v>
+        <v>-0.2380469248181782</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.294419653061297</v>
+        <v>-0.2960378602901983</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 2.109</t>
+          <t>X &lt; 2.113</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3340</v>
+        <v>3345</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.05766568910499359</v>
+        <v>0.05680658422173224</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.08306253610006564</v>
+        <v>-0.08376413756906942</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1083249655583174</v>
+        <v>-0.1090367200995459</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.002076411960132418</v>
+        <v>-0.002934673477867022</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.08268983667285568</v>
+        <v>-0.05441837757233969</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.08717341585010985</v>
+        <v>-0.0588834915715637</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.09856986591013595</v>
+        <v>-0.08722717843632921</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1813512122225518</v>
+        <v>-0.1699729454827192</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1227826984860414</v>
+        <v>-0.1114751658150865</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.04473140147856469</v>
+        <v>-0.03378869268586016</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.05129074319366822</v>
+        <v>-0.04024625683817362</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.0448537143047929</v>
+        <v>0.05566704569847047</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.01781290724303375</v>
+        <v>-0.007269345741534039</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1020843305339127</v>
+        <v>-0.09148455829188862</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1460937617693716</v>
+        <v>-0.1356402422660707</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1603562760260857</v>
+        <v>-0.1496850400816996</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2169540832397558</v>
+        <v>-0.2062394050037923</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1846224277692201</v>
+        <v>-0.1739874873085085</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2197418524216275</v>
+        <v>-0.208981340019065</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2242822966507134</v>
+        <v>-0.2433109310395167</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1814370228178745</v>
+        <v>-0.2007130109862629</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.2694397255621723</v>
+        <v>-0.2886152763163139</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2162375265331704</v>
+        <v>-0.2354090950737557</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.2743635535945685</v>
+        <v>-0.2934792478661095</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/volume/volume_ratio_12.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volume/volume_ratio_12.xlsx
@@ -618,821 +618,821 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.4008</t>
+          <t>X ≈ 0.4003</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>46.03136398195772</v>
+        <v>46.1315377633558</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>45.7138032528693</v>
+        <v>45.90228073698549</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>44.30169682802549</v>
+        <v>44.67220054152411</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>43.60702373056641</v>
+        <v>44.0978189810379</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>43.2862493317085</v>
+        <v>43.83671029851924</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>43.48765962931985</v>
+        <v>44.00813519099851</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.011038717820803</v>
+        <v>-6.515942121013154</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.290292054704494</v>
+        <v>-6.821732419410878</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.252267831039902</v>
+        <v>-6.697201420222321</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.023431686528212</v>
+        <v>-7.491497094787988</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>42.06078266292433</v>
+        <v>42.59275376911157</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>41.79740128511666</v>
+        <v>42.33170834502427</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>40.69061229311735</v>
+        <v>41.23342090144759</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>40.46994541331414</v>
+        <v>40.98569357399158</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>39.82725859664581</v>
+        <v>40.31909604748021</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>40.43420069840798</v>
+        <v>40.89315887754898</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>40.31457591814872</v>
+        <v>40.80356643160409</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>40.22361089801936</v>
+        <v>40.68461691691243</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>40.45305229777581</v>
+        <v>40.91267093532259</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>40.65291495247375</v>
+        <v>41.14023432158852</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>40.1107479859545</v>
+        <v>40.57323076347546</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>40.04866121897347</v>
+        <v>40.51175309892177</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>40.33670668981365</v>
+        <v>40.76895501479674</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>40.27453271028038</v>
+        <v>40.62046970136272</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.4737</t>
+          <t>X ≈ 0.4731</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>21.20788550289091</v>
+        <v>21.30664488989041</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>20.88197900000102</v>
+        <v>21.06910755739827</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>19.46153878638703</v>
+        <v>19.830757516141</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>18.7585107995851</v>
+        <v>19.24808730981897</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.427001151297773</v>
+        <v>-5.87884873939872</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-31.10714142362475</v>
+        <v>-30.58992841142432</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-31.88414727803816</v>
+        <v>-31.39007819424421</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.290220425448368</v>
+        <v>-6.821666933967677</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>17.63781371150303</v>
+        <v>18.19376023104393</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>16.87507930509089</v>
+        <v>17.4078263753522</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>17.15359078941741</v>
+        <v>17.68481201205029</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>16.88180325179387</v>
+        <v>17.41542830751111</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>15.76660444631677</v>
+        <v>16.30879913218322</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>15.54593840420365</v>
+        <v>16.06107282672071</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>39.82703759832359</v>
+        <v>40.3188763494114</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>40.43400516974023</v>
+        <v>40.8929648549192</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>40.31440941209355</v>
+        <v>40.80340118887685</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>40.22347258593615</v>
+        <v>40.68447975976812</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>40.45294153550925</v>
+        <v>40.91256119017238</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>40.65283067249875</v>
+        <v>41.1401507643378</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>40.11066447852135</v>
+        <v>40.57314809733629</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>40.04860572504011</v>
+        <v>40.51169806971178</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>40.33667884422364</v>
+        <v>40.7689274037313</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>40.27453271027469</v>
+        <v>40.6204697013684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.5465</t>
+          <t>X ≈ 0.5459</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-36.71168816654075</v>
+        <v>-31.09961715102942</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-20.50325689453382</v>
+        <v>-31.35472165130198</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.378139109563719</v>
+        <v>-21.57044259338755</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.089542322339732</v>
+        <v>-22.16698664315129</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-6.426881319593626</v>
+        <v>-11.40250622673588</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.242072724972992</v>
+        <v>-22.30072460905029</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.010669735937768</v>
+        <v>-12.04307530761317</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9.297470063717739</v>
+        <v>-12.35090089856627</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.252244247372381</v>
+        <v>-23.29087686897224</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.023387149467005</v>
+        <v>-13.02453640746541</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.753309308874435</v>
+        <v>-1.687852337185937</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>25.18665786675938</v>
+        <v>20.18359039035191</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>24.07430608580254</v>
+        <v>19.0779307296389</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>23.85364144550498</v>
+        <v>18.83020664967265</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>23.20529095483491</v>
+        <v>29.23726620681177</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>23.80665338179418</v>
+        <v>29.80767204977315</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>7.048778402073523</v>
+        <v>18.62581856574554</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>23.58490949195709</v>
+        <v>29.59182606565403</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>23.80876524854114</v>
+        <v>29.81622103740477</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>24.00303555497617</v>
+        <v>30.04011895634122</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>23.46087065385873</v>
+        <v>29.47311822982371</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>23.39319177725104</v>
+        <v>29.40797716894712</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>23.67564030334437</v>
+        <v>29.66151245702789</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>18.39824747913796</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.6194</t>
+          <t>X ≈ 0.6187</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-21.48540215220795</v>
+        <v>-20.06488184085125</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-25.79872713988368</v>
+        <v>-20.3163579955684</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-23.26103992205693</v>
+        <v>-21.5687402323878</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-8.076859258370192</v>
+        <v>-11.12206577763921</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4613414664112341</v>
+        <v>-4.037044317098086</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2745176157153679</v>
+        <v>-0.1977245467478497</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.020533814323436</v>
+        <v>-8.357480315572879</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.29945941939657</v>
+        <v>-4.977998548659372</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.260798505598096</v>
+        <v>-8.540253815584322</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-13.99839833492221</v>
+        <v>-16.71247981422082</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.760523932724936</v>
+        <v>-9.067471918466545</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.054002038618556</v>
+        <v>-1.963872095151295</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.175568045960908</v>
+        <v>-3.07695438058488</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.383899521426983</v>
+        <v>-7.017034191243368</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-4.053810123077959</v>
+        <v>-4.006277984260663</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.5286890892057485</v>
+        <v>0.2477968996757767</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.395672757384844</v>
+        <v>0.1446861437822591</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.2911603927543354</v>
+        <v>0.01206448178189135</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.487401296108025</v>
+        <v>-3.472154736867147</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.6934626935264561</v>
+        <v>0.4404232670149568</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>4.147183797660766</v>
+        <v>3.573343381869101</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.07570797383240091</v>
+        <v>-0.2016854191527386</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.35023400831831</v>
+        <v>3.744309308764691</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-3.725467289718722</v>
+        <v>-0.1202710393788706</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.6923</t>
+          <t>X ≈ 0.6915</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.061318434790927</v>
+        <v>-1.223986371517313</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.362894350417932</v>
+        <v>6.169871982112909</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.385076327227218</v>
+        <v>3.398421303503547</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.675536608036069</v>
+        <v>2.809718254991076</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.766018284571302</v>
+        <v>-2.053794468882593</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.687190362854068</v>
+        <v>-6.487354253533724</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.900595513788893</v>
+        <v>-5.748652940385412</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-10.3985681730273</v>
+        <v>-10.64751606552111</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.58478947832684</v>
+        <v>-1.335261521380119</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.425776701229836</v>
+        <v>5.532749595081533</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.082669334405743</v>
+        <v>-1.857578012531384</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.309424663332791</v>
+        <v>2.465346971419827</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.74666221901645</v>
+        <v>2.887507563963453</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.08369909743368</v>
+        <v>4.173556615731478</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-5.362312096666408</v>
+        <v>-4.176416389023032</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.653495963618298</v>
+        <v>-0.5480039198808697</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.2280350831683222</v>
+        <v>0.883879164424421</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.452277281478231</v>
+        <v>-2.320039109978353</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.1169753298221323</v>
+        <v>0.9662629926123714</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.491760272133547</v>
+        <v>-0.3564764785420991</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-2.033945207574796</v>
+        <v>-0.923493011929132</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-3.671665217697715</v>
+        <v>-2.536235447380228</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-4.960404739932542</v>
+        <v>-3.831434567073551</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-3.475467289719624</v>
+        <v>-2.45645337556001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.7651</t>
+          <t>X ≈ 0.7642</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.396607368644432</v>
+        <v>0.2315063601938263</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.401799138846513</v>
+        <v>-6.570539395247856</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3633504892017001</v>
+        <v>-2.195637426710348</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1622338757982789</v>
+        <v>-2.786127116932768</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.326009124826889</v>
+        <v>-0.2499887565425709</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.338065920429365</v>
+        <v>3.659236004285027</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.660908202106548</v>
+        <v>-0.8820156470622109</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.210590348325127</v>
+        <v>0.6915481081309451</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.077397505856041</v>
+        <v>2.695492868314972</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.05079890887221</v>
+        <v>5.661463088798257</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>10.98147454001249</v>
+        <v>8.753728481037854</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>10.70719574018236</v>
+        <v>8.480788557040626</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>12.3336175777335</v>
+        <v>10.1925624853287</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>11.19857215549011</v>
+        <v>9.004565263968992</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>11.4615659987042</v>
+        <v>9.268587832499314</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>6.568263916303394</v>
+        <v>6.068083157434941</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>3.691165336249455</v>
+        <v>3.143021855182951</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>5.419526474754164</v>
+        <v>5.836711207833176</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>7.469455721633146</v>
+        <v>7.937243180488437</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>4.909002043237635</v>
+        <v>5.326773799910171</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>5.283266979643834</v>
+        <v>5.702155300993255</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>5.20961649571003</v>
+        <v>5.629214310959334</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.56890768307909</v>
+        <v>4.931800344281548</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.577285003858563</v>
+        <v>3.828016871174036</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.838</t>
+          <t>X ≈ 0.837</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1064716330801403</v>
+        <v>1.460437768847136</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5708834772056974</v>
+        <v>1.485130097465728</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.154992935873878</v>
+        <v>2.015702757280735</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.06626860472862006</v>
+        <v>0.9255459089971154</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.431018687178501</v>
+        <v>-1.357462561722251</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.259627051262285</v>
+        <v>-2.707079379380076</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.531178638029871</v>
+        <v>-1.487517271884123</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.010820852029127</v>
+        <v>-1.289399085301994</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.07639445009262147</v>
+        <v>1.347738841615211</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.121272930740801</v>
+        <v>1.561223550904472</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>5.458193032199773</v>
+        <v>5.855733568611228</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.608440593264433</v>
+        <v>1.557408360629744</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.013208509104039</v>
+        <v>2.962203397415976</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7927717928730686</v>
+        <v>2.211446582527017</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.171988978877565</v>
+        <v>4.050084255275564</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.748929092891231</v>
+        <v>3.10121874605872</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.161855638074798</v>
+        <v>5.015122026838519</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.01467767292185584</v>
+        <v>0.8519076841780659</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.83657127289316</v>
+        <v>-0.4462281827563004</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.141431151257613</v>
+        <v>0.2719781258674558</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.6643849447735448</v>
+        <v>0.2094591821393834</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>1.808904762431588</v>
+        <v>2.657920598175409</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.9758220346471234</v>
+        <v>-0.6313201594741145</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>2.009226587831279</v>
+        <v>1.73158081247383</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 0.9109</t>
+          <t>X ≈ 0.9098</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4728445876741816</v>
+        <v>0.005001428170928079</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.801834144114387</v>
+        <v>2.040623603723112</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.273031823000103</v>
+        <v>1.702618361025088</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.919297851539319</v>
+        <v>2.379723040758826</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.58469746367669</v>
+        <v>1.877108972119736</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.093058068137054</v>
+        <v>1.122114269316953</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.135248801858026</v>
+        <v>1.931181674568272</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.9508006888056997</v>
+        <v>0.4854149738858311</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7656091610774425</v>
+        <v>0.3822110761626405</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.579843314754264</v>
+        <v>0.9607629260288846</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.210212453409888</v>
+        <v>2.147116814533298</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.748390787043689</v>
+        <v>3.475139402485254</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.30885791038893</v>
+        <v>2.591928831640381</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.180368308918368</v>
+        <v>1.657022279686295</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>4.607643754949372</v>
+        <v>3.955317040885895</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>3.614409234596387</v>
+        <v>3.143326402095539</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.937484618626243</v>
+        <v>3.729236723361389</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>4.517540903479954</v>
+        <v>4.286448575844837</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>5.190369856006491</v>
+        <v>4.732488443267549</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>3.786531863801315</v>
+        <v>3.112674163193198</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>3.471843448698472</v>
+        <v>3.004038473070722</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.715210904058246</v>
+        <v>2.241163593891628</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.308248441620989</v>
+        <v>2.025890255496776</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.777949566772406</v>
+        <v>1.540009931247724</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.9837</t>
+          <t>X ≈ 0.9826</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.728176794587576</v>
+        <v>0.6339708829521769</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.5858144056335135</v>
+        <v>-0.9771961805579252</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.141772531373462</v>
+        <v>1.859038337672239</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.6400375213028724</v>
+        <v>0.8745153395968899</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.873226339607079</v>
+        <v>-1.634718571551119</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.091345077234187</v>
+        <v>-1.088968519246684</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.065751933446109</v>
+        <v>-0.9125084563541606</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.135217940143562</v>
+        <v>-1.693681864372302</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.900008236952409</v>
+        <v>-1.062553869901585</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.6856804276836073</v>
+        <v>0.09521701646495728</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.789286977777152</v>
+        <v>-3.236206203413062</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.884200752449416</v>
+        <v>-1.362233008542319</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.006412782942071</v>
+        <v>-2.281706402603831</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.027751705703693</v>
+        <v>-2.334305211752543</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-3.288094302913763</v>
+        <v>-2.821340957949637</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1935873489918265</v>
+        <v>-0.104833839140106</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.121359914818242</v>
+        <v>-0.9928090914028331</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.6278649732128301</v>
+        <v>-0.7342017707154653</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.6109956271477444</v>
+        <v>-0.7158912662748449</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.4246412070478129</v>
+        <v>-0.3034550308218869</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.2287114256754421</v>
+        <v>0.5028688770326823</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.643316752307264</v>
+        <v>-0.4402774912490059</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.7672477672197004</v>
+        <v>-0.6712223456052371</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.442034155987095</v>
+        <v>-1.226288648342546</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 1.056</t>
+          <t>X ≈ 1.055</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.521388988546448</v>
+        <v>-3.434510490962083</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2044686868564227</v>
+        <v>-0.4741205719821053</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.48347348158169</v>
+        <v>-2.717966469477126</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4576144014328278</v>
+        <v>0.387836642823153</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3668095920940999</v>
+        <v>-0.1377402956819935</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.42218266605758</v>
+        <v>-0.4758296968394333</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2194000610618687</v>
+        <v>-0.5368365241767918</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.432221116465783</v>
+        <v>1.871596479874356</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.499580137342086</v>
+        <v>0.7713885654356503</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.459502168452467</v>
+        <v>0.8564037789555741</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.0005789547265</v>
+        <v>0.3878867416416156</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.233426572483651</v>
+        <v>-1.617942912477389</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.870223215471356</v>
+        <v>-2.489962074017022</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.603534904119485</v>
+        <v>-1.750837904366897</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.527285758244062</v>
+        <v>-1.794818265089084</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.4398975669640848</v>
+        <v>-0.8423773427256904</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.280752628338952</v>
+        <v>1.177123611831377</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.318762557127783</v>
+        <v>1.542386085225857</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.781800053537765</v>
+        <v>2.50277597145854</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.48071998926428</v>
+        <v>1.975625898722257</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.2023046643764417</v>
+        <v>0.911903481708741</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.7603681162318239</v>
+        <v>1.333018875386237</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.7915879782979687</v>
+        <v>1.328514402848178</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.453893889641556</v>
+        <v>1.910792282007876</v>
       </c>
     </row>
     <row r="16">
@@ -1442,1145 +1442,1145 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6998986324825651</v>
+        <v>0.7025747732312553</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.246394158856532</v>
+        <v>2.662912459561369</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.317437671765511</v>
+        <v>2.515117920709692</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.09864765712460155</v>
+        <v>0.8175429255006676</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.235972621173218</v>
+        <v>0.5450066270196317</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.839434389142546</v>
+        <v>1.808465570571947</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.957115312298498</v>
+        <v>2.859333498993344</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.347245527744164</v>
+        <v>-0.02710956491284833</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.8329418671494651</v>
+        <v>1.944160073897102</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.05975153996117655</v>
+        <v>1.148108578677764</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4233952785054171</v>
+        <v>0.6827283408989189</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6497088182563573</v>
+        <v>1.145876637091881</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.4724030202975626</v>
+        <v>0.7705768738862133</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6937729019414363</v>
+        <v>-0.2174817193876351</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-3.625868119120952</v>
+        <v>-2.747442865094804</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-3.788769991295311</v>
+        <v>-2.184449264413161</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-3.543727475583751</v>
+        <v>-1.918742329806655</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-3.269802530180762</v>
+        <v>-1.470485563440882</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-5.331564794520361</v>
+        <v>-3.845686205100129</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-7.04626824304124</v>
+        <v>-5.485085432956893</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-7.969318321989505</v>
+        <v>-6.422900304707916</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-6.527248481092208</v>
+        <v>-5.757322085922532</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.838909805371138</v>
+        <v>-1.809983896940366</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-5.35284371557514</v>
+        <v>-4.564715483822425</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 1.203</t>
+          <t>X ≈ 1.201</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.037925989858167</v>
+        <v>3.209288387044218</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.786299723020242</v>
+        <v>-6.070755841128054</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.95995744640642</v>
+        <v>2.842386038833247</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1179104116508043</v>
+        <v>1.120797237154115</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.488373823070852</v>
+        <v>1.966690865902279</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.109972190242487</v>
+        <v>2.124330957183275</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9074054540554144</v>
+        <v>2.455291489061572</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.470816568428482</v>
+        <v>4.407979183583244</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.561310345505241</v>
+        <v>1.155025454617245</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.767931266613758</v>
+        <v>4.325916108158218</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.632564009204181</v>
+        <v>1.196071805838571</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.9204469773095312</v>
+        <v>-0.4618636240984557</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.746266566633793</v>
+        <v>-3.282814046241576</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.688120643112498</v>
+        <v>-1.264512871301292</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-4.052094023922621</v>
+        <v>-3.650845621822882</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-5.17071421870186</v>
+        <v>-4.785859646984612</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-5.304631355679334</v>
+        <v>-5.456720646831826</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-3.700264548745011</v>
+        <v>-4.456105947787471</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.776035225751407</v>
+        <v>-2.213575544065172</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-3.302391893585387</v>
+        <v>-3.704782402653812</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.703023046132856</v>
+        <v>-3.135863267670977</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-3.919935623466195</v>
+        <v>-4.347389425989832</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-4.792492179353424</v>
+        <v>-5.240118577075094</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-4.296895861148194</v>
+        <v>-4.265893935000989</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 1.276</t>
+          <t>X ≈ 1.274</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.406373507207483</v>
+        <v>1.907137258040294</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>5.70175399173894</v>
+        <v>4.372806841158749</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5669614988876575</v>
+        <v>-0.5025403580853975</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7820950455455389</v>
+        <v>-0.1913446442322666</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4314118228879735</v>
+        <v>-0.4575106142707668</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.104004996053447</v>
+        <v>-3.918717777734258</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.485508947820584</v>
+        <v>3.440824942949547</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.4681735740049504</v>
+        <v>-0.4870785779876599</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.254793626457939</v>
+        <v>-3.084061120487767</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.878861160370782</v>
+        <v>-5.695539612952238</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.8943155328317474</v>
+        <v>-1.794811878946149</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.97433953196763</v>
+        <v>-3.883278918029738</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.3996181595165</v>
+        <v>-1.368186226015844</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.692060249544177</v>
+        <v>-1.6158283040877</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-5.098553544820206</v>
+        <v>-5.019735616873476</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-6.347919054906924</v>
+        <v>-6.275827692865057</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-8.34812385859415</v>
+        <v>-8.195130921530335</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.722642752463834</v>
+        <v>-4.696972065024283</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-3.028855688517538</v>
+        <v>-4.48231251009139</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.914155959553433</v>
+        <v>-3.363873311744726</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.524588597077823</v>
+        <v>-2.11313599494364</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.605366376108371</v>
+        <v>-2.188298516898925</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>4.83634627191492</v>
+        <v>3.509881422924913</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.825934579439249</v>
+        <v>1.529560610453629</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 1.349</t>
+          <t>X ≈ 1.347</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.532175134422815</v>
+        <v>-5.314794750114494</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.759774454002667</v>
+        <v>-5.562890823525741</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.627392039877456</v>
+        <v>-2.309446931793943</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-7.026997612847929</v>
+        <v>-6.512956924686478</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-9.169502299800556</v>
+        <v>-6.775379638541239</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.999610875639284</v>
+        <v>-1.199364762962198</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.88149243932294</v>
+        <v>-1.092036135366094</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.358893059984027</v>
+        <v>0.420123311032448</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.812061903065619</v>
+        <v>-5.799055217299987</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.894534394459392</v>
+        <v>-3.880506161555182</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.925495545972638</v>
+        <v>-0.8887119183007002</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.184579457808724</v>
+        <v>3.365835603812044</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2731523640572391</v>
+        <v>0.4469662985820904</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.645339747437077</v>
+        <v>-1.615308566418904</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.09504143952838</v>
+        <v>2.242476107419122</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.01054503742676616</v>
+        <v>0.07926388745601542</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.043125815003307</v>
+        <v>-0.9314987247157163</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.048052472673966</v>
+        <v>-1.972647043696426</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.630626223548049</v>
+        <v>-2.665343419671814</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-3.449861763747464</v>
+        <v>-2.454782402653819</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.3888043281097922</v>
+        <v>-0.29495417676182</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.167352992221595</v>
+        <v>-3.097389425989839</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.892878279739591</v>
+        <v>-2.853754940711461</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.968710532962866</v>
+        <v>-2.106803025910011</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 1.421</t>
+          <t>X ≈ 1.419</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.859982708173234</v>
+        <v>-2.077801938371493</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>6.835639380720643</v>
+        <v>6.173580814680932</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3500689041878076</v>
+        <v>-2.178224186414276</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.055754892382716</v>
+        <v>0.06731593585175233</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>8.705295706701847</v>
+        <v>6.89337888799222</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.13192852882581</v>
+        <v>1.385368621225268</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.363941108057702</v>
+        <v>0.5902739787620632</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.091995523763877</v>
+        <v>0.2914141414140587</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.571134442797508</v>
+        <v>4.683412315167445</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.679004868901075</v>
+        <v>6.726538309125687</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>8.840116473662242</v>
+        <v>9.844768994725698</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>5.675098340172454</v>
+        <v>6.722191369258724</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.12591023776352</v>
+        <v>4.204463933489514</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.352602403844784</v>
+        <v>5.383720247149363</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>8.035020012411785</v>
+        <v>8.980234289865102</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>4.288846028207217</v>
+        <v>5.262869884083969</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>5.602306759266654</v>
+        <v>6.585719307316303</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>4.050481361899429</v>
+        <v>5.026485637265168</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>5.713357436369797</v>
+        <v>6.667297429300476</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>5.911673684744628</v>
+        <v>6.895866947995614</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>3.919852154459598</v>
+        <v>4.899851018043378</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>5.29328155536934</v>
+        <v>4.824688496088093</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>5.567756267851394</v>
+        <v>5.068322981366542</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>7.763326844219939</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 1.494</t>
+          <t>X ≈ 1.492</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>7.619747089588778</v>
+        <v>6.971207979725634</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.733498408952457</v>
+        <v>-0.7104145460062981</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.094516156737576</v>
+        <v>4.242220539506981</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.638235397783191</v>
+        <v>-3.795093756651163</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.306473588606764</v>
+        <v>2.125437237260975</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.809811430537337</v>
+        <v>-4.464612080294948</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.067434402036113</v>
+        <v>-2.786836410848252</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.362721975674475</v>
+        <v>-3.083423520923468</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.829345954980333</v>
+        <v>-5.451327944572739</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.583050986020844</v>
+        <v>-6.257796106458812</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-11.61982505301305</v>
+        <v>-12.20535275852106</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-8.115062553523494</v>
+        <v>-8.749643046325779</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.745473287887876</v>
+        <v>-6.130879227223147</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.439740020465486</v>
+        <v>-2.636418869937309</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.834206437150961</v>
+        <v>-2.070659626422696</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-6.291277331261931</v>
+        <v>-6.49787073676206</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.636330297238366</v>
+        <v>-2.860103187247816</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-5.266899909086561</v>
+        <v>-5.487244856988916</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.262685975082299</v>
+        <v>-1.531657897343869</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.077869518337451</v>
+        <v>-1.31841876629025</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.620415686303446</v>
+        <v>-3.135863267670878</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.227907217332756</v>
+        <v>-4.461025789626191</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.953432504850781</v>
+        <v>-4.217391304347863</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.763441973263923</v>
+        <v>-4.379530298637356</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 1.567</t>
+          <t>X ≈ 1.565</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>73</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>7.932249763530216</v>
+        <v>5.945691143374667</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8238078519370049</v>
+        <v>0.2575856904356471</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.989071588246532</v>
+        <v>-3.703247842736111</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.10116979665095</v>
+        <v>2.498683298997307</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.783155263917934</v>
+        <v>3.580869836206006</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.261831687388444</v>
+        <v>2.357618948890007</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.244688153008752</v>
+        <v>-1.158169085862951</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-6.613208371247623</v>
+        <v>-5.581250719287517</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-5.210950574564094</v>
+        <v>-5.437438121898545</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.356632259138181</v>
+        <v>-7.572677784190773</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.348236300751829</v>
+        <v>-4.579709934894403</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.262216624841365</v>
+        <v>-4.850997326797447</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.449662405945595</v>
+        <v>0.8427087593875484</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.229383222417006</v>
+        <v>0.5910414573186529</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.890235471351154</v>
+        <v>-5.573998219996788</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.928680391295906</v>
+        <v>-3.649697668750186</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.428965993467713</v>
+        <v>-5.120007853537999</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.5636993124581977</v>
+        <v>-1.146736158239534</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.7779913075466425</v>
+        <v>0.4444555638765593</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.511197071658067</v>
+        <v>-4.023898218344975</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-5.053743239624133</v>
+        <v>-4.591342719725745</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.020000159937304</v>
+        <v>-0.5569162005850998</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.115388461153884</v>
+        <v>-1.683144729005392</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8213577006785258</v>
+        <v>-0.475420709596186</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 1.639</t>
+          <t>X ≈ 1.637</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>5.854354410755036</v>
+        <v>6.254670829489825</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.519380993851193</v>
+        <v>6.003740351074889</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.2832813351453751</v>
+        <v>1.078042452942853</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.522665030377162</v>
+        <v>1.710145459999922</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.476542934991258</v>
+        <v>2.661604347121518</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>6.506285662728835</v>
+        <v>6.479494463937762</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.753114727124611</v>
+        <v>5.709241185152678</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>9.319406182533285</v>
+        <v>9.06636724632628</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.244861878406496</v>
+        <v>4.278746659683776</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.18480867256541</v>
+        <v>2.282210426147458</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.461469805381498</v>
+        <v>2.546871404547858</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.180118911279337</v>
+        <v>2.277863486280495</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.06215982573157</v>
+        <v>1.852208663384005</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8423816946120297</v>
+        <v>1.603974601950895</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.085989443521171</v>
+        <v>-0.3127476811687373</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.7864297909368645</v>
+        <v>1.483124238885502</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.6525126539593913</v>
+        <v>1.379243827160494</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.5450704594840445</v>
+        <v>1.246359721998893</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-4.348565918997728</v>
+        <v>-4.712017557028176</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>3.514795200909546</v>
+        <v>2.909976295438177</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.690197750892239</v>
+        <v>1.10796389282288</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.231802056670716</v>
+        <v>-1.436334431601502</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.170877784016469</v>
+        <v>2.511003757380536</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>5.659148094895762</v>
+        <v>6.052568466794817</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 1.712</t>
+          <t>X ≈ 1.711</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>50</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.592871676855438</v>
+        <v>-3.526928140983408</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.945943108353134</v>
+        <v>-1.77890509704315</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.472495336379041</v>
+        <v>2.927258990494913</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.109709626580532</v>
+        <v>-3.632280832593842</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-12.3654521910948</v>
+        <v>-11.8668133316675</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2690507432894336</v>
+        <v>-1.744416617349202</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.933946987989088</v>
+        <v>1.450663589151752</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.662643931061631</v>
+        <v>5.145743145743225</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.708084970159568</v>
+        <v>1.273672055427333</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.06956664470074259</v>
+        <v>-1.522379439792083</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.177424282899203</v>
+        <v>4.749855574812244</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.883858777259249</v>
+        <v>6.473273620340919</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.188728676835943</v>
+        <v>-2.641618497109818</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.571422487342211</v>
+        <v>1.110147441457066</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.905371475395306</v>
+        <v>4.427993059572039</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>6.499758397338297</v>
+        <v>4.989297078391701</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.376312464549294</v>
+        <v>2.885416666666629</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.2775980669131</v>
+        <v>0.7525325615050917</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.487363141652438</v>
+        <v>2.966994788650801</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>-0.8184187662901294</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>-1.385863267670864</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.075890251021598</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.649635036496356</v>
+        <v>-3.217391304347757</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.725467289719631</v>
+        <v>-3.379530298637277</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 1.786</t>
+          <t>X ≈ 1.784</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.452034732739293</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.325671634716052</v>
+        <v>2.608573602523478</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-6.656143642568971</v>
+        <v>-1.216797685429924</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.931819232778011</v>
+        <v>-1.796050640319635</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3581173093149559</v>
+        <v>3.036872481908439</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1901218737693995</v>
+        <v>0.6560020116408865</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.934804505569552</v>
+        <v>-5.267285128796964</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-6.304638986971852</v>
+        <v>-8.136308136308173</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.236973794585964</v>
+        <v>-2.880174098418905</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-9.431355439208879</v>
+        <v>-6.240328157740812</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-9.144206791811342</v>
+        <v>-8.53219570723904</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-9.383689179552533</v>
+        <v>-8.808777661710295</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6115632882934605</v>
+        <v>2.896843041351715</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.319553159504395</v>
+        <v>0.08450641581604401</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-4.030052478027407</v>
+        <v>-0.5976479660690472</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.564334443915619</v>
+        <v>5.091861180955732</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.082671698297467</v>
+        <v>2.42387820512824</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.174423396883071</v>
+        <v>2.290994099966561</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.9716210211943235</v>
+        <v>2.505456327112412</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>5.694282380396729</v>
+        <v>5.284145336273923</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>2.152598270790627</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>7.575890251021598</v>
+        <v>9.769743441143028</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.350364963503651</v>
+        <v>7.449275362318893</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.774532710280376</v>
+        <v>4.723033803926818</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 1.859</t>
+          <t>X ≈ 1.856</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>12.83283709709431</v>
+        <v>8.461592240539538</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.209171409855614</v>
+        <v>1.373437237580653</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-10.8592569959005</v>
+        <v>-17.01716195840224</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.241216863296479</v>
+        <v>-10.7471262059862</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.580073607233281</v>
+        <v>-11.01258945410088</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.7085908173712454</v>
+        <v>-3.993217896878434</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.195518098743911</v>
+        <v>-4.825198479813757</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.77002583979322</v>
+        <v>-1.681843061153415</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.728538657878573</v>
+        <v>-1.55391415146935</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-9.908861741322418</v>
+        <v>-12.69479323289548</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-9.634802099160495</v>
+        <v>-8.97428235622224</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.506144095201194</v>
+        <v>-2.35431258655565</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-11.03671356946461</v>
+        <v>-13.81403229021322</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-11.2577924459112</v>
+        <v>-14.06226635164633</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-11.91593574349181</v>
+        <v>-14.74442073353143</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-22.43265993265993</v>
+        <v>-24.52794430091867</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-22.56657706963745</v>
+        <v>-24.63182471264368</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-22.67141777345859</v>
+        <v>-24.76470881780528</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-18.75182268883056</v>
+        <v>-21.10197072859054</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-18.56497687886247</v>
+        <v>-17.43910842146259</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-11.70011563942116</v>
+        <v>-14.55827706077436</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-11.7759616008302</v>
+        <v>-14.63343958272969</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-11.50148688834815</v>
+        <v>-14.38980509745132</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-11.57731914157148</v>
+        <v>-11.10366822967177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 1.931</t>
+          <t>X ≈ 1.929</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4829152628056619</v>
+        <v>2.93533129469504</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-7.988495198910556</v>
+        <v>-1.601453269921429</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.274039000416728</v>
+        <v>1.442301526088109</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.29716539598213</v>
+        <v>13.78310186592583</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.977128676229491</v>
+        <v>13.52268606380342</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.172159378455873</v>
+        <v>13.6947620077784</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.285963382737577</v>
+        <v>4.320228806543092</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.174418604651109</v>
+        <v>8.363134450090968</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.21590578656587</v>
+        <v>8.491063359775104</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.442990110529323</v>
+        <v>7.69501186455571</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>3.619420792203577</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2716336825766632</v>
+        <v>3.342838837732309</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-5.018195050946204</v>
+        <v>-6.467705453631602</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.07260726072613</v>
+        <v>-2.368113428108209</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>5.645384363919867</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.196969696969632</v>
+        <v>6.2066883827395</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>11.22971922665896</v>
+        <v>10.45063405797101</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>11.12487852283772</v>
+        <v>10.31774995280941</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>6.184386092998665</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>11.52761571373</v>
+        <v>10.74679862501419</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>10.17935412363346</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.742556917688198</v>
+        <v>10.10419160167815</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>7.017031630170251</v>
+        <v>10.34782608695652</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.774532710280376</v>
+        <v>5.837861005710572</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 2.004</t>
+          <t>X ≈ 2.002</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.6270859158836615</v>
+        <v>-0.9306953158695919</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.016302066530393</v>
+        <v>-1.142665499989725</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-14.8004298537878</v>
+        <v>-12.82246081645619</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.112835782707208</v>
+        <v>-3.023698452273266</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.948326832911555</v>
+        <v>-3.27663215798345</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.02839745718151931</v>
+        <v>-3.097074117596215</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7973699505957157</v>
+        <v>-9.180915358216701</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.174418604651166</v>
+        <v>-4.222677906888443</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.21590578656587</v>
+        <v>-4.09474899720437</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.442990110529337</v>
+        <v>-4.890800492423708</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.71704975269126</v>
+        <v>-4.618565477819374</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-8.061699650756651</v>
+        <v>-15.42146322176435</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>15.81513828238715</v>
+        <v>9.779434134469078</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.344059405940556</v>
+        <v>4.268042178299169</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2.43591610836004</v>
+        <v>-1.677270098322772</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>9.280303030303031</v>
+        <v>4.147191815233775</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>2.896385893325558</v>
+        <v>-1.219846491228068</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.791545189504376</v>
+        <v>-1.352730596389641</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.007436570428702</v>
+        <v>-1.138268369243896</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-15.55571761960323</v>
+        <v>-16.71315560839547</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-9.848263787569302</v>
+        <v>-12.01744221503937</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-3.674109748978445</v>
+        <v>-6.829446842257703</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-9.649635036496306</v>
+        <v>-11.84897025171625</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-9.725467289719667</v>
+        <v>-12.01110924600574</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 2.077</t>
+          <t>X ≈ 2.075</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>12.80152693763777</v>
+        <v>14.27249932230961</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.948461664477719</v>
+        <v>6.631634503412386</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.059605693732017</v>
+        <v>-1.765916741336291</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.745728761635419</v>
+        <v>5.036639043048737</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.444444845333862</v>
+        <v>-2.549843466798549</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>16.8060142060344</v>
+        <v>11.72473719802313</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16.28596338273757</v>
+        <v>14.87923501772319</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>22.67441860465111</v>
+        <v>21.71717171717171</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>22.71590578656587</v>
+        <v>21.84510062685582</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15.27632344386271</v>
+        <v>13.90619198877928</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>15.55038308602463</v>
+        <v>14.17842700338362</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>15.27163368257663</v>
+        <v>13.90184504891242</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>14.14847161572052</v>
+        <v>12.78695293146155</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.072607260726024</v>
+        <v>-8.889852558542877</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>-2.429149797570851</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>-1.867845778751189</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.396385893325558</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.2915451895043759</v>
+        <v>-2.104610295637841</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>-1.890148068492024</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.6942823803966789</v>
+        <v>5.467295519424113</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>4.899851018043378</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.07589025102159752</v>
+        <v>4.824688496088093</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.3503649635036012</v>
+        <v>5.068322981366471</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>4.906183987077007</v>
       </c>
     </row>
   </sheetData>
@@ -2774,2457 +2774,2457 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2948</v>
+        <v>2972</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.04726336147541588</v>
+        <v>0.04908727122116829</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.03357539426156819</v>
+        <v>-0.01179559590003265</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1643819802050928</v>
+        <v>0.1891360922344347</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.009613404100520029</v>
+        <v>0.1168784966897434</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2735173010321361</v>
+        <v>-0.2069390919337835</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.09829723663425938</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1244154020873296</v>
+        <v>0.0961272650807885</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1355934864877639</v>
+        <v>0.07809411694206858</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.03991994798326459</v>
+        <v>-0.04291085914561421</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2200171375564111</v>
+        <v>0.1518832947923556</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2096148084533809</v>
+        <v>0.1752662352212297</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2885369956259964</v>
+        <v>0.2868215747339775</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.0708948593104779</v>
+        <v>-0.003577571246026423</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1567015003833845</v>
+        <v>-0.08408268266235552</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1858700892042364</v>
+        <v>-0.1089196921058431</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.01115213044146657</v>
+        <v>0.1030936544239012</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.1458781072727433</v>
+        <v>0.2877000783523584</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.1967263611941803</v>
+        <v>0.3427240294257885</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.3990354864178656</v>
+        <v>0.5772098424142769</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.03010074705209576</v>
+        <v>0.2067913177434306</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1396904226082754</v>
+        <v>0.07632160627866114</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.05970296931738517</v>
+        <v>0.08840258966095149</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.09943244400551521</v>
+        <v>0.2175229237046494</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.04386785274984817</v>
+        <v>0.1763243447005394</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.07287</t>
+          <t>X &gt; 0.07279</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2948</v>
+        <v>2972</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.04726336147541588</v>
+        <v>0.04908727122116829</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.03357539426156819</v>
+        <v>-0.01179559590003265</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1643819802050928</v>
+        <v>0.1891360922344347</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.009613404100520029</v>
+        <v>0.1168784966897434</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2735173010321361</v>
+        <v>-0.2069390919337835</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.09829723663425938</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1244154020873296</v>
+        <v>0.0961272650807885</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1355934864877639</v>
+        <v>0.07809411694206858</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.03991994798326459</v>
+        <v>-0.04291085914561421</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2200171375564111</v>
+        <v>0.1518832947923556</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2096148084533809</v>
+        <v>0.1752662352212297</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2885369956259964</v>
+        <v>0.2868215747339775</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.0708948593104779</v>
+        <v>-0.003577571246026423</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1567015003833845</v>
+        <v>-0.08408268266235552</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1858700892042364</v>
+        <v>-0.1089196921058431</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.01115213044146657</v>
+        <v>0.1030936544239012</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.1458781072727433</v>
+        <v>0.2877000783523584</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.1967263611941803</v>
+        <v>0.3427240294257885</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.3990354864178656</v>
+        <v>0.5772098424142769</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.03010074705209576</v>
+        <v>0.2067913177434306</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1396904226082754</v>
+        <v>0.07632160627866114</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.05970296931738517</v>
+        <v>0.08840258966095149</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.09943244400551521</v>
+        <v>0.2175229237046494</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.04386785274984817</v>
+        <v>0.1763243447005394</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.1457</t>
+          <t>X &gt; 0.1456</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2948</v>
+        <v>2972</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.04726336147541588</v>
+        <v>0.04908727122116829</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.03357539426156819</v>
+        <v>-0.01179559590003265</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1643819802050928</v>
+        <v>0.1891360922344347</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.009613404100520029</v>
+        <v>0.1168784966897434</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2735173010321361</v>
+        <v>-0.2069390919337835</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.09829723663425938</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1244154020873296</v>
+        <v>0.0961272650807885</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1355934864877639</v>
+        <v>0.07809411694206858</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.03991994798326459</v>
+        <v>-0.04291085914561421</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2200171375564111</v>
+        <v>0.1518832947923556</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2096148084533809</v>
+        <v>0.1752662352212297</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2885369956259964</v>
+        <v>0.2868215747339775</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.0708948593104779</v>
+        <v>-0.003577571246026423</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1567015003833845</v>
+        <v>-0.08408268266235552</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.1858700892042364</v>
+        <v>-0.1089196921058431</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.01115213044146657</v>
+        <v>0.1030936544239012</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1458781072727433</v>
+        <v>0.2877000783523584</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.1967263611941803</v>
+        <v>0.3427240294257885</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.3990354864178656</v>
+        <v>0.5772098424142769</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.03010074705209576</v>
+        <v>0.2067913177434306</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1396904226082754</v>
+        <v>0.07632160627866114</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.05970296931738517</v>
+        <v>0.08840258966095149</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.09943244400551521</v>
+        <v>0.2175229237046494</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.04386785274984817</v>
+        <v>0.1763243447005394</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.2186</t>
+          <t>X &gt; 0.2184</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2948</v>
+        <v>2972</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.04726336147541588</v>
+        <v>0.04908727122116829</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.03357539426156819</v>
+        <v>-0.01179559590003265</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1643819802050928</v>
+        <v>0.1891360922344347</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.009613404100520029</v>
+        <v>0.1168784966897434</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2735173010321361</v>
+        <v>-0.2069390919337835</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.09829723663425938</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1244154020873296</v>
+        <v>0.0961272650807885</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1355934864877639</v>
+        <v>0.07809411694206858</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.03991994798326459</v>
+        <v>-0.04291085914561421</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2200171375564111</v>
+        <v>0.1518832947923556</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2096148084533809</v>
+        <v>0.1752662352212297</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2885369956259964</v>
+        <v>0.2868215747339775</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.0708948593104779</v>
+        <v>-0.003577571246026423</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1567015003833845</v>
+        <v>-0.08408268266235552</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.1858700892042364</v>
+        <v>-0.1089196921058431</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.01115213044146657</v>
+        <v>0.1030936544239012</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.1458781072727433</v>
+        <v>0.2877000783523584</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.1967263611941803</v>
+        <v>0.3427240294257885</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.3990354864178656</v>
+        <v>0.5772098424142769</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.03010074705209576</v>
+        <v>0.2067913177434306</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1396904226082754</v>
+        <v>0.07632160627866114</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.05970296931738517</v>
+        <v>0.08840258966095149</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.09943244400551521</v>
+        <v>0.2175229237046494</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.04386785274984817</v>
+        <v>0.1763243447005394</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.2915</t>
+          <t>X &gt; 0.2911</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2948</v>
+        <v>2972</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.04726336147541588</v>
+        <v>0.04908727122116829</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.03357539426156819</v>
+        <v>-0.01179559590003265</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1643819802050928</v>
+        <v>0.1891360922344347</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.009613404100520029</v>
+        <v>0.1168784966897434</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2735173010321361</v>
+        <v>-0.2069390919337835</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.09829723663425938</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1244154020873296</v>
+        <v>0.0961272650807885</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1355934864877639</v>
+        <v>0.07809411694206858</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.03991994798326459</v>
+        <v>-0.04291085914561421</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2200171375564111</v>
+        <v>0.1518832947923556</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2096148084533809</v>
+        <v>0.1752662352212297</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2885369956259964</v>
+        <v>0.2868215747339775</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.0708948593104779</v>
+        <v>-0.003577571246026423</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1567015003833845</v>
+        <v>-0.08408268266235552</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.1858700892042364</v>
+        <v>-0.1089196921058431</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.01115213044146657</v>
+        <v>0.1030936544239012</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.1458781072727433</v>
+        <v>0.2877000783523584</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.1967263611941803</v>
+        <v>0.3427240294257885</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.3990354864178656</v>
+        <v>0.5772098424142769</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.03010074705209576</v>
+        <v>0.2067913177434306</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.1396904226082754</v>
+        <v>0.07632160627866114</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.05970296931738517</v>
+        <v>0.08840258966095149</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.09943244400551521</v>
+        <v>0.2175229237046494</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.04386785274984817</v>
+        <v>0.1763243447005394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.3644</t>
+          <t>X &gt; 0.3639</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2948</v>
+        <v>2972</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.04726336147541588</v>
+        <v>0.04908727122116829</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.03357539426156819</v>
+        <v>-0.01179559590003265</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1643819802050928</v>
+        <v>0.1891360922344347</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.009613404100520029</v>
+        <v>0.1168784966897434</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2735173010321361</v>
+        <v>-0.2069390919337835</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.09829723663425938</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1244154020873296</v>
+        <v>0.0961272650807885</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1355934864877639</v>
+        <v>0.07809411694206858</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.03991994798326459</v>
+        <v>-0.04291085914561421</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2200171375564111</v>
+        <v>0.1518832947923556</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2096148084533809</v>
+        <v>0.1752662352212297</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2885369956259964</v>
+        <v>0.2868215747339775</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.0708948593104779</v>
+        <v>-0.003577571246026423</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1567015003833845</v>
+        <v>-0.08408268266235552</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1858700892042364</v>
+        <v>-0.1089196921058431</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.01115213044146657</v>
+        <v>0.1030936544239012</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.1458781072727433</v>
+        <v>0.2877000783523584</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.1967263611941803</v>
+        <v>0.3427240294257885</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.3990354864178656</v>
+        <v>0.5772098424142769</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.03010074705209576</v>
+        <v>0.2067913177434306</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.1396904226082754</v>
+        <v>0.07632160627866114</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.05970296931738517</v>
+        <v>0.08840258966095149</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.09943244400551521</v>
+        <v>0.2175229237046494</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.04386785274984817</v>
+        <v>0.1763243447005394</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.4372</t>
+          <t>X &gt; 0.4367</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2946</v>
+        <v>2970</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.01604537055859367</v>
+        <v>0.01805531802781957</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.06463267779661663</v>
+        <v>-0.04271416582115961</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1344177474502999</v>
+        <v>0.1591811666793603</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.01998429469546181</v>
+        <v>0.08726170175079062</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.30308944402789</v>
+        <v>-0.2365981150923417</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1646852775089158</v>
+        <v>-0.1279985379323278</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1292595664592895</v>
+        <v>0.1005798370579569</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1406348208673833</v>
+        <v>0.08274046477799146</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.03502358146387508</v>
+        <v>-0.03842985540077848</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2256135047146444</v>
+        <v>0.1570303522937522</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1812026103172784</v>
+        <v>0.1467022705519341</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2603571828021742</v>
+        <v>0.2585085196698103</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.09856730136915814</v>
+        <v>-0.03134659378655869</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1842823876296151</v>
+        <v>-0.111739097650009</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.213034467130818</v>
+        <v>-0.1361439451291275</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.0386099395581283</v>
+        <v>0.07562559703460181</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.1186081155477794</v>
+        <v>0.2604166666666643</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1695526446043445</v>
+        <v>0.3155577715890914</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.3718433500897191</v>
+        <v>0.550047915752387</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.002522461780252172</v>
+        <v>0.1792267096600426</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.1670159069318018</v>
+        <v>0.04905096038155676</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.08693200135288492</v>
+        <v>0.06118147820690467</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.07211589665601537</v>
+        <v>0.1902155620271415</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.01655579242565608</v>
+        <v>0.1490892299822448</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.5101</t>
+          <t>X &gt; 0.5095</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2942</v>
+        <v>2966</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.0127674644275757</v>
+        <v>-0.01065484997199917</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.09311209544147658</v>
+        <v>-0.07118594157735458</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1081402205448825</v>
+        <v>0.1326517312788766</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.04551589917442556</v>
+        <v>0.06142107382353146</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2947632554388093</v>
+        <v>-0.2289888762193684</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1226153167392212</v>
+        <v>-0.08691704113732612</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1727856124749252</v>
+        <v>0.1430486948209975</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1507379551247823</v>
+        <v>0.09205187057536079</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.05905191224969286</v>
+        <v>-0.06301810905748084</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2029765695679728</v>
+        <v>0.1337656240091221</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1581266236699719</v>
+        <v>0.1230500659106681</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2377583438232591</v>
+        <v>0.2353703945344989</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1201378951797381</v>
+        <v>-0.05338320299217258</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2056694995151815</v>
+        <v>-0.1335500375345262</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.2674737221484307</v>
+        <v>-0.1907023002127985</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.09363728844908792</v>
+        <v>0.02057861219590507</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.0639571280609772</v>
+        <v>0.2057396814715062</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.115094561747334</v>
+        <v>0.2611155302024741</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.3173483151673295</v>
+        <v>0.4956143172703662</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.05274648208204269</v>
+        <v>0.1239860838277025</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2217782188086872</v>
+        <v>-0.005600552952159887</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1415010533262304</v>
+        <v>0.00662919689671071</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.01737141950093246</v>
+        <v>0.1354903943377224</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.03817973023627275</v>
+        <v>0.09450881127504829</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.583</t>
+          <t>X &gt; 0.5823</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2936</v>
+        <v>2957</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.06223032992278377</v>
+        <v>0.08396830211102468</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.05140199026622128</v>
+        <v>0.02402941905419453</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1193519630450979</v>
+        <v>0.1987078181649125</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.03316434653852696</v>
+        <v>0.1290760178386705</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2822316790134209</v>
+        <v>-0.1949808761670653</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1101096135888753</v>
+        <v>-0.0193065345051906</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1874656983368084</v>
+        <v>0.1801386900938837</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.132045723295235</v>
+        <v>0.1299235563792962</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.04435192791361686</v>
+        <v>0.007678789433981592</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2197879395660109</v>
+        <v>0.1738145649233047</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1742944082732549</v>
+        <v>0.1285617742731588</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1867728543349614</v>
+        <v>0.174655487546886</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1695815817893802</v>
+        <v>-0.1116117540214887</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2548370286943751</v>
+        <v>-0.1912686070931642</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.3154425872921323</v>
+        <v>-0.280270009567964</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1424798443147068</v>
+        <v>-0.07008213888227743</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.04968297014404754</v>
+        <v>0.149675863426701</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.06713172469649464</v>
+        <v>0.1718438376698188</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.269341332333461</v>
+        <v>0.4063733769655968</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1019067995964633</v>
+        <v>0.03293258506117525</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.270176002608423</v>
+        <v>-0.09532272713037315</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.1895964746421157</v>
+        <v>-0.08285748952481242</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.03097654143335404</v>
+        <v>0.04562424670018572</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.05244276655885471</v>
+        <v>0.0387990892558463</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.6558</t>
+          <t>X &gt; 0.6551</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2911</v>
+        <v>2930</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2472838551901404</v>
+        <v>0.2696403000154604</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1697189746051109</v>
+        <v>0.2114664361855318</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3201454350916677</v>
+        <v>0.399295223408906</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.03591582274892602</v>
+        <v>0.2327554814830108</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2806934637317511</v>
+        <v>-0.1595761959946671</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1086976589158581</v>
+        <v>-0.01766240947770115</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.232192592124683</v>
+        <v>0.2588129949242628</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1786921089246718</v>
+        <v>0.1769931457431397</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.0004475102320853352</v>
+        <v>0.08644813425837583</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3418953448776563</v>
+        <v>0.329422055789145</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2252633050526995</v>
+        <v>0.2133033816806602</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.206016884676373</v>
+        <v>0.1943620557150965</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1437658272018538</v>
+        <v>-0.0842860711145903</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1936118269361131</v>
+        <v>-0.1283690607545722</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.2833370605334125</v>
+        <v>-0.2459347824974216</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.1482439196627041</v>
+        <v>-0.07301139964713599</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.04671157039103235</v>
+        <v>0.1497218437783872</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.06520774094470738</v>
+        <v>0.1733162071609371</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.3016046664835912</v>
+        <v>0.4421140797210512</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.1087375235154227</v>
+        <v>0.02917755147320378</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3081127923736986</v>
+        <v>-0.1291295479300274</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1918749395036343</v>
+        <v>-0.08176248812551279</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.03425042111173582</v>
+        <v>0.0115408007357658</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.02089841304494655</v>
+        <v>0.04026492320572572</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.7287</t>
+          <t>X &gt; 0.7279</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2847</v>
+        <v>2865</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2991807805708149</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.05297741364549324</v>
+        <v>0.07628446044896009</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2737261948048086</v>
+        <v>0.3312522233369464</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.0009425299937362297</v>
+        <v>0.1742903574767141</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2473036539201061</v>
+        <v>-0.116600912316585</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.005774043512957405</v>
+        <v>0.129119429916237</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3250968558333085</v>
+        <v>0.3951080335962018</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4164668395340669</v>
+        <v>0.4225753791575144</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.05856312922321649</v>
+        <v>0.1187033271437201</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2500904952792879</v>
+        <v>0.2113709946882665</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2996249801230704</v>
+        <v>0.2602867291933251</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1812124948505911</v>
+        <v>0.1428388377322563</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.186262277836903</v>
+        <v>-0.1517089633589492</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2672851318745302</v>
+        <v>-0.2259694687725826</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.1691627007467886</v>
+        <v>-0.1567615523319148</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.114406149795073</v>
+        <v>-0.06223495503451204</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.0528878211208621</v>
+        <v>0.1330655694879823</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.1442801123655286</v>
+        <v>0.2298844778813702</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3110142624665784</v>
+        <v>0.4302223940882683</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.07764744416467551</v>
+        <v>0.03792711934440973</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2693164191482467</v>
+        <v>-0.1111073401953178</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1136499385185843</v>
+        <v>-0.02607636514066769</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.07648855900927032</v>
+        <v>0.09872872356564244</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.05675961579495237</v>
+        <v>0.09690949193863219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.8016</t>
+          <t>X &gt; 0.8006</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2738</v>
+        <v>2759</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2554921399206975</v>
+        <v>0.3062941351987618</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2303224261442551</v>
+        <v>0.3316535538537622</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2990882687846153</v>
+        <v>0.4283346093119462</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.005478491442602262</v>
+        <v>0.2880287599005698</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3099373620586903</v>
+        <v>-0.1114761890516505</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1388925811571156</v>
+        <v>-0.006506650867777353</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2719180988048961</v>
+        <v>0.4441747643500307</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3052325581395365</v>
+        <v>0.4122415229519376</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.1412370705769916</v>
+        <v>0.01970380145899497</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.02064625310698176</v>
+        <v>0.00197999723425113</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.1256203091493688</v>
+        <v>-0.06602890172204923</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2378277439153536</v>
+        <v>-0.1775028332524045</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6846797008672709</v>
+        <v>-0.5491329479768794</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7237418317732676</v>
+        <v>-0.580604003629638</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.632182944808207</v>
+        <v>-0.5188808110459817</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.3804437820831268</v>
+        <v>-0.2977600438064485</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.09195229909426672</v>
+        <v>0.01742389993972182</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.06572786919048923</v>
+        <v>0.01447178002893423</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.02603613279194406</v>
+        <v>0.1418047777930767</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2761663609385465</v>
+        <v>-0.1652688749071203</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4903652104076883</v>
+        <v>-0.3344512473957479</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3255696029929993</v>
+        <v>-0.2433510341028366</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.1023550072886081</v>
+        <v>-0.08695652173912549</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.0833927827802583</v>
+        <v>-0.04643859874602185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.8745</t>
+          <t>X &gt; 0.8734</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2542</v>
+        <v>2561</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2834012270600326</v>
+        <v>0.2170631943700272</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2040635882182116</v>
+        <v>0.2424741881235164</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2330940458304482</v>
+        <v>0.305609543596276</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.01101052560844096</v>
+        <v>0.2387400463038745</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1463921458024018</v>
+        <v>-0.01514456008296605</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1017305329815983</v>
+        <v>0.2022842121722235</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5651545112437759</v>
+        <v>0.5935207320088978</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5609156692304254</v>
+        <v>0.5438013981703236</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1580174710692148</v>
+        <v>-0.08297130121610508</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1086935229866768</v>
+        <v>-0.1185706562709044</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5561582379079937</v>
+        <v>-0.5238613769762424</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3030789611015194</v>
+        <v>-0.3116349755361441</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.8155947634771792</v>
+        <v>-0.8206068239580659</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8406720719112286</v>
+        <v>-0.7964673445351451</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.8483976171301535</v>
+        <v>-0.8721237173839995</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.5446283153226972</v>
+        <v>-0.5605471583684505</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.4199406372866861</v>
+        <v>-0.3689658810544145</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.06966407629853677</v>
+        <v>-0.05027336211146149</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.1696518100202198</v>
+        <v>0.1872676931342667</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2094504290335308</v>
+        <v>-0.1990739924992297</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.4769474810860004</v>
+        <v>-0.3765028932559389</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.4901474848274603</v>
+        <v>-0.4676586417526138</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.03500664483295424</v>
+        <v>-0.0448698367443896</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.2447434502231616</v>
+        <v>-0.1839035903202202</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.9473</t>
+          <t>X &gt; 0.9462</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2103</v>
+        <v>2126</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4412670913816257</v>
+        <v>0.2604530665697524</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1294700656279346</v>
+        <v>-0.1254444364229599</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.01600765297382623</v>
+        <v>0.01976813457392979</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3873433194146969</v>
+        <v>-0.1993256181307004</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.5077560728405928</v>
+        <v>-0.4023177898610371</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1052085007479562</v>
+        <v>0.01407815626537001</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2373982613247776</v>
+        <v>0.3198224676564365</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4795274031374461</v>
+        <v>0.5557478208249549</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3508239815363581</v>
+        <v>-0.1781520792780853</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.4611745842174244</v>
+        <v>-0.3394126639380843</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.133636475420388</v>
+        <v>-1.070369144288875</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.148820862877912</v>
+        <v>-1.086445349214088</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.676571807617556</v>
+        <v>-1.518844364026414</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.471312455736324</v>
+        <v>-1.298474864072453</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.987343010540954</v>
+        <v>-1.859864418158885</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.412824931782268</v>
+        <v>-1.318395229300641</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.329550569453012</v>
+        <v>-1.207497458157356</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.027240389243254</v>
+        <v>-0.9376082835653605</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.8784200978199976</v>
+        <v>-0.7427280859381682</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.043609357495015</v>
+        <v>-0.8766894429819132</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.301255240560749</v>
+        <v>-1.068194094738587</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.159264143277689</v>
+        <v>-1.021909663627142</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.524159751325243</v>
+        <v>-0.468567221563255</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.6669794152545734</v>
+        <v>-0.5366328386184662</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 1.02</t>
+          <t>X &gt; 1.019</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1602</v>
+        <v>1617</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.03880656622171585</v>
+        <v>0.1428769573930921</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.01324436280077634</v>
+        <v>0.1426703673894636</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.648791475664261</v>
+        <v>-0.5591981816765639</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7086403239087673</v>
+        <v>-0.5373497662341791</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.08072698192298589</v>
+        <v>-0.01438210780770532</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2031900166175902</v>
+        <v>0.3612956935786968</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.644937741711928</v>
+        <v>0.7077361598774701</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.297247388770273</v>
+        <v>1.263824326554946</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.1336587350450742</v>
+        <v>0.1002403211099008</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.390963955268262</v>
+        <v>-0.4762255936382402</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.303124052398708</v>
+        <v>-0.3886059636492902</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-0.9996327835999423</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.260685210465518</v>
+        <v>-1.278710302408655</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.9845608550910967</v>
+        <v>-0.9724157131948061</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.58055374869403</v>
+        <v>-1.557210392955731</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.794122078460177</v>
+        <v>-1.700400639066693</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.394658882793841</v>
+        <v>-1.275077160493829</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.152138693507453</v>
+        <v>-1.001636678766715</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.9620528442661893</v>
+        <v>-0.7511757923133189</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.237181794058095</v>
+        <v>-1.057132433575276</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.779727962024126</v>
+        <v>-1.562734015970236</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.32061847715795</v>
+        <v>-1.204996105025081</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.4481378437327876</v>
+        <v>-0.4047753488747219</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.4245933821041419</v>
+        <v>-0.3195426672210857</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 1.093</t>
+          <t>X &gt; 1.092</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1195</v>
+        <v>1214</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.251358525042335</v>
+        <v>1.330428144944271</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.0873943303409348</v>
+        <v>0.3474205721396686</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.02392488452753128</v>
+        <v>0.1574275349491572</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.105850092288705</v>
+        <v>-0.8444750733594759</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2331515724041111</v>
+        <v>0.02656793314233141</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4161830558216053</v>
+        <v>0.6391882243352924</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.9393189013177263</v>
+        <v>1.12088508217883</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9106914831869446</v>
+        <v>1.062068002182848</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.3315546630594355</v>
+        <v>-0.1225543596670917</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.021206392384862</v>
+        <v>-0.9186058548864295</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7471467502229387</v>
+        <v>-0.6463708402820956</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8116996507566938</v>
+        <v>-0.7943782680005924</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.053085237212478</v>
+        <v>-0.8766226055732602</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7737470994805946</v>
+        <v>-0.7140103235388295</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.598696068453975</v>
+        <v>-1.478333974117398</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.25535168195718</v>
+        <v>-1.985230448313338</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.305865983238242</v>
+        <v>-2.089110860038346</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.993692508577361</v>
+        <v>-1.846151649021252</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.896570107367623</v>
+        <v>-1.831359120814191</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.162860476746133</v>
+        <v>-2.063888288530713</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.454780078296118</v>
+        <v>-2.384215821212919</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.029372906873135</v>
+        <v>-2.047516728670686</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.8703708224495301</v>
+        <v>-0.9801590143972376</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.064379423610838</v>
+        <v>-1.059925685787199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 1.166</t>
+          <t>X &gt; 1.165</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.406974353093005</v>
+        <v>1.510004850836765</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5218513294225886</v>
+        <v>-0.3148493532881531</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.6846312711209563</v>
+        <v>-0.5169118762323563</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.445745916425729</v>
+        <v>-1.319840390830066</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2323555039209992</v>
+        <v>-0.1217143204030862</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.01455741133297295</v>
+        <v>0.3047550850514966</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3699192703220646</v>
+        <v>0.6236593697424766</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.265667270606343</v>
+        <v>1.37359124700896</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6601625895025052</v>
+        <v>-0.7136697167246524</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.326240658701394</v>
+        <v>-1.50972121194399</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8385058028642547</v>
+        <v>-1.02651573320464</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.224092813149859</v>
+        <v>-1.349324056533398</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.216947279110137</v>
+        <v>-1.347749575333921</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.7963149256102042</v>
+        <v>-0.8560259200651288</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.026650736559752</v>
+        <v>-1.115347320977676</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.822638146167563</v>
+        <v>-1.928250490318682</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.956555283145036</v>
+        <v>-2.137839147286826</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.6335885003352</v>
+        <v>-1.953598516719033</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.9272529370659441</v>
+        <v>-1.255227433571392</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.7848172980598562</v>
+        <v>-1.085367918832553</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.8986389215457251</v>
+        <v>-1.229083606653973</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.7601226107147383</v>
+        <v>-0.9864495184397555</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.3148710879984904</v>
+        <v>-0.7428150331613779</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.1457773454735118</v>
+        <v>-0.05749640033220516</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 1.239</t>
+          <t>X &gt; 1.237</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.261113670881763</v>
+        <v>1.120585707122565</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.9263368725319481</v>
+        <v>1.004212550175161</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.295995901989244</v>
+        <v>-1.286750981768222</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.807225252506825</v>
+        <v>-1.879153180576445</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6301462994607192</v>
+        <v>-0.6003071755980685</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2386758598812548</v>
+        <v>-0.1122310523120191</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.2456655290363017</v>
+        <v>0.2039103423985154</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.7558903523515639</v>
+        <v>0.6782106782106752</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.173713135904563</v>
+        <v>-1.141912360157171</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.735065080009392</v>
+        <v>-2.847054764467416</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.409757080423013</v>
+        <v>-1.535858710902041</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.294288349836847</v>
+        <v>-1.552700405633075</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.6322301386654416</v>
+        <v>-0.904297300750919</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5901511203751895</v>
+        <v>-0.7624143270734933</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.3272417863768027</v>
+        <v>-0.5342956270339769</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.048644338118017</v>
+        <v>-1.273381725249422</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.18256147509549</v>
+        <v>-1.37726213697443</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.155823231548254</v>
+        <v>-1.380107230432515</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.7310351028255795</v>
+        <v>-1.035605991583232</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.2028152449330847</v>
+        <v>-0.4850854329568435</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.48150917015505</v>
+        <v>-0.7921132676709135</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.02965064607602841</v>
+        <v>-0.2162341229595341</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.7202460731469813</v>
+        <v>0.2878170289855149</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.17281540512846</v>
+        <v>0.9069280346960511</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 1.312</t>
+          <t>X &gt; 1.31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.237201667055842</v>
+        <v>0.9890953262700606</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1402297467548053</v>
+        <v>0.4410736869408183</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.602667351056674</v>
+        <v>-1.417850022201513</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.233467209263146</v>
+        <v>-2.161309622822429</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8048950980627296</v>
+        <v>-0.6241789411695038</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2330013979194092</v>
+        <v>0.5241117133360618</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4522779260558849</v>
+        <v>-0.33721519872703</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8032529604793837</v>
+        <v>0.8730158730158664</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.9957506551519231</v>
+        <v>-0.8172370354818455</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.382163263703745</v>
+        <v>-2.370864288276941</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.49460668902649</v>
+        <v>-1.492568667611991</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.8531106937014741</v>
+        <v>-1.163090016022693</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5059062644638033</v>
+        <v>-0.8267474804178647</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.5733753098812144</v>
+        <v>-0.619746336995135</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.4581895338592687</v>
+        <v>0.2155499639726202</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.1763021924312298</v>
+        <v>-0.4371065634899622</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.002999667350323421</v>
+        <v>-0.237496838644411</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.5686698642590642</v>
+        <v>-0.825616148661851</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.3527784833347383</v>
+        <v>-0.4594088532307978</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.07889776501210832</v>
+        <v>-0.003829100636686178</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.3098022491077614</v>
+        <v>-0.5712736020174205</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.2297364048677579</v>
+        <v>0.1134422954801835</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.04267265581133728</v>
+        <v>-0.2508259548037444</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.7360711718188426</v>
+        <v>0.8028405220314099</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 1.385</t>
+          <t>X &gt; 1.383</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.425329357156272</v>
+        <v>2.254474721164769</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.3552584411594</v>
+        <v>1.646249044881188</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.185701784342186</v>
+        <v>-1.238879839619095</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.246302320955323</v>
+        <v>-1.287803777557755</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.9176863479352235</v>
+        <v>0.6105511258211749</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.104652534032603</v>
+        <v>0.8700650206222207</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.2539239495890868</v>
+        <v>-0.1857000472118813</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.454455573227875</v>
+        <v>0.9639249639249527</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.2020425702996889</v>
+        <v>0.1827629645181545</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.864773290579677</v>
+        <v>-2.067833985246637</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.405870764868766</v>
+        <v>-1.613780788824116</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.684620168316762</v>
+        <v>-2.072180925113599</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6663431990942996</v>
+        <v>-1.082419954304726</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1466813348001494</v>
+        <v>-0.4199072033516771</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.1211012935452231</v>
+        <v>-0.191314772850582</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.2104377104377164</v>
+        <v>-0.5407575664170707</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.2112007081403675</v>
+        <v>-0.09818989071038686</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.2640103660511812</v>
+        <v>-0.5953727208264468</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.3222513852435114</v>
+        <v>-0.01661176872621439</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.8055996345711307</v>
+        <v>0.4881505767755172</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.2935328042668957</v>
+        <v>-0.6267391800796744</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.9293225330253065</v>
+        <v>0.7579523125635816</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.6472109746353709</v>
+        <v>0.2716597905426923</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.499022506198742</v>
+        <v>1.386893059026953</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 1.457</t>
+          <t>X &gt; 1.456</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.201258149725923</v>
+        <v>2.888908541598944</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5506918776919107</v>
+        <v>0.9832506685506814</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.30837980291804</v>
+        <v>-1.101318952013102</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.274276305150032</v>
+        <v>-1.486252271153276</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2256009834581718</v>
+        <v>-0.3095282535762607</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.8070311645842381</v>
+        <v>0.7946021502410261</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.05584452686694164</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.36085928261727</v>
+        <v>1.062409812409811</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.2925687897053137</v>
+        <v>-0.476327944572752</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.972264126758759</v>
+        <v>-3.355712773125425</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.910068891376497</v>
+        <v>-3.291811091854427</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.765089481265171</v>
+        <v>-3.360059712992388</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.223078278122365</v>
+        <v>-1.856649812349907</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8072144794097227</v>
+        <v>-1.269810804889495</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.040729326884126</v>
+        <v>-1.534428652327776</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.8709708550472897</v>
+        <v>-1.390661167954889</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.5802595419186076</v>
+        <v>-1.077005045233122</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.8974144707928673</v>
+        <v>-1.418657417618107</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.4692088648154638</v>
+        <v>-0.9954269232489494</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.05598450805630506</v>
+        <v>-0.4502179294700994</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.9120935748033432</v>
+        <v>-1.436072472691833</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.2886562084684101</v>
+        <v>0.1624051727168947</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.0751669513899671</v>
+        <v>-0.4307804256867414</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>0.7000646251739937</v>
+        <v>0.4531056846263084</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 1.53</t>
+          <t>X &gt; 1.529</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.308519975175628</v>
+        <v>2.068345840467956</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.21424950593974</v>
+        <v>1.323685887557104</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.995921441825438</v>
+        <v>-2.175397241765893</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7966477416768356</v>
+        <v>-1.022163530349687</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7371966131081251</v>
+        <v>-0.7989685532420339</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.73984590886711</v>
+        <v>1.851730638790961</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.3505892330777201</v>
+        <v>0.200663589151759</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.113194114855247</v>
+        <v>1.89574314574314</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.6240690518719916</v>
+        <v>0.523672055427248</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.444764991511434</v>
+        <v>-2.77237943979209</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.150297186084209</v>
+        <v>-1.500144425187756</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.684148630348524</v>
+        <v>-2.276726379659053</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5113923298577063</v>
+        <v>-0.9975082214206026</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.4773691654879713</v>
+        <v>-0.9951157164376667</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.8804104222522042</v>
+        <v>-1.426643531906691</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.224180581323445</v>
+        <v>-0.3640863802549461</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.1648385964703607</v>
+        <v>-0.7185933583959923</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.01457725947521027</v>
+        <v>-0.6008508971415552</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3088899601835422</v>
+        <v>-0.887641802827865</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2850752192714125</v>
+        <v>-0.2757051984509786</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.7689799001012787</v>
+        <v>-1.094405981238758</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.201209944116222</v>
+        <v>1.091738029469283</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.7084212294883017</v>
+        <v>0.3303473891195097</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.399852403375</v>
+        <v>1.424489801865228</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 1.603</t>
+          <t>X &gt; 1.601</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.017537979735735</v>
+        <v>1.197434433968915</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.303879193808285</v>
+        <v>1.563148393372082</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.997493892489793</v>
+        <v>-1.832218491394116</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.920989503620007</v>
+        <v>-1.812999895095317</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.774887452802787</v>
+        <v>-1.78274763764113</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.849578733294599</v>
+        <v>1.738100341445637</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.9463604569277564</v>
+        <v>0.5058783130781421</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.116424874243641</v>
+        <v>3.575190998503871</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.963554689387188</v>
+        <v>1.862629110641969</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.317197977244916</v>
+        <v>-1.694158580896385</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.416179087434088</v>
+        <v>-0.808426633776719</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.32188773853099</v>
+        <v>-1.698505520763348</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.191131310089297</v>
+        <v>-1.410849266340598</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.098730562711438</v>
+        <v>-1.351391020081394</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.189475741169737</v>
+        <v>-0.4950838635049095</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.7183908045977034</v>
+        <v>0.3739124630070521</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.5844736676202302</v>
+        <v>0.270032051282044</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.147326283849857</v>
+        <v>-0.4782366692641631</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.5583941505744363</v>
+        <v>-1.186851365195317</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.386106279767795</v>
+        <v>0.5661966183252005</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.2146292941917025</v>
+        <v>-0.3089401907478333</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.71111037680776</v>
+        <v>1.462051133450728</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.356654271679751</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.909752836066538</v>
+        <v>1.851238932131949</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 1.676</t>
+          <t>X &gt; 1.674</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5544273603455423</v>
+        <v>-0.4814022383146792</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.06615889120565299</v>
+        <v>0.08901745659369453</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.738745841471207</v>
+        <v>-2.798329706522374</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.040177227169089</v>
+        <v>-2.982568640024475</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.156602328835845</v>
+        <v>-3.25812678012381</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3361489812284759</v>
+        <v>0.1641129483232575</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.6158346808862163</v>
+        <v>-1.221467558389222</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.425455949049507</v>
+        <v>1.752300522792325</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.222129852955916</v>
+        <v>1.060557301328892</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.455350138433275</v>
+        <v>-3.014182718480612</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.351414977599156</v>
+        <v>-1.922275572728736</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.460039899719348</v>
+        <v>-3.018529658347575</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.923450929231073</v>
+        <v>-2.494077513503264</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.729592046341565</v>
+        <v>-2.33247550936261</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.101891212094479</v>
+        <v>-0.5556134978050409</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.6962781340374704</v>
+        <v>0.005690521014621197</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.5623609970599972</v>
+        <v>-0.09818989071038686</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.3723552254333811</v>
+        <v>-1.050746127019529</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.6734116741631411</v>
+        <v>-0.01661176872621439</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>-0.211861389240994</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.2649304542359658</v>
+        <v>-0.7793058906217283</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.992556917688262</v>
+        <v>2.424220112013145</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.7670316301703153</v>
+        <v>0.2088382038489058</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.6911993769470399</v>
+        <v>0.4565352751332057</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 1.749</t>
+          <t>X &gt; 1.747</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2451632492623332</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.4285211659384274</v>
+        <v>0.5704407951598895</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-4.63644088827391</v>
+        <v>-4.273996896475282</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.758721332587122</v>
+        <v>-2.815117044001447</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7332207861361226</v>
+        <v>-1.039393132818731</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.495412066627928</v>
+        <v>0.6560020116408865</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.549987751642874</v>
+        <v>-1.910161153116285</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.836722269572633</v>
+        <v>0.8777019086297315</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.83108903263917</v>
+        <v>1.00563081831384</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.083187899941827</v>
+        <v>-3.398668099585905</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.332688467203987</v>
+        <v>-3.641897002507342</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-5.18211849892424</v>
+        <v>-5.464870709555953</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.116798890387685</v>
+        <v>-2.456051486800547</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.861437976258351</v>
+        <v>-3.219749465759428</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.425340436142584</v>
+        <v>-1.840048177541398</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.8309535141995923</v>
+        <v>-1.278744158721736</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4413104417529752</v>
+        <v>-0.8671606529209583</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.069711354998248</v>
+        <v>-1.515508675608345</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.3302597646498313</v>
+        <v>-0.7855825309367859</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>-0.05553216835203045</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.3745795770429865</v>
+        <v>-0.6229766697327648</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.2337849878637</v>
+        <v>2.910108230992357</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.402996542451021</v>
+        <v>1.091887046167642</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>1.327164289227746</v>
+        <v>1.44521196940395</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 1.822</t>
+          <t>X &gt; 1.82</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.9644160444627659</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.6296392461129514</v>
+        <v>0.05762028233937855</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-4.09785348712856</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.179228559202883</v>
+        <v>-3.071527300411702</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.8332483799551085</v>
+        <v>-2.06503415845976</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.6782211174005539</v>
+        <v>0.6560020116408865</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.380703283929094</v>
+        <v>-1.065465443106305</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.007751937984494</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>1.983349474782081</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.390343222803956</v>
+        <v>-2.683669762372737</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.78295024730869</v>
+        <v>-2.411434747768403</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.061699650756694</v>
+        <v>-4.623500573207437</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.518195050946147</v>
+        <v>-3.802908819690472</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.739273927392738</v>
+        <v>-4.051142881123582</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.7307505583066245</v>
+        <v>-2.15265210171831</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.469696969696976</v>
+        <v>-2.881670663543815</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.2702807733411063</v>
+        <v>-1.695228494623656</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-1.04178814382896</v>
+        <v>-2.473273890107841</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.1592300962379625</v>
+        <v>-1.613650372639484</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.6390509529366071</v>
+        <v>-1.399063927580499</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5149304542359658</v>
+        <v>-1.32134713863865</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.075890251021598</v>
+        <v>1.184135500696378</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>-0.5077138849929881</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.941199376947047</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 1.895</t>
+          <t>X &gt; 1.892</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.640847113431967</v>
+        <v>-1.574122791102731</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3756239117817799</v>
+        <v>-0.2452264772002906</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.613642960812768</v>
+        <v>-2.287322153895026</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.726596980255508</v>
+        <v>-1.304921203096946</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.01077454957697199</v>
+        <v>-0.00567619358998428</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.9826432494236315</v>
+        <v>1.726060562014396</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.6762072851766021</v>
+        <v>-0.2001300616418931</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.276044620911321</v>
+        <v>4.256854256854254</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.691515542663431</v>
+        <v>2.797481579236774</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.4795754763830331</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.05937301153633712</v>
+        <v>-0.9009380759814078</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.403163065390835</v>
+        <v>-5.145773998706666</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.6482763517591579</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.8693552282057482</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1.724533994538902</v>
+        <v>0.7454533770323266</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>3.131929046563187</v>
+        <v>2.100408189502787</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.624028169748328</v>
+        <v>3.58382936507936</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>3.706179335845839</v>
+        <v>2.657294466266968</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.922070716770165</v>
+        <v>2.871756693412742</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.295908396656884</v>
+        <v>2.292692344820935</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.940354098609561</v>
+        <v>1.725247843440201</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>5.116540657525654</v>
+        <v>4.824688496088093</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.951990979763806</v>
+        <v>2.687370600414084</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>3.689166856621839</v>
+        <v>3.318882399775411</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 1.968</t>
+          <t>X &gt; 1.965</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.155698598580479</v>
+        <v>-2.581088266572138</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.469920642673671</v>
+        <v>0.05762028233937855</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.938395436060297</v>
+        <v>-3.120150742629122</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-4.641448465404025</v>
+        <v>-4.674091402975812</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.46238745280278</v>
+        <v>-3.02657261999822</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2754212667054006</v>
+        <v>-0.9465620909232086</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.5283876251618196</v>
+        <v>-1.209530585605528</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.300681230913796</v>
+        <v>3.339917903024691</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.321966392626479</v>
+        <v>1.526099239893263</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4812523137130427</v>
+        <v>-2.182573614549376</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2071926715511196</v>
+        <v>-1.910338599945042</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-5.536447125504161</v>
+        <v>-7.04128948645517</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.41109787834678</v>
+        <v>-0.3891913126438098</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.8200820082008136</v>
+        <v>-1.608299160484684</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.5419767144206489</v>
+        <v>-0.3487059695542101</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>2.146464646464644</v>
+        <v>1.183471835673224</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.022648519588188</v>
+        <v>2.050465210355981</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.907706805665988</v>
+        <v>0.9467073187866148</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.133699196691332</v>
+        <v>2.132043332340153</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.300342986457338</v>
+        <v>0.4048822045836005</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.7577968184913075</v>
+        <v>-0.1625622967971339</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.722354897486248</v>
+        <v>3.645770326878662</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>1.966526579665263</v>
+        <v>0.9767834529337307</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>3.910896346644009</v>
+        <v>2.756392031459796</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 2.04</t>
+          <t>X &gt; 2.038</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.450370922955777</v>
+        <v>-2.954391433992953</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.786280850122985</v>
+        <v>0.3291134950090608</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.6517381989080064</v>
+        <v>-0.9255806068825194</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.936120789779324</v>
+        <v>-5.047394570396627</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.890958881374218</v>
+        <v>-2.970011534025367</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3230403143244516</v>
+        <v>-0.4601367515566963</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.7839553506090553</v>
+        <v>0.5935207320088978</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.325021014289725</v>
+        <v>5.050505050505045</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.956869641987559</v>
+        <v>2.797481579236774</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.430503865374227</v>
+        <v>-1.569998487411134</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.156444223212304</v>
+        <v>-1.2977634728068</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-5.049651457985604</v>
+        <v>-5.145773998706666</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-2.558355693516418</v>
+        <v>-2.689237544728869</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.779434569963009</v>
+        <v>-2.937471606161978</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.1768799637817295</v>
+        <v>-0.04819741661846422</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.7712668857247209</v>
+        <v>0.5131066022011979</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.046988302964117</v>
+        <v>2.790178571428569</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.737328322034493</v>
+        <v>1.466818275790772</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.158038980067261</v>
+        <v>2.871756693412742</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.549704067143708</v>
+        <v>4.276819328947916</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.802338622069257</v>
+        <v>2.518898637090992</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>6.34095049198546</v>
+        <v>6.015164686564283</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>4.20578665025063</v>
+        <v>3.877846790890274</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>6.539592951244238</v>
+        <v>6.096660177553197</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 2.113</t>
+          <t>X &gt; 2.111</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-5.814760156910225</v>
+        <v>-6.399769585253459</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3524355059846727</v>
+        <v>-0.9313907066716069</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.3411791926968277</v>
+        <v>-0.7575133799917637</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-6.851234661414928</v>
+        <v>-7.064201293085702</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.288474409324529</v>
+        <v>-3.054045147470745</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-4.10150822322715</v>
+        <v>-2.897111541472661</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-2.63560524471341</v>
+        <v>-2.263622125133956</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.497948016415876</v>
+        <v>1.717171717171716</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1.401741272257659</v>
+        <v>-1.012042230287037</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-5.115833418882382</v>
+        <v>-4.665236582649229</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-4.841773776720458</v>
+        <v>-4.393001568044895</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-9.53228788605081</v>
+        <v>-8.955297808230483</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-6.243685247024573</v>
+        <v>-5.784475639966963</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.052999417588815</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.2300337554188587</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.8244206773618501</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>3.631680010972616</v>
+        <v>3.742559523809518</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>2.056251071857318</v>
+        <v>2.181103990076494</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>3.74273068807576</v>
+        <v>3.824137645793691</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>5.400164733337903</v>
+        <v>4.038724090852675</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>3.387030330077756</v>
+        <v>2.042708160900517</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>7.722949074551018</v>
+        <v>6.25325992465951</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>5.056247316444825</v>
+        <v>3.639751552795033</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>7.921591533809796</v>
+        <v>6.334755415648424</v>
       </c>
     </row>
   </sheetData>
@@ -5448,2379 +5448,2379 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.07287</t>
+          <t>X &lt; 0.07279</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.7500548222114105</v>
+        <v>-0.5511737366576028</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.4424333336233204</v>
+        <v>0.2712954960145879</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.880452382654312</v>
+        <v>-1.197073819552202</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.094477065908613</v>
+        <v>-0.7210999499843496</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.7110600846704429</v>
+        <v>1.140094046668445</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1726375407953427</v>
+        <v>0.01497637061525126</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.801117273936235</v>
+        <v>-1.634806496318319</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.865195956376674</v>
+        <v>-1.512376512376512</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.753044962898791</v>
+        <v>-0.5297467479915525</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.382491688185823</v>
+        <v>-1.966823884236533</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.322564808336537</v>
+        <v>-2.121939296982625</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.815446974097171</v>
+        <v>-2.612196465129131</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.5124848439511425</v>
+        <v>-0.5219603774516983</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.03611949177751228</v>
+        <v>0.2107898397440024</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.236345292909391</v>
+        <v>0.5992992694221186</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.8860059825725131</v>
+        <v>-0.5524588102592958</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-1.878292218262423</v>
+        <v>-1.512870271234831</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-2.197725196761724</v>
+        <v>-1.85988713870907</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-3.483979738584175</v>
+        <v>-3.144354247751735</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.151211181835031</v>
+        <v>-0.7884401795664076</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.06331755101015801</v>
+        <v>0.2707890928441046</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.5692710393009861</v>
+        <v>-0.2335579784674024</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.585118907464086</v>
+        <v>-1.06288486657958</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-1.230843633805641</v>
+        <v>-1.010431586190933</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.1457</t>
+          <t>X &lt; 0.1456</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.7500548222114105</v>
+        <v>-0.5511737366576028</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4424333336233204</v>
+        <v>0.2712954960145879</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.880452382654312</v>
+        <v>-1.197073819552202</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.094477065908613</v>
+        <v>-0.7210999499843496</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.7110600846704429</v>
+        <v>1.140094046668445</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1726375407953427</v>
+        <v>0.01497637061525126</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.801117273936235</v>
+        <v>-1.634806496318319</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.865195956376674</v>
+        <v>-1.512376512376512</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.753044962898791</v>
+        <v>-0.5297467479915525</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.382491688185823</v>
+        <v>-1.966823884236533</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.322564808336537</v>
+        <v>-2.121939296982625</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.815446974097171</v>
+        <v>-2.612196465129131</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5124848439511425</v>
+        <v>-0.5219603774516983</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.03611949177751228</v>
+        <v>0.2107898397440024</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.236345292909391</v>
+        <v>0.5992992694221186</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.8860059825725131</v>
+        <v>-0.5524588102592958</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-1.878292218262423</v>
+        <v>-1.512870271234831</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-2.197725196761724</v>
+        <v>-1.85988713870907</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-3.483979738584175</v>
+        <v>-3.144354247751735</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-1.151211181835031</v>
+        <v>-0.7884401795664076</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.06331755101015801</v>
+        <v>0.2707890928441046</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.5692710393009861</v>
+        <v>-0.2335579784674024</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-1.585118907464086</v>
+        <v>-1.06288486657958</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-1.230843633805641</v>
+        <v>-1.010431586190933</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.2186</t>
+          <t>X &lt; 0.2184</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.7500548222114105</v>
+        <v>-0.5511737366576028</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.4424333336233204</v>
+        <v>0.2712954960145879</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.880452382654312</v>
+        <v>-1.197073819552202</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.094477065908613</v>
+        <v>-0.7210999499843496</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.7110600846704429</v>
+        <v>1.140094046668445</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1726375407953427</v>
+        <v>0.01497637061525126</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.801117273936235</v>
+        <v>-1.634806496318319</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.865195956376674</v>
+        <v>-1.512376512376512</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.753044962898791</v>
+        <v>-0.5297467479915525</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.382491688185823</v>
+        <v>-1.966823884236533</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.322564808336537</v>
+        <v>-2.121939296982625</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.815446974097171</v>
+        <v>-2.612196465129131</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.5124848439511425</v>
+        <v>-0.5219603774516983</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.03611949177751228</v>
+        <v>0.2107898397440024</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.236345292909391</v>
+        <v>0.5992992694221186</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.8860059825725131</v>
+        <v>-0.5524588102592958</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.878292218262423</v>
+        <v>-1.512870271234831</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-2.197725196761724</v>
+        <v>-1.85988713870907</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.483979738584175</v>
+        <v>-3.144354247751735</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.151211181835031</v>
+        <v>-0.7884401795664076</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.06331755101015801</v>
+        <v>0.2707890928441046</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.5692710393009861</v>
+        <v>-0.2335579784674024</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.585118907464086</v>
+        <v>-1.06288486657958</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-1.230843633805641</v>
+        <v>-1.010431586190933</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.2915</t>
+          <t>X &lt; 0.2911</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.7500548222114105</v>
+        <v>-0.5511737366576028</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4424333336233204</v>
+        <v>0.2712954960145879</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.880452382654312</v>
+        <v>-1.197073819552202</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.094477065908613</v>
+        <v>-0.7210999499843496</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.7110600846704429</v>
+        <v>1.140094046668445</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1726375407953427</v>
+        <v>0.01497637061525126</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.801117273936235</v>
+        <v>-1.634806496318319</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.865195956376674</v>
+        <v>-1.512376512376512</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.753044962898791</v>
+        <v>-0.5297467479915525</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.382491688185823</v>
+        <v>-1.966823884236533</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.322564808336537</v>
+        <v>-2.121939296982625</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.815446974097171</v>
+        <v>-2.612196465129131</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.5124848439511425</v>
+        <v>-0.5219603774516983</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.03611949177751228</v>
+        <v>0.2107898397440024</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.236345292909391</v>
+        <v>0.5992992694221186</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.8860059825725131</v>
+        <v>-0.5524588102592958</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.878292218262423</v>
+        <v>-1.512870271234831</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-2.197725196761724</v>
+        <v>-1.85988713870907</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.483979738584175</v>
+        <v>-3.144354247751735</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.151211181835031</v>
+        <v>-0.7884401795664076</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.06331755101015801</v>
+        <v>0.2707890928441046</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.5692710393009861</v>
+        <v>-0.2335579784674024</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-1.585118907464086</v>
+        <v>-1.06288486657958</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-1.230843633805641</v>
+        <v>-1.010431586190933</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.3644</t>
+          <t>X &lt; 0.3639</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7500548222114105</v>
+        <v>-0.5511737366576028</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.4424333336233204</v>
+        <v>0.2712954960145879</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.880452382654312</v>
+        <v>-1.197073819552202</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.094477065908613</v>
+        <v>-0.7210999499843496</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.7110600846704429</v>
+        <v>1.140094046668445</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1726375407953427</v>
+        <v>0.01497637061525126</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.801117273936235</v>
+        <v>-1.634806496318319</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.865195956376674</v>
+        <v>-1.512376512376512</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.753044962898791</v>
+        <v>-0.5297467479915525</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.382491688185823</v>
+        <v>-1.966823884236533</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.322564808336537</v>
+        <v>-2.121939296982625</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.815446974097171</v>
+        <v>-2.612196465129131</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.5124848439511425</v>
+        <v>-0.5219603774516983</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.03611949177751228</v>
+        <v>0.2107898397440024</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.236345292909391</v>
+        <v>0.5992992694221186</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.8860059825725131</v>
+        <v>-0.5524588102592958</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.878292218262423</v>
+        <v>-1.512870271234831</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.197725196761724</v>
+        <v>-1.85988713870907</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.483979738584175</v>
+        <v>-3.144354247751735</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.151211181835031</v>
+        <v>-0.7884401795664076</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.06331755101015801</v>
+        <v>0.2707890928441046</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.5692710393009861</v>
+        <v>-0.2335579784674024</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.585118907464086</v>
+        <v>-1.06288486657958</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.230843633805641</v>
+        <v>-1.010431586190933</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.4372</t>
+          <t>X &lt; 0.4367</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.5491626784639578</v>
+        <v>-0.3511373664084729</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2442806281996894</v>
+        <v>0.4667855851216984</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.682299677230681</v>
+        <v>-1.000674474216687</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.9027163832405876</v>
+        <v>-0.5292468857908688</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.8936893062590485</v>
+        <v>1.32285454857788</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.01455741133297295</v>
+        <v>0.2031924098951166</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.823489353580833</v>
+        <v>-1.655719389571644</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.888481182129219</v>
+        <v>-1.535107918086645</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.7808959191910603</v>
+        <v>-0.5561151786153005</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.406690060046309</v>
+        <v>-1.990464546175069</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.132630417884386</v>
+        <v>-1.93099548901754</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.624599437537078</v>
+        <v>-2.42034340093565</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3362476451181493</v>
+        <v>-0.343746156684297</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2094440213252113</v>
+        <v>0.3852007463611145</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.4060015784455047</v>
+        <v>0.7691444454995136</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.7090132090132073</v>
+        <v>-0.3753084653183478</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.697631200691532</v>
+        <v>-1.332067341862121</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.016147118187938</v>
+        <v>-1.678171063228419</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-3.295982232990099</v>
+        <v>-2.956246149515472</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.9723842862699357</v>
+        <v>-0.6094635424095785</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1089096599681696</v>
+        <v>0.4431965613889162</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.3952018260661916</v>
+        <v>-0.05931638791679461</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.405523687459947</v>
+        <v>-0.8840579710144851</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.053090416057955</v>
+        <v>-0.8325217516287324</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.5101</t>
+          <t>X &lt; 0.5095</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3638915108949661</v>
+        <v>-0.1670993019502589</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.06441883778600754</v>
+        <v>0.6418461830209736</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.502437886816999</v>
+        <v>-0.8238183830056229</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.7354764728559289</v>
+        <v>-0.3613682611387432</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.8314814689731165</v>
+        <v>1.261807775977111</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2500512878470573</v>
+        <v>-0.05805186696995435</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.079082424168696</v>
+        <v>-1.907986199877776</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.93446088794925</v>
+        <v>-1.579995250881332</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6244747631170071</v>
+        <v>-0.3972140205221208</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.243056401098528</v>
+        <v>-1.826176908146522</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.968996758936605</v>
+        <v>-1.764912357677204</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.459162652870859</v>
+        <v>-2.252464776283524</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1996608719468469</v>
+        <v>-0.2027999317089808</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3398221178049994</v>
+        <v>0.5181812680955389</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.7410008541227526</v>
+        <v>1.104525829128036</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.3595274781715503</v>
+        <v>-0.02550207594236298</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.34090224226766</v>
+        <v>-0.9750484496124017</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.657607352868503</v>
+        <v>-1.31934904526026</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-2.924766819401803</v>
+        <v>-2.584802251518298</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.6192769416371675</v>
+        <v>-0.2560509015967369</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.4489761275050057</v>
+        <v>0.7836282577528095</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.05149828401025047</v>
+        <v>0.2847369222382028</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.05090892184667</v>
+        <v>-0.530950626381717</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.70211272496379</v>
+        <v>-0.4812252138915269</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.583</t>
+          <t>X &lt; 0.5823</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8224755059163087</v>
+        <v>-0.7475956722099752</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.3221792353725945</v>
+        <v>0.04169417945675491</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.551430017180202</v>
+        <v>-1.212999922434825</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8030061660592693</v>
+        <v>-0.7702054338724551</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7401177664038912</v>
+        <v>1.024629800769418</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3255256508390261</v>
+        <v>-0.4747512930254558</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.141315670846275</v>
+        <v>-2.097990655154661</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.793222313929206</v>
+        <v>-1.781793086140915</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7078937958975899</v>
+        <v>-0.8257068265603351</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.315882540827616</v>
+        <v>-2.035836996727909</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.041822898665693</v>
+        <v>-1.763601982123575</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.111804034890312</v>
+        <v>-1.83314459912075</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1053261738276916</v>
+        <v>0.157553345540272</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6359004101247052</v>
+        <v>0.8611847858554071</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.023782217146653</v>
+        <v>1.631312561646702</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.05547102827437556</v>
+        <v>0.5328655431219644</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.235413269854362</v>
+        <v>-0.6083592669432889</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.340253973675544</v>
+        <v>-0.7412433721048899</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.588797739194725</v>
+        <v>-1.979063302635474</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3099017200216778</v>
+        <v>0.3102119391040148</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.7387383088667576</v>
+        <v>1.320997439189796</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.2436051357176225</v>
+        <v>0.8300345014340991</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.7397817870204548</v>
+        <v>0.03416794721142935</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.6059704343737167</v>
+        <v>-0.1279710470780344</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.6558</t>
+          <t>X &lt; 0.6551</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.855132827717675</v>
+        <v>-1.777920845757649</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.594671530829395</v>
+        <v>-1.043435524598777</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.635865183034994</v>
+        <v>-2.298129626490358</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.166279519938051</v>
+        <v>-1.321904374318194</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>0.7554786620530578</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3230403143244516</v>
+        <v>-0.4601367515566963</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.285465188690992</v>
+        <v>-2.431689352024712</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.968438538205973</v>
+        <v>-1.952296069943131</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9348878642277825</v>
+        <v>-1.236131866141378</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.898279730740455</v>
+        <v>-2.816497086850909</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.22739469175314</v>
+        <v>-2.152105209501478</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.109318698375738</v>
+        <v>-1.84045186985513</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.05787759062868503</v>
+        <v>-0.01416751671766292</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2362065232368167</v>
+        <v>0.4421710170955677</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.7709061680021847</v>
+        <v>1.331725869002263</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.02635700945839403</v>
+        <v>0.5177843082541429</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.154309931724143</v>
+        <v>-0.5684143745907093</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.259150635545325</v>
+        <v>-0.7012984797523103</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.633716511082227</v>
+        <v>-2.058545486398273</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.2599919734800125</v>
+        <v>0.3171411551243608</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.9087083239844844</v>
+        <v>1.440908385872397</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.2352528008223942</v>
+        <v>0.7751946828147496</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.6854916102015238</v>
+        <v>0.231427593289979</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.7613238634247992</v>
+        <v>-0.1275617947002843</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.7287</t>
+          <t>X &lt; 0.7279</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.880283733150279</v>
+        <v>-1.716539771588856</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.8066098272747411</v>
+        <v>-0.223316172510124</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.068572538277557</v>
+        <v>-1.651923317879962</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.8449068394104415</v>
+        <v>-0.8530211688620994</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4038097302957979</v>
+        <v>0.4366380823429168</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8176747878321677</v>
+        <v>-1.145558746441608</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.469905161863359</v>
+        <v>-2.810205976065632</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.92417294464461</v>
+        <v>-2.941213375995993</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.122122382448218</v>
+        <v>-1.248067075007533</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.071094396512869</v>
+        <v>-1.870205526748613</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.325203768435458</v>
+        <v>-2.11970964257906</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.723671481742606</v>
+        <v>-1.352813336180787</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1461241978801482</v>
+        <v>0.3149032420206055</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5587860373338955</v>
+        <v>0.8662450024326702</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.07700958278685022</v>
+        <v>0.7067387041713147</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2104377104377164</v>
+        <v>0.396962583618155</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.049822219549227</v>
+        <v>-0.4037819396051177</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.507396609437428</v>
+        <v>-0.8850981005158474</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-2.349706286714159</v>
+        <v>-1.71593204061746</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.3991920464110379</v>
+        <v>0.2408146831871747</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.5757644809819311</v>
+        <v>1.172600955714778</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.2067952613458885</v>
+        <v>0.399358154527377</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.169069665471611</v>
+        <v>-0.2296077092343793</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.06822347346521</v>
+        <v>-0.3917467035238431</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.8016</t>
+          <t>X &lt; 0.8006</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.351334558040527</v>
+        <v>-1.41340499536463</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.39069038150113</v>
+        <v>-1.218783196707278</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.794736018419862</v>
+        <v>-1.739262907996796</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7351641885272997</v>
+        <v>-1.156922081841728</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5538607008161236</v>
+        <v>0.3296343155038741</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.145436037754159</v>
+        <v>-0.3944893472205209</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.80364764631215</v>
+        <v>-2.511157262536933</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.934148603620621</v>
+        <v>-2.375549071584317</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.1201355723706143</v>
+        <v>-0.6323485025756881</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.5976302735178862</v>
+        <v>-0.6941856071929706</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.1758601439113576</v>
+        <v>-0.4219505925886367</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2839428898636882</v>
+        <v>0.1825247216625385</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.114990571899746</v>
+        <v>1.857647288499578</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.280449938484978</v>
+        <v>2.13955920616295</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.918164629070098</v>
+        <v>2.045640118395546</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.8853326161018487</v>
+        <v>1.283414725450491</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2840874794555077</v>
+        <v>0.1501225490196063</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.3889281832766898</v>
+        <v>0.1642972673874183</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.7647527786837287</v>
+        <v>-0.2094757995844532</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.4575959898641884</v>
+        <v>1.034522410180408</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.336921397615889</v>
+        <v>1.880705215392418</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.6684828436141927</v>
+        <v>1.216441073407672</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.2422276290889371</v>
+        <v>0.5764231286418706</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.3180598823122125</v>
+        <v>0.2670087293450436</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.8745</t>
+          <t>X &lt; 0.8734</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.069418542003397</v>
+        <v>-0.7616959676111676</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9470524832103564</v>
+        <v>-0.6067153819962812</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.127928675098488</v>
+        <v>-0.8907817043863631</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.583739837398376</v>
+        <v>-0.6868244037634241</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1195303099456453</v>
+        <v>-0.05225740165570869</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.8468498381339771</v>
+        <v>-0.9192145806405492</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.190227093452897</v>
+        <v>-2.283124806752681</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.176839976584532</v>
+        <v>-2.132982679057775</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.07585622716410256</v>
+        <v>-0.1848034849595521</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.2105035893560654</v>
+        <v>-0.1844954807477208</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.0944838878574</v>
+        <v>0.9978646760636636</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3575443354976073</v>
+        <v>0.4937514360406041</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.868975624884328</v>
+        <v>2.109234745210998</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.947270415114914</v>
+        <v>2.157983432345446</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.977200512029768</v>
+        <v>2.50088599806859</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.080761745899366</v>
+        <v>1.695447420077322</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.7174868107567534</v>
+        <v>1.249881359149576</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.3047850857249799</v>
+        <v>0.3197307391816011</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.006324897461205</v>
+        <v>-0.2630735484790065</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.09795210516737285</v>
+        <v>0.8626746277872641</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.8865238128899406</v>
+        <v>1.503532399375842</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.9254884140525874</v>
+        <v>1.542394962939362</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.4073847494699407</v>
+        <v>0.3037033364731627</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.2056463727373199</v>
+        <v>0.5976646842589588</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.9473</t>
+          <t>X &lt; 0.9462</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8693968476764624</v>
+        <v>-0.5077253624049902</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.02425613062676746</v>
+        <v>0.2737291544846983</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3224575504784326</v>
+        <v>-0.0280300973169858</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2563817431487365</v>
+        <v>0.3339518845351606</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4525061642184909</v>
+        <v>0.5907131360708036</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1963939110823034</v>
+        <v>-0.240946413824652</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.7403790691367931</v>
+        <v>-0.8839371713045168</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.127862764170132</v>
+        <v>-1.264903242089559</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2064000831438122</v>
+        <v>0.003710078240935388</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.390478695004262</v>
+        <v>0.1962517389151373</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.470667422150562</v>
+        <v>1.381034282036573</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.496563867902864</v>
+        <v>1.484680464447408</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.353599820848729</v>
+        <v>2.270929031407292</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.026986235208895</v>
+        <v>1.992948050285072</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.864977893257063</v>
+        <v>2.985070685142787</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.93381180223286</v>
+        <v>2.176511690263816</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.799894665255387</v>
+        <v>2.072631278538807</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.313665708192403</v>
+        <v>1.63533317033307</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.071891185226569</v>
+        <v>1.393174392912634</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.335014645842961</v>
+        <v>1.607760837971618</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.754789647545209</v>
+        <v>2.00027534619047</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.526271930410907</v>
+        <v>1.772789899635029</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.5030367192288452</v>
+        <v>0.8740024504122701</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.732547977455944</v>
+        <v>0.9101038477041783</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 1.02</t>
+          <t>X &lt; 1.019</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1499180315188227</v>
+        <v>-0.1874712452955478</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1802443738279891</v>
+        <v>-0.07674317080136461</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3619345969430015</v>
+        <v>0.5001912310716676</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3640520846509787</v>
+        <v>0.4845887147207009</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.191760390096519</v>
+        <v>-0.03365930040364873</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.444838208399581</v>
+        <v>-0.4781472362317061</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.8317483884395429</v>
+        <v>-0.8905064491205223</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.40923577069281</v>
+        <v>-1.383797335657306</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3771046702310485</v>
+        <v>-0.2950197891266626</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.09276984621219242</v>
+        <v>0.167823077996637</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.01319300338000318</v>
+        <v>0.08830026265452773</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5608898809237388</v>
+        <v>0.6879505097166287</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8702347011199691</v>
+        <v>0.9969357197576443</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6271354809130329</v>
+        <v>0.781380318169397</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.160405904278406</v>
+        <v>1.359499908887074</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.347080072245639</v>
+        <v>1.537242283871123</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.9924123833917804</v>
+        <v>1.21418378995434</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.7771964036324093</v>
+        <v>0.971710643696845</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.606774318773077</v>
+        <v>0.8026112270069987</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.8488077667101877</v>
+        <v>1.071992192613926</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.333403799399221</v>
+        <v>1.57904901303084</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.9262491687466081</v>
+        <v>1.153346124800571</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.1515797619575423</v>
+        <v>0.4423232949935638</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.130965620274857</v>
+        <v>0.3129463625378932</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 1.093</t>
+          <t>X &lt; 1.092</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2218</v>
+        <v>2224</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7708919564812931</v>
+        <v>-0.774769585253452</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1846862715843827</v>
+        <v>-0.1485156986961087</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.162296461710433</v>
+        <v>-0.08344214291783913</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3814820143584967</v>
+        <v>0.4662923527409788</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.08895836842217619</v>
+        <v>-0.05251179710019471</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.4405918232583659</v>
+        <v>-0.4769735399393156</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7188241696262807</v>
+        <v>-0.8248283607587936</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.7023214043295312</v>
+        <v>-0.7916170332277801</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.03218581648756924</v>
+        <v>-0.1014398514662105</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3437088886066419</v>
+        <v>0.292219754117454</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1945778425789442</v>
+        <v>0.1423286930918195</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2304351807039779</v>
+        <v>0.2689725450721312</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3657000801400017</v>
+        <v>0.3637578469761991</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.216361564213976</v>
+        <v>0.3212635328958839</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.6646610476312915</v>
+        <v>0.786737454190849</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.016351635163517</v>
+        <v>1.105941313474666</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.044742489453434</v>
+        <v>1.208576451226804</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.8771307750899666</v>
+        <v>1.075692346065203</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.8227518857440117</v>
+        <v>1.110621359566458</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.9645526506669952</v>
+        <v>1.235441197803183</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.125147659028265</v>
+        <v>1.458321734574263</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.8964493132398133</v>
+        <v>1.185874479915583</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2692107705370148</v>
+        <v>0.6028334147532988</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.3737211683507056</v>
+        <v>0.6024840898519273</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 1.166</t>
+          <t>X &lt; 1.165</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2481</v>
+        <v>2494</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.614795009223549</v>
+        <v>-0.6155060590544466</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.0740954146015369</v>
+        <v>0.1556895437552512</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1018002802622391</v>
+        <v>0.1979042593637033</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3515418083525859</v>
+        <v>0.5047210126787078</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1045856076363236</v>
+        <v>0.0122264349556005</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1984056229027544</v>
+        <v>-0.2297230862900363</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3285572751043802</v>
+        <v>-0.4264804076571735</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6642651834708246</v>
+        <v>-0.7090054576088178</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.05940498399765204</v>
+        <v>0.1199794406567918</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.31312258744628</v>
+        <v>0.3849688030194045</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1286963390366793</v>
+        <v>0.2009143043368198</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2749817473951737</v>
+        <v>0.3638049827061067</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.276769459566772</v>
+        <v>0.407522533653264</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1197828786094135</v>
+        <v>0.262825299170899</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.2093379016853305</v>
+        <v>0.4040026557335494</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.5061678734245163</v>
+        <v>0.7492970783916775</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.5573516880941725</v>
+        <v>0.869410264105646</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.4364727257362588</v>
+        <v>0.8005709922496607</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.1692723192209726</v>
+        <v>0.5746809375699726</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.1145722354691898</v>
+        <v>0.5090432032854793</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.1597909848833794</v>
+        <v>0.606127120795243</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.1081223219321501</v>
+        <v>0.4348075437071373</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.06059394060593348</v>
+        <v>0.3417269321251197</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.2333270236978606</v>
+        <v>0.04308397562093802</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 1.239</t>
+          <t>X &lt; 1.237</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2656</v>
+        <v>2670</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4397988169138074</v>
+        <v>-0.3630060512790578</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.3801182938042587</v>
+        <v>-0.2543073733382784</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.2251730751557588</v>
+        <v>0.3717332572563592</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3364978118014292</v>
+        <v>0.5445637319116372</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.00070733925415567</v>
+        <v>0.1409535223882585</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1120642041351587</v>
+        <v>-0.07455235019838824</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.2470702128662694</v>
+        <v>-0.2364872488370722</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3915484118405885</v>
+        <v>-0.3713954533626662</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1587254341099253</v>
+        <v>0.1875744035450353</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.6076562770710154</v>
+        <v>0.643168658641919</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2283067883385783</v>
+        <v>0.2657078687324201</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.196558607501558</v>
+        <v>0.3090945158633289</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.0118349790838792</v>
+        <v>0.1643516521438997</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.0007435967028897039</v>
+        <v>0.1620324731853202</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.07159703964897091</v>
+        <v>0.1367309236496723</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.1319565440196797</v>
+        <v>0.384142054110761</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.1708219835511287</v>
+        <v>0.4519338565022437</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.1636775700985851</v>
+        <v>0.4534671409443192</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.04109584083110462</v>
+        <v>0.3910785582843417</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.1105314593926749</v>
+        <v>0.2316934251832663</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.02885069501851234</v>
+        <v>0.3597409223777177</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.1574556277890906</v>
+        <v>0.1198125337270923</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.3722545321681565</v>
+        <v>-0.02607718978399021</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.5010696993581831</v>
+        <v>-0.2409535196110681</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 1.312</t>
+          <t>X &lt; 1.31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2763</v>
+        <v>2780</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3674658184679416</v>
+        <v>-0.2736020764492864</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1433101298458368</v>
+        <v>-0.07159289190595786</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2379049153571344</v>
+        <v>0.3375374397640911</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3528846612131744</v>
+        <v>0.5160153429249235</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.01709418866590084</v>
+        <v>0.1174345356368462</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2279050680012986</v>
+        <v>-0.2265263127479002</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.0639286259017311</v>
+        <v>-0.0913757668410895</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3576303690614822</v>
+        <v>-0.3760893524673179</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.06460895659468235</v>
+        <v>0.05849124626147528</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3934405609798333</v>
+        <v>0.3930933395775327</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1838846481491245</v>
+        <v>0.1844668252601096</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.03422534022779899</v>
+        <v>0.1435245163983012</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.04313795273722576</v>
+        <v>0.1039012161518258</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.02643121455002273</v>
+        <v>0.09186131739826209</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.2661769988214857</v>
+        <v>-0.06698541962454385</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.1195164642818085</v>
+        <v>0.1209798914523077</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.1597715642403514</v>
+        <v>0.1101115697535278</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.0263738856401261</v>
+        <v>0.2498395633003909</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.07803505949540579</v>
+        <v>0.1983166277313018</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.1803110420824936</v>
+        <v>0.08962721072131075</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.0868755012352409</v>
+        <v>0.2619987517326052</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.2134406712207166</v>
+        <v>0.02855005508983766</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.1706191175383154</v>
+        <v>0.1137845316823842</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.33350203456218</v>
+        <v>-0.1708972051121052</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 1.385</t>
+          <t>X &lt; 1.383</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2874</v>
+        <v>2890</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.5288139184112168</v>
+        <v>-0.4659680825279224</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3609577063165474</v>
+        <v>-0.2809682268130942</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.08808714299345155</v>
+        <v>0.2371300914318937</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.06717464604206214</v>
+        <v>0.2487472862083706</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3378199787543394</v>
+        <v>-0.1452671784518174</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3737251780934372</v>
+        <v>-0.2637208357928031</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.2110944227314491</v>
+        <v>-0.1293708342561644</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4349996778973093</v>
+        <v>-0.3459923914469414</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2006165549651371</v>
+        <v>-0.1641508863571204</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.1896983572376243</v>
+        <v>0.2308941646186611</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.1026650039911274</v>
+        <v>0.1438576430645711</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1560534699090468</v>
+        <v>0.2663770686168121</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.03090887433958045</v>
+        <v>0.1170021925453497</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1274112843126076</v>
+        <v>0.02701532693481568</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.1751178958037301</v>
+        <v>0.02081569587291199</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.1153061331818677</v>
+        <v>0.1194317004144523</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.1938918844522135</v>
+        <v>0.07049953959484156</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.1044256336981206</v>
+        <v>0.1653132178090431</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.2152875435393327</v>
+        <v>0.08931683426244774</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.30641254663594</v>
+        <v>-0.007084972233514009</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.09852447578619206</v>
+        <v>0.2408218342993678</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.3274477183803484</v>
+        <v>-0.09034805795261747</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.275721993018081</v>
+        <v>0.0008722722692695584</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.4352793982791212</v>
+        <v>-0.2445822017514772</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 1.457</t>
+          <t>X &lt; 1.456</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2943</v>
+        <v>2960</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.5844472485214567</v>
+        <v>-0.5046945360998549</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.191840127998006</v>
+        <v>-0.1283589499796776</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.07807721492227415</v>
+        <v>0.1801515751404423</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.04102721710846424</v>
+        <v>0.2447464795717522</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1257872500315855</v>
+        <v>0.02158510463009122</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.291648447232788</v>
+        <v>-0.2248426339096383</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1508182264578224</v>
+        <v>-0.1123616209322762</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3759703030255324</v>
+        <v>-0.3310557782649326</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1122403568712045</v>
+        <v>-0.04957046054987302</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.318624628295872</v>
+        <v>0.3847538038149096</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.3077741941266368</v>
+        <v>0.3735513001572457</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2857436272656528</v>
+        <v>0.4194015664688919</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.04304210900419037</v>
+        <v>0.2136003581090336</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.02247175937105794</v>
+        <v>0.1535964141751478</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.01724447162672504</v>
+        <v>0.2325752698145962</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.0120698510529067</v>
+        <v>0.2410665424968244</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.05800542576566414</v>
+        <v>0.2245940098898558</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.006962273182196554</v>
+        <v>0.2803571820784185</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.07620781369074336</v>
+        <v>0.244997487706172</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.1608245079643211</v>
+        <v>0.1559402080687988</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.004407711533993108</v>
+        <v>0.3508900229129495</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.1957566080615933</v>
+        <v>0.02580743117056272</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.1387654712789512</v>
+        <v>0.1206701613732193</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.2623344320913503</v>
+        <v>-0.05520597431295471</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 1.53</t>
+          <t>X &lt; 1.529</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3022</v>
+        <v>3040</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3688970969900041</v>
+        <v>-0.3073326104635399</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2585186486238911</v>
+        <v>-0.1435515435464083</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1309440743961758</v>
+        <v>0.287053563855757</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.05552096840951037</v>
+        <v>0.1380044174615236</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.06225583055863382</v>
+        <v>0.07703189067435545</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3833870336573497</v>
+        <v>-0.3369057897775534</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2007603390091859</v>
+        <v>-0.1827242995552822</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4273265385822853</v>
+        <v>-0.403700207236561</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2353458603379508</v>
+        <v>-0.1917717703179136</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1637479359000551</v>
+        <v>0.2102548983468324</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.004440029774087861</v>
+        <v>0.04254649582174608</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.06556708185127746</v>
+        <v>0.1781916531278398</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.08195934294262486</v>
+        <v>0.04690609305411186</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.08558427601254692</v>
+        <v>0.08030159035834572</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.03108059130992302</v>
+        <v>0.172087547760988</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.1762007663295222</v>
+        <v>0.06379658610418204</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.1254106720641417</v>
+        <v>0.1434600021886538</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.1445301325967208</v>
+        <v>0.1285588340830586</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.1072362649976029</v>
+        <v>0.1982694272842167</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.1847658681161519</v>
+        <v>0.1171922718175722</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.04661089500731919</v>
+        <v>0.2592238174424679</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.301093875962529</v>
+        <v>-0.09218949771297957</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.2384540904162904</v>
+        <v>0.006548189239822477</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.3277174551729729</v>
+        <v>-0.1690039828478191</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 1.603</t>
+          <t>X &lt; 1.601</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3095</v>
+        <v>3113</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1726390209464199</v>
+        <v>-0.1603676343007763</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2332532082803382</v>
+        <v>-0.1338894527388206</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.08121565101242112</v>
+        <v>0.1930430878060818</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.04306882951313185</v>
+        <v>0.1931788228060682</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.02861511789129167</v>
+        <v>0.1590995353224969</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3448523178143716</v>
+        <v>-0.2732700585707732</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.24891286284263</v>
+        <v>-0.2054565770355268</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5731698197861306</v>
+        <v>-0.5243335805995741</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.352604988602998</v>
+        <v>-0.3144315582599901</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.0132518457125812</v>
+        <v>0.02720469328532715</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1067352489179711</v>
+        <v>-0.06614442518775121</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.01276211051201415</v>
+        <v>0.05970127719113805</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.02222081584147872</v>
+        <v>0.06516767446507288</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.03094059405940186</v>
+        <v>0.09189576038117764</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.1220922706280376</v>
+        <v>0.03721791543364361</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.2176015473887745</v>
+        <v>-0.02319891648177475</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2034206207021754</v>
+        <v>0.0200320512820511</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1278096492052967</v>
+        <v>0.09847677439380931</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.08630334567326514</v>
+        <v>0.2036849746675173</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.2866792201195665</v>
+        <v>0.02020811853497406</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.1645969057100345</v>
+        <v>0.1455873099927558</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.3180393582777228</v>
+        <v>-0.1030803642650397</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.282709971896864</v>
+        <v>-0.03306246683979452</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.3393606661331958</v>
+        <v>-0.1761894698547621</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 1.676</t>
+          <t>X &lt; 1.674</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3173</v>
+        <v>3194</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02355929633206699</v>
+        <v>0.00214939129238445</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.09091213233315898</v>
+        <v>0.0217308218775969</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.08620034849465696</v>
+        <v>0.2150175116430475</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.08029957146862898</v>
+        <v>0.2311612963945393</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.08933668512825221</v>
+        <v>0.2220623067188967</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1763306426853433</v>
+        <v>-0.1018096773448889</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.101618931467506</v>
+        <v>-0.05603214426461989</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3306002159260046</v>
+        <v>-0.2810481315154334</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2398519793581926</v>
+        <v>-0.1978143889479469</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.04091854744086021</v>
+        <v>0.0836055976143939</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.04354679361953373</v>
+        <v>-0.0003782886115146766</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.04131542462019411</v>
+        <v>0.1151950177208647</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.004582203216600078</v>
+        <v>0.1103315808933019</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.009334685825592715</v>
+        <v>0.1301224726680559</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.145819195003682</v>
+        <v>0.02836770833879854</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.1929674099485368</v>
+        <v>0.01490607277018086</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.18241247093993</v>
+        <v>0.05442635114027183</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1112238476258938</v>
+        <v>0.1275325615050633</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.1913358563890526</v>
+        <v>0.07921735820382025</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.1933474590744666</v>
+        <v>0.09340112113945764</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.1190446439924742</v>
+        <v>0.1699703263234511</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.3650546308681655</v>
+        <v>-0.1368705956337095</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1978391952865195</v>
+        <v>0.03143498673199474</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.1919028396723519</v>
+        <v>-0.01822785655838288</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 1.749</t>
+          <t>X &lt; 1.747</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3223</v>
+        <v>3244</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.07932999964843646</v>
+        <v>-0.05211846111733109</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1199792479939958</v>
+        <v>-0.005991450491336536</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1556257834019803</v>
+        <v>0.2570174323331642</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.01537832838646125</v>
+        <v>0.1719092099570716</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1043627614447615</v>
+        <v>0.03608360789405651</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1778602910956479</v>
+        <v>-0.1271461496121447</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.05447090768127794</v>
+        <v>-0.03293040042199635</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2533145639714434</v>
+        <v>-0.1978151364654508</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1941961596806578</v>
+        <v>-0.1752386533791395</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.03940543809427766</v>
+        <v>0.05895880452957414</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.05321667695714183</v>
+        <v>0.07254516646099773</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1634085743515286</v>
+        <v>0.2128313598986793</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.01381315590541732</v>
+        <v>0.06805892224500809</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.03094059405940186</v>
+        <v>0.1451812460053219</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.05170382354958036</v>
+        <v>0.09599182993782307</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.08889201613659736</v>
+        <v>0.09138809930188074</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.1115112884644702</v>
+        <v>0.09796665128678939</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.07400623552660335</v>
+        <v>0.137147946120443</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1185318212663731</v>
+        <v>0.1236583774473914</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.1795942852369876</v>
+        <v>0.07936448494135107</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.1148477925290052</v>
+        <v>0.1460123097852062</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.3272105241722016</v>
+        <v>-0.1264601704025452</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.2203546394740172</v>
+        <v>-0.01862396998726012</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2156937867720643</v>
+        <v>-0.07003584734258794</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 1.822</t>
+          <t>X &lt; 1.82</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3263</v>
+        <v>3283</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1085694033223419</v>
+        <v>-0.04792173567489044</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1224408475112995</v>
+        <v>0.02502575821942798</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.07081773388558332</v>
+        <v>0.2398483258168085</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.04613370686325879</v>
+        <v>0.1487432426934774</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1076175655732783</v>
+        <v>0.07184743919130199</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1778602910956479</v>
+        <v>-0.1178907622518821</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1266382432786841</v>
+        <v>-0.09479095630278067</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3264963084320911</v>
+        <v>-0.2916621285824164</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2676207540076518</v>
+        <v>-0.2072254582173869</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.07715026176234829</v>
+        <v>-0.01555505398681589</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.06011752447597729</v>
+        <v>-0.02927063877999103</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.04517057825093929</v>
+        <v>0.1060505550905688</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.02175847998299929</v>
+        <v>0.1015509017972747</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.01089018159376565</v>
+        <v>0.1444626555475566</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1007587082658787</v>
+        <v>0.08777434754284741</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.06890210574099598</v>
+        <v>0.1506462123935037</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.1234917825154156</v>
+        <v>0.1255382472137754</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.0877757037351472</v>
+        <v>0.1626876238340387</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.1290383377720374</v>
+        <v>0.1519096304999792</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.1076766033804333</v>
+        <v>0.1411188059641617</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.1115828322723047</v>
+        <v>0.1698275418239064</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2303884626078059</v>
+        <v>-0.008970995105649138</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1520860168885037</v>
+        <v>0.0700630196473071</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.1790376237680391</v>
+        <v>-0.01309715821693658</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 1.895</t>
+          <t>X &lt; 1.892</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3290</v>
+        <v>3312</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.001463241489950917</v>
+        <v>0.02665941466084831</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07834294501441263</v>
+        <v>0.03684897443935853</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.01926399435764381</v>
+        <v>0.08882515542240554</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.08064776622891401</v>
+        <v>0.05335242308704835</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.1443705241449891</v>
+        <v>-0.02530211872771559</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1822854941018406</v>
+        <v>-0.1519714307573068</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1680231105594743</v>
+        <v>-0.1359990723081381</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3382855695775149</v>
+        <v>-0.3037760850260867</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2795556355218736</v>
+        <v>-0.2189639529887373</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1574941509718357</v>
+        <v>-0.1261076418365903</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1383847008357932</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.02430882895257724</v>
+        <v>0.08458529302446749</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1118535382732162</v>
+        <v>-0.0198911423099446</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1029102910290973</v>
+        <v>0.02044244446730659</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1974576412610531</v>
+        <v>-0.04174497114163245</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.2519892680596101</v>
+        <v>-0.0649197890782105</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3072841097075099</v>
+        <v>-0.09078098322788009</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.2727751988451388</v>
+        <v>-0.05518292975473571</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.2816377846547553</v>
+        <v>-0.03390964306456112</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2589659499007837</v>
+        <v>-0.01262865772564226</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2065996515231419</v>
+        <v>0.04098439447086832</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.3250818024413391</v>
+        <v>-0.1369461275863699</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.2451986949588232</v>
+        <v>-0.05650992795180798</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2725797517257007</v>
+        <v>-0.1102066271396964</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 1.968</t>
+          <t>X &lt; 1.965</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3314</v>
+        <v>3335</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.002331297362637486</v>
+        <v>0.04688771931269287</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1363917582124969</v>
+        <v>0.02553079852164331</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.02810440695738947</v>
+        <v>0.09835206603761293</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.004148000663683149</v>
+        <v>0.1485084777636061</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0998424347955833</v>
+        <v>0.06853164942755541</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.136123758449628</v>
+        <v>-0.056163706491418</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1575470745825527</v>
+        <v>-0.1054223297026553</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.2985543683218097</v>
+        <v>-0.2442896802789463</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2399368088081104</v>
+        <v>-0.1591637654682714</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1243175817783069</v>
+        <v>-0.07239436962189671</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1334161324905381</v>
+        <v>-0.08168564382575028</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.02609349416212581</v>
+        <v>0.1069754428685883</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1472677326503984</v>
+        <v>-0.06421263936923793</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1099117131929788</v>
+        <v>0.004018891382330025</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1483451013901842</v>
+        <v>-0.002628949997365737</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1981737908890153</v>
+        <v>-0.02177082468939773</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2239091985142494</v>
+        <v>-0.01823384201077261</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1903825213389894</v>
+        <v>0.01622606644370705</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2277246227017642</v>
+        <v>0.008910956315503427</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1737103863302139</v>
+        <v>0.06148539663285391</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.1557705708071708</v>
+        <v>0.1108413458701278</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2739288080857634</v>
+        <v>-0.06635992208049402</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1926214618357136</v>
+        <v>0.01522260452507851</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.250512552242256</v>
+        <v>-0.0691854710510782</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 2.04</t>
+          <t>X &lt; 2.038</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3330</v>
+        <v>3354</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.001228975007151689</v>
+        <v>0.04149649463821703</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1111058574696315</v>
+        <v>0.0188738435929352</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1002101249918752</v>
+        <v>0.02494068047059983</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.02029659207993717</v>
+        <v>0.1307502125684366</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.07051170608832535</v>
+        <v>0.04966608791308147</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1355945562184004</v>
+        <v>-0.07344751638473213</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1606056840884449</v>
+        <v>-0.1565746190950534</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2723835471719056</v>
+        <v>-0.2667197622687354</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2138401028212797</v>
+        <v>-0.1813591110910053</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1024644349251602</v>
+        <v>-0.09957658943579872</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1102012194893689</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.01262723902718932</v>
+        <v>0.01932234286026357</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.07082400435330527</v>
+        <v>-0.008631870066729164</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.06462322878994087</v>
+        <v>0.02810225715267478</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.135961699366824</v>
+        <v>-0.01209019942292855</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.1527407084626944</v>
+        <v>0.001789642341698539</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2089482391287376</v>
+        <v>-0.02502665377368629</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.1760807097762012</v>
+        <v>0.008484942457442912</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2122036094813424</v>
+        <v>0.002421999130142183</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.2475292572757368</v>
+        <v>-0.033427700179395</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.2022991911096597</v>
+        <v>0.04219750087243312</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.290256207561832</v>
+        <v>-0.1046491507704204</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.2380469248181782</v>
+        <v>-0.0519665651525969</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2960378602901983</v>
+        <v>-0.1368350094303707</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 2.113</t>
+          <t>X &lt; 2.111</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3345</v>
+        <v>3368</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.05680658422173224</v>
+        <v>0.09936678412767463</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.08376413756906942</v>
+        <v>0.04627469577255283</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1090367200995459</v>
+        <v>0.0172621542998499</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.002934673477867022</v>
+        <v>0.1494941024278802</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.05441837757233969</v>
+        <v>0.03802959207963141</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.0588834915715637</v>
+        <v>-0.02478009264977743</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.08722717843632921</v>
+        <v>-0.0943881095188388</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1699729454827192</v>
+        <v>-0.1757698566209243</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1114751658150865</v>
+        <v>-0.09020615917517461</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.03378869268586016</v>
+        <v>-0.041598836598709</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.04024625683817362</v>
+        <v>-0.04813318590944249</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.05566704569847047</v>
+        <v>0.07682391619893281</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.007269345741534039</v>
+        <v>0.04438327856345836</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.09148455829188862</v>
+        <v>-0.008857887139733123</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1356402422660707</v>
+        <v>-0.02211058271404198</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1496850400816996</v>
+        <v>-0.005963585115431158</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2062394050037923</v>
+        <v>-0.03310185185185333</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1739874873085085</v>
+        <v>-0.0002830875761432594</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.208981340019065</v>
+        <v>-0.005433316893189044</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2433109310395167</v>
+        <v>-0.01058958479551819</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2007130109862629</v>
+        <v>0.0623716774492209</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.2886152763163139</v>
+        <v>-0.08417119021967068</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2354090950737557</v>
+        <v>-0.03068901880315167</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.2934792478661095</v>
+        <v>-0.115872341392631</v>
       </c>
     </row>
   </sheetData>
